--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -866,13 +866,13 @@
         <v>2.98</v>
       </c>
       <c r="I2" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
         <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>5.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="I3" t="n">
         <v>2.02</v>
@@ -1144,7 +1144,7 @@
         <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="G4" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
         <v>4.4</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I6" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Q6" t="n">
         <v>2.42</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -3914,13 +3914,13 @@
         <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J14" t="n">
         <v>3.2</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="Q14" t="n">
         <v>2.16</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="G15" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="H15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J15" t="n">
         <v>3.9</v>
@@ -4192,7 +4192,7 @@
         <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,13 +866,13 @@
         <v>2.98</v>
       </c>
       <c r="I2" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J2" t="n">
         <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q2" t="n">
         <v>2</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="I3" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="J3" t="n">
         <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,31 +1356,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.91</v>
+        <v>1.46</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1</v>
+        <v>1.54</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,31 +1610,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IF Vestri</t>
+          <t>Central Espanol</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>Racing Club (Uru)</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,36 +1859,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Racing Club (Uru)</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,31 +2118,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
@@ -2372,28 +2372,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>2.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>Jonkopings Sodra</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>FC Trollhattan</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
@@ -2880,12 +2880,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Jonkopings Sodra</t>
+          <t>Gefle</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Trollhattan</t>
+          <t>Hammarby TFF</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,36 +3129,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gefle</t>
+          <t>Deportes Copiapo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hammarby TFF</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>7.6</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
@@ -3388,31 +3388,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Deportes Copiapo</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa Calama</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,36 +3637,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Torque</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cobreloa Calama</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
@@ -3891,36 +3891,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Torque</t>
+          <t>Nacional (Uru)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.42</v>
+        <v>1.67</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7</v>
+        <v>1.78</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="I14" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="K14" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.69</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,36 +4145,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Cavalry</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="H15" t="n">
-        <v>5.4</v>
+        <v>2.14</v>
       </c>
       <c r="I15" t="n">
-        <v>7.2</v>
+        <v>19.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
@@ -4404,31 +4404,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>FC Supra du Quebec</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>1.7</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,261 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>FC Supra du Quebec</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Pacific</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K17" t="n">
-        <v>950</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB17" t="inlineStr">
-        <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -890,7 +890,7 @@
         <v>1.83</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
         <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="G4" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="H4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I4" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
         <v>6.6</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -1625,10 +1625,10 @@
         <v>5.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="I5" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="J5" t="n">
         <v>3.1</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="G7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H7" t="n">
         <v>3.5</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>2.32</v>
       </c>
       <c r="G8" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="I8" t="n">
         <v>3.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>1.62</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.08</v>
+        <v>1.31</v>
       </c>
       <c r="G11" t="n">
         <v>3.05</v>
@@ -3158,7 +3158,7 @@
         <v>2.82</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="G13" t="n">
         <v>2.7</v>
@@ -3660,7 +3660,7 @@
         <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J13" t="n">
         <v>3.2</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="Q13" t="n">
         <v>2.1</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
         <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="H15" t="n">
-        <v>2.14</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
-        <v>19.5</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,217 +860,217 @@
         <v>2.4</v>
       </c>
       <c r="G2" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H2" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="I2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
@@ -1117,214 +1117,214 @@
         <v>4.9</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="I3" t="n">
         <v>2.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
         <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IF Vestri</t>
+          <t>Vendsyssel FF</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>Naestved</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
-        <v>6.6</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P4" t="n">
-        <v>2.88</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.45</v>
+        <v>1.03</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Racing Club (Uru)</t>
+          <t>Thisted</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="H5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="I5" t="n">
-        <v>2.14</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.42</v>
+        <v>1.21</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Skive</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ishoj IF</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P6" t="n">
         <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Brabrand</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>Fremad Amager</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="G7" t="n">
-        <v>2.02</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="I7" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.73</v>
+        <v>1.02</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>VSK Aarhus FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>FC Helsingor</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P8" t="n">
-        <v>2.88</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.44</v>
+        <v>1.03</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Jonkopings Sodra</t>
+          <t>Roskilde</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Trollhattan</t>
+          <t>HIK Hellerup</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,36 +2875,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Gefle</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hammarby TFF</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>1.48</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>2.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,36 +3129,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deportes Copiapo</t>
+          <t>Central Espanol</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Racing Club (Uru)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.31</v>
+        <v>4.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="H11" t="n">
-        <v>2.58</v>
+        <v>1.92</v>
       </c>
       <c r="I11" t="n">
-        <v>4.2</v>
+        <v>2.12</v>
       </c>
       <c r="J11" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.6</v>
+        <v>2.42</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,36 +3383,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Gefle</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cobreloa Calama</t>
+          <t>Hammarby TFF</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.98</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,36 +3637,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Torque</t>
+          <t>Jonkopings Sodra</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>FC Trollhattan</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,36 +3891,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,36 +4145,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="G15" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,261 +4382,1785 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Grotta</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Grindavik</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>950</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-06-04 09:43:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Deportes Copiapo</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Santiago Wanderers</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K17" t="n">
+        <v>950</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-06-04 09:43:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Cobreloa Calama</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-06-04 09:43:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-06-04 09:43:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Juventud De Las Piedras</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-06-04 09:43:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Canadian Premier League</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Cavalry</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>HFX Wanderers</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-06-04 09:43:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>FC Supra du Quebec</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Pacific</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="F22" t="n">
         <v>1.54</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G22" t="n">
         <v>1.7</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H22" t="n">
         <v>4.5</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I22" t="n">
         <v>7.4</v>
       </c>
-      <c r="J16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="J22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K22" t="n">
         <v>5.2</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q22" t="n">
         <v>1.56</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB16" t="inlineStr">
-        <is>
-          <t>2026-06-04 07:35:20</t>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -866,7 +866,7 @@
         <v>2.94</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
         <v>3.25</v>
@@ -875,7 +875,7 @@
         <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -896,7 +896,7 @@
         <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T2" t="n">
         <v>1.78</v>
@@ -905,10 +905,10 @@
         <v>2.06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X2" t="n">
         <v>15.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>4.1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H3" t="n">
         <v>1.94</v>
@@ -1123,7 +1123,7 @@
         <v>2.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
         <v>3.8</v>
@@ -1141,7 +1141,7 @@
         <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
         <v>2.02</v>
@@ -1153,16 +1153,16 @@
         <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U3" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V3" t="n">
         <v>1.91</v>
       </c>
       <c r="W3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
         <v>15.5</v>
@@ -1204,7 +1204,7 @@
         <v>120</v>
       </c>
       <c r="AK3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AL3" t="n">
         <v>85</v>
@@ -1243,7 +1243,7 @@
         <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -1252,22 +1252,22 @@
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG3" t="n">
         <v>12</v>
@@ -1276,19 +1276,19 @@
         <v>3.35</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN3" t="n">
         <v>8</v>
@@ -1300,13 +1300,13 @@
         <v>40</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR3" t="n">
         <v>55</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT3" t="n">
         <v>4.8</v>
@@ -1318,13 +1318,13 @@
         <v>15.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BX3" t="n">
         <v>32</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1365,166 +1365,166 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>1.87</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O4" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>2.22</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="S4" t="n">
-        <v>1.02</v>
+        <v>2.18</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1</v>
+        <v>1.59</v>
       </c>
       <c r="H5" t="n">
-        <v>1.94</v>
+        <v>6.4</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>5.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,94 +1643,94 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>2.66</v>
       </c>
       <c r="O5" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.21</v>
+        <v>1.54</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>1.21</v>
+        <v>2.32</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9</v>
+        <v>2.72</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
         <v>1.03</v>
@@ -1739,37 +1739,37 @@
         <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
         <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
         <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
         <v>1.03</v>
@@ -1787,7 +1787,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK5" t="n">
         <v>1.01</v>
@@ -1799,25 +1799,25 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO5" t="n">
         <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ5" t="n">
         <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS5" t="n">
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BU5" t="n">
         <v>1.01</v>
@@ -1835,14 +1835,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA5" t="n">
         <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1873,112 +1873,112 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>1.88</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="S6" t="n">
-        <v>1.26</v>
+        <v>2.32</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP6" t="n">
         <v>1.01</v>
@@ -2035,68 +2035,68 @@
         <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -2127,112 +2127,112 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>3.35</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.02</v>
+        <v>1.84</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP7" t="n">
         <v>1.01</v>
@@ -2244,7 +2244,7 @@
         <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
         <v>1.01</v>
@@ -2280,7 +2280,7 @@
         <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -2289,68 +2289,68 @@
         <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -2381,112 +2381,112 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="H8" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O8" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.03</v>
+        <v>1.63</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>1.02</v>
+        <v>2.54</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF8" t="n">
         <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.51</v>
       </c>
       <c r="H9" t="n">
-        <v>1.28</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>8.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="S9" t="n">
-        <v>1.18</v>
+        <v>2.04</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -2889,230 +2889,230 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="G10" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="I10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="K10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P10" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>4.5</v>
       </c>
       <c r="G11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H11" t="n">
         <v>1.92</v>
@@ -3158,215 +3158,215 @@
         <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P11" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -3415,212 +3415,212 @@
         <v>950</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="R12" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -3669,202 +3669,202 @@
         <v>950</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -3905,230 +3905,230 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -4159,230 +4159,230 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G15" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="I15" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K15" t="n">
         <v>4.5</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -4413,230 +4413,230 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="G16" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="H16" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I16" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>1.03</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P16" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="G17" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="H17" t="n">
-        <v>1.49</v>
+        <v>3.3</v>
       </c>
       <c r="I17" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="J17" t="n">
-        <v>2.82</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
         <v>2.7</v>
       </c>
       <c r="I18" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J18" t="n">
         <v>3.25</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G19" t="n">
         <v>2.7</v>
@@ -5184,13 +5184,13 @@
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J19" t="n">
         <v>3.15</v>
       </c>
       <c r="K19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q19" t="n">
         <v>2.12</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
         <v>2.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G21" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H21" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I21" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -5716,7 +5716,7 @@
         <v>2.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -5943,13 +5943,13 @@
         <v>1.7</v>
       </c>
       <c r="H22" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="I22" t="n">
         <v>7.4</v>
       </c>
       <c r="J22" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K22" t="n">
         <v>5.2</v>
@@ -5967,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -872,10 +872,10 @@
         <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -899,7 +899,7 @@
         <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
         <v>2.06</v>
@@ -908,7 +908,7 @@
         <v>1.41</v>
       </c>
       <c r="W2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X2" t="n">
         <v>15.5</v>
@@ -974,7 +974,7 @@
         <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT2" t="n">
         <v>7.8</v>
@@ -986,7 +986,7 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -998,25 +998,25 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -1117,10 +1117,10 @@
         <v>4.8</v>
       </c>
       <c r="H3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J3" t="n">
         <v>3.6</v>
@@ -1129,19 +1129,19 @@
         <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
         <v>2.02</v>
@@ -1153,10 +1153,10 @@
         <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V3" t="n">
         <v>1.91</v>
@@ -1168,22 +1168,22 @@
         <v>15.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA3" t="n">
         <v>29</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
         <v>28</v>
@@ -1192,10 +1192,10 @@
         <v>40</v>
       </c>
       <c r="AG3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
         <v>50</v>
@@ -1213,7 +1213,7 @@
         <v>140</v>
       </c>
       <c r="AN3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AO3" t="n">
         <v>20</v>
@@ -1234,7 +1234,7 @@
         <v>10.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
         <v>7.8</v>
@@ -1243,7 +1243,7 @@
         <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -1252,22 +1252,22 @@
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BG3" t="n">
         <v>12</v>
@@ -1276,7 +1276,7 @@
         <v>3.35</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -1365,64 +1365,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="G4" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S4" t="n">
         <v>2.18</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="X4" t="n">
         <v>32</v>
       </c>
       <c r="Y4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z4" t="n">
         <v>55</v>
@@ -1440,7 +1440,7 @@
         <v>25</v>
       </c>
       <c r="AE4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
         <v>970</v>
@@ -1452,16 +1452,16 @@
         <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
         <v>22</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AL4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM4" t="n">
         <v>85</v>
@@ -1473,59 +1473,59 @@
         <v>55</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AQ4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV4" t="n">
         <v>3.65</v>
       </c>
-      <c r="AR4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="AW4" t="n">
         <v>4</v>
       </c>
-      <c r="AT4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV4" t="n">
+      <c r="AX4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>3.55</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="BA4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BG4" t="n">
         <v>3.95</v>
       </c>
-      <c r="AX4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BH4" t="n">
         <v>1000</v>
       </c>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -1622,19 +1622,19 @@
         <v>1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="H5" t="n">
-        <v>6.4</v>
+        <v>2.68</v>
       </c>
       <c r="I5" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="K5" t="n">
-        <v>5.8</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,88 +1643,88 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="R5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="T5" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="X5" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
         <v>1.01</v>
@@ -1787,7 +1787,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
         <v>1.01</v>
@@ -1799,25 +1799,25 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
         <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
         <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
         <v>1.01</v>
@@ -1835,14 +1835,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
         <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G6" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="R6" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="S6" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="T6" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="U6" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X6" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y6" t="n">
         <v>28</v>
       </c>
-      <c r="Y6" t="n">
-        <v>27</v>
-      </c>
       <c r="Z6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA6" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AB6" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AC6" t="n">
         <v>12.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF6" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
         <v>19.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK6" t="n">
         <v>19</v>
       </c>
       <c r="AL6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM6" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN6" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO6" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BP6" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BR6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT6" t="n">
         <v>9</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX6" t="n">
         <v>38</v>
       </c>
-      <c r="BW6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>40</v>
-      </c>
       <c r="BY6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -2133,49 +2133,49 @@
         <v>2.7</v>
       </c>
       <c r="H7" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="T7" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
         <v>1.59</v>
@@ -2190,7 +2190,7 @@
         <v>29</v>
       </c>
       <c r="AA7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="n">
         <v>970</v>
@@ -2202,7 +2202,7 @@
         <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF7" t="n">
         <v>970</v>
@@ -2214,25 +2214,25 @@
         <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL7" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO7" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AP7" t="n">
         <v>1.01</v>
@@ -2244,7 +2244,7 @@
         <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
         <v>1.01</v>
@@ -2289,40 +2289,40 @@
         <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.42</v>
+        <v>1.05</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
@@ -2334,23 +2334,23 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.37</v>
+        <v>1.05</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -2381,85 +2381,85 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="G8" t="n">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="I8" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K8" t="n">
         <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="T8" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="U8" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="X8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
         <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA8" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AB8" t="n">
         <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
         <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
         <v>970</v>
@@ -2468,25 +2468,25 @@
         <v>970</v>
       </c>
       <c r="AI8" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ8" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AK8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AL8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM8" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN8" t="n">
         <v>970</v>
       </c>
       <c r="AO8" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AP8" t="n">
         <v>1.01</v>
@@ -2504,7 +2504,7 @@
         <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -2635,67 +2635,67 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="G9" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="H9" t="n">
         <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="K9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="O9" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="R9" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="S9" t="n">
         <v>2.04</v>
       </c>
       <c r="T9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U9" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="V9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W9" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="X9" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="Y9" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Z9" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
@@ -2704,13 +2704,13 @@
         <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AE9" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF9" t="n">
         <v>970</v>
@@ -2719,7 +2719,7 @@
         <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI9" t="n">
         <v>90</v>
@@ -2728,137 +2728,137 @@
         <v>970</v>
       </c>
       <c r="AK9" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AL9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM9" t="n">
         <v>100</v>
       </c>
       <c r="AN9" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="AV9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB9" t="n">
         <v>4.4</v>
       </c>
-      <c r="AW9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BC9" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BD9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
         <v>4.4</v>
       </c>
-      <c r="BE9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>2.18</v>
-      </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -2913,22 +2913,22 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
         <v>1.15</v>
       </c>
       <c r="P10" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R10" t="n">
         <v>1.78</v>
       </c>
       <c r="S10" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="T10" t="n">
         <v>1.67</v>
@@ -2955,10 +2955,10 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
         <v>40</v>
@@ -2967,10 +2967,10 @@
         <v>120</v>
       </c>
       <c r="AF10" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
         <v>23</v>
@@ -2979,10 +2979,10 @@
         <v>95</v>
       </c>
       <c r="AJ10" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AL10" t="n">
         <v>30</v>
@@ -3054,7 +3054,7 @@
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
@@ -3072,7 +3072,7 @@
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -3146,13 +3146,13 @@
         <v>4.5</v>
       </c>
       <c r="G11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H11" t="n">
         <v>1.92</v>
       </c>
       <c r="I11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J11" t="n">
         <v>3.1</v>
@@ -3173,7 +3173,7 @@
         <v>1.47</v>
       </c>
       <c r="P11" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q11" t="n">
         <v>2.38</v>
@@ -3203,19 +3203,19 @@
         <v>8</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AA11" t="n">
         <v>29</v>
       </c>
       <c r="AB11" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
         <v>30</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
         <v>950</v>
@@ -3421,13 +3421,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O12" t="n">
         <v>1.17</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q12" t="n">
         <v>1.17</v>
@@ -3505,52 +3505,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K13" t="n">
         <v>950</v>
@@ -3675,22 +3675,22 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="O13" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="R13" t="n">
         <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3759,52 +3759,52 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -3905,52 +3905,52 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="G14" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H14" t="n">
-        <v>2.26</v>
+        <v>4.4</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>2.26</v>
+        <v>3.65</v>
       </c>
       <c r="K14" t="n">
         <v>4.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
         <v>1.39</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
         <v>2.12</v>
       </c>
       <c r="R14" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
         <v>3.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -3959,176 +3959,176 @@
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP14" t="n">
-        <v>9.6</v>
+        <v>3.35</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="AS14" t="n">
-        <v>90</v>
+        <v>4.2</v>
       </c>
       <c r="AT14" t="n">
         <v>5.9</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.2</v>
+        <v>3.05</v>
       </c>
       <c r="AV14" t="n">
-        <v>18</v>
+        <v>3.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>55</v>
+        <v>4.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.4</v>
+        <v>3.15</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18.5</v>
+        <v>3.8</v>
       </c>
       <c r="BA14" t="n">
-        <v>70</v>
+        <v>4.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>13.5</v>
+        <v>3.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>17</v>
+        <v>3.7</v>
       </c>
       <c r="BD14" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>100</v>
+        <v>4.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>22</v>
+        <v>1.45</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BT14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>22</v>
+        <v>1.46</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>16</v>
+        <v>8.4</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -4162,109 +4162,109 @@
         <v>1.76</v>
       </c>
       <c r="G15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H15" t="n">
         <v>4.3</v>
       </c>
       <c r="I15" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>2.12</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
         <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W15" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP15" t="n">
         <v>1.01</v>
@@ -4279,10 +4279,10 @@
         <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV15" t="n">
         <v>1.01</v>
@@ -4291,10 +4291,10 @@
         <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ15" t="n">
         <v>1.01</v>
@@ -4315,16 +4315,16 @@
         <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG15" t="n">
         <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
@@ -4339,10 +4339,10 @@
         <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -4416,109 +4416,109 @@
         <v>2.46</v>
       </c>
       <c r="G16" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="H16" t="n">
         <v>2.5</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="J16" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>2.92</v>
+        <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="P16" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="S16" t="n">
         <v>2.04</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="V16" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W16" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H17" t="n">
         <v>3.3</v>
@@ -4679,208 +4679,208 @@
         <v>4.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -4939,202 +4939,202 @@
         <v>3.7</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P18" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>2.4</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="H19" t="n">
         <v>3</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
         <v>2.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -5686,19 +5686,19 @@
         <v>1.6</v>
       </c>
       <c r="G21" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="I21" t="n">
         <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -5937,16 +5937,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G22" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="H22" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J22" t="n">
         <v>4.2</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB22"/>
+  <dimension ref="A1:CB23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,7 +926,7 @@
         <v>12</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>16</v>
@@ -977,10 +977,10 @@
         <v>4.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.8</v>
+        <v>3.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
         <v>1.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="W3" t="n">
         <v>1.26</v>
@@ -1180,13 +1180,13 @@
         <v>17</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
         <v>12.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AF3" t="n">
         <v>40</v>
@@ -1216,10 +1216,10 @@
         <v>75</v>
       </c>
       <c r="AO3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.4</v>
@@ -1243,7 +1243,7 @@
         <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -1252,22 +1252,22 @@
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BC3" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BF3" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BG3" t="n">
         <v>12</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G4" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I4" t="n">
         <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1389,43 +1389,43 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T4" t="n">
         <v>1.6</v>
       </c>
-      <c r="S4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.59</v>
-      </c>
       <c r="U4" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
         <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X4" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y4" t="n">
         <v>32</v>
       </c>
-      <c r="Y4" t="n">
-        <v>30</v>
-      </c>
       <c r="Z4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
@@ -1437,10 +1437,10 @@
         <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF4" t="n">
         <v>970</v>
@@ -1449,13 +1449,13 @@
         <v>970</v>
       </c>
       <c r="AH4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>21</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>22</v>
       </c>
       <c r="AK4" t="n">
         <v>970</v>
@@ -1470,16 +1470,16 @@
         <v>970</v>
       </c>
       <c r="AO4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AQ4" t="n">
         <v>3.75</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS4" t="n">
         <v>4.1</v>
@@ -1503,7 +1503,7 @@
         <v>3.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BA4" t="n">
         <v>4</v>
@@ -1518,14 +1518,14 @@
         <v>3.75</v>
       </c>
       <c r="BE4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BG4" t="n">
         <v>4</v>
       </c>
-      <c r="BF4" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BH4" t="n">
         <v>1000</v>
       </c>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="G6" t="n">
         <v>1.85</v>
@@ -1882,7 +1882,7 @@
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>3.85</v>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
         <v>1.18</v>
@@ -1906,13 +1906,13 @@
         <v>2.36</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="R6" t="n">
         <v>1.6</v>
       </c>
       <c r="S6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T6" t="n">
         <v>1.58</v>
@@ -1924,7 +1924,7 @@
         <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="X6" t="n">
         <v>32</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -2235,58 +2235,58 @@
         <v>36</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BH7" t="n">
         <v>11.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.36</v>
       </c>
       <c r="G8" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="H8" t="n">
         <v>2.56</v>
@@ -2393,58 +2393,58 @@
         <v>3.25</v>
       </c>
       <c r="J8" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="K8" t="n">
         <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U8" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V8" t="n">
         <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y8" t="n">
         <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB8" t="n">
         <v>970</v>
@@ -2474,73 +2474,73 @@
         <v>44</v>
       </c>
       <c r="AK8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
         <v>40</v>
       </c>
       <c r="AM8" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN8" t="n">
         <v>970</v>
       </c>
       <c r="AO8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>1.46</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="I9" t="n">
         <v>11</v>
@@ -2659,10 +2659,10 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="O9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P9" t="n">
         <v>2.92</v>
@@ -2719,7 +2719,7 @@
         <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
         <v>90</v>
@@ -2734,7 +2734,7 @@
         <v>32</v>
       </c>
       <c r="AM9" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN9" t="n">
         <v>4.3</v>
@@ -2743,58 +2743,58 @@
         <v>95</v>
       </c>
       <c r="AP9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD9" t="n">
         <v>5.4</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BE9" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH9" t="n">
         <v>5.7</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -3054,65 +3054,65 @@
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G11" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="H11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J11" t="n">
         <v>3.1</v>
@@ -3170,10 +3170,10 @@
         <v>2.72</v>
       </c>
       <c r="O11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P11" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q11" t="n">
         <v>2.38</v>
@@ -3194,7 +3194,7 @@
         <v>1.89</v>
       </c>
       <c r="W11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X11" t="n">
         <v>11.5</v>
@@ -3218,10 +3218,10 @@
         <v>970</v>
       </c>
       <c r="AE11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG11" t="n">
         <v>24</v>
@@ -3236,7 +3236,7 @@
         <v>160</v>
       </c>
       <c r="AK11" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AL11" t="n">
         <v>120</v>
@@ -3254,7 +3254,7 @@
         <v>7.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AR11" t="n">
         <v>8.4</v>
@@ -3263,7 +3263,7 @@
         <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU11" t="n">
         <v>6</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K12" t="n">
         <v>950</v>
@@ -3445,7 +3445,7 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -3684,13 +3684,13 @@
         <v>1.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="R13" t="n">
         <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G14" t="n">
         <v>1.78</v>
@@ -3914,10 +3914,10 @@
         <v>4.4</v>
       </c>
       <c r="I14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
         <v>4.4</v>
@@ -3938,19 +3938,19 @@
         <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R14" t="n">
         <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
         <v>1.87</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -3959,19 +3959,19 @@
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z14" t="n">
         <v>65</v>
       </c>
       <c r="AA14" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC14" t="n">
         <v>10.5</v>
@@ -4013,58 +4013,58 @@
         <v>200</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AR14" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AV14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BC14" t="n">
         <v>3.8</v>
       </c>
-      <c r="AW14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BD14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH14" t="n">
         <v>3.2</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -4324,65 +4324,65 @@
         <v>4</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BN15" t="n">
         <v>4.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         <v>1.14</v>
       </c>
       <c r="P16" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="R16" t="n">
         <v>1.78</v>
       </c>
       <c r="S16" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="T16" t="n">
         <v>1.44</v>
@@ -4509,7 +4509,7 @@
         <v>28</v>
       </c>
       <c r="AL16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM16" t="n">
         <v>55</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H17" t="n">
         <v>3.3</v>
@@ -4679,10 +4679,10 @@
         <v>4.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4691,22 +4691,22 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.26</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -4718,7 +4718,7 @@
         <v>1.32</v>
       </c>
       <c r="W17" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4775,52 +4775,52 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
         <v>1.01</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
         <v>2.7</v>
       </c>
       <c r="I18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J18" t="n">
         <v>3.25</v>
@@ -4945,16 +4945,16 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>1.34</v>
       </c>
       <c r="P18" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R18" t="n">
         <v>1.24</v>
@@ -4963,13 +4963,13 @@
         <v>3.35</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W18" t="n">
         <v>1.5</v>
@@ -4990,7 +4990,7 @@
         <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18" t="n">
         <v>1000</v>
@@ -4999,13 +4999,13 @@
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG18" t="n">
         <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
@@ -5014,7 +5014,7 @@
         <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -5029,52 +5029,52 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
         <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
         <v>1.01</v>
@@ -5092,49 +5092,49 @@
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BN18" t="n">
         <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G19" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="H19" t="n">
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="J19" t="n">
         <v>3.15</v>
@@ -5193,16 +5193,16 @@
         <v>3.65</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P19" t="n">
         <v>1.78</v>
@@ -5211,201 +5211,201 @@
         <v>2.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,36 +5415,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="G20" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="H20" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="I20" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="J20" t="n">
         <v>3.95</v>
       </c>
       <c r="K20" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,55 +5669,55 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>Nacional (Uru)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="G21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1.71</v>
       </c>
-      <c r="H21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I21" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4</v>
-      </c>
-      <c r="K21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.74</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -5928,28 +5928,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FC Supra du Quebec</t>
+          <t>Cavalry</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="G22" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="H22" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="I22" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
         <v>5.2</v>
@@ -5967,200 +5967,454 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:10:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>FC Supra du Quebec</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>2.26</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>1.61</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB22" t="inlineStr">
-        <is>
-          <t>2026-06-04 14:01:32</t>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -860,7 +860,7 @@
         <v>2.4</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H2" t="n">
         <v>2.94</v>
@@ -926,7 +926,7 @@
         <v>12</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
         <v>16</v>
@@ -968,7 +968,7 @@
         <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>3.85</v>
       </c>
       <c r="AR2" t="n">
         <v>16.5</v>
@@ -980,7 +980,7 @@
         <v>3.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>3.25</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
@@ -1153,10 +1153,10 @@
         <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U3" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V3" t="n">
         <v>1.92</v>
@@ -1276,7 +1276,7 @@
         <v>3.35</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>7.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.23</v>
@@ -1389,7 +1389,7 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
         <v>1.17</v>
@@ -1404,13 +1404,13 @@
         <v>1.61</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="T4" t="n">
         <v>1.6</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
         <v>1.18</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -1876,16 +1876,16 @@
         <v>1.67</v>
       </c>
       <c r="G6" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
@@ -1894,10 +1894,10 @@
         <v>1.24</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="O6" t="n">
         <v>1.18</v>
@@ -1906,13 +1906,13 @@
         <v>2.36</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="R6" t="n">
         <v>1.6</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T6" t="n">
         <v>1.58</v>
@@ -1969,70 +1969,70 @@
         <v>19</v>
       </c>
       <c r="AL6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM6" t="n">
         <v>75</v>
       </c>
       <c r="AN6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AO6" t="n">
         <v>46</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AR6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW6" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AX6" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AZ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB6" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.2</v>
       </c>
       <c r="BC6" t="n">
         <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF6" t="n">
         <v>3.15</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH6" t="n">
         <v>4.7</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>2.9</v>
       </c>
       <c r="H8" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I8" t="n">
         <v>3.25</v>
@@ -2396,37 +2396,37 @@
         <v>2.88</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="U8" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
         <v>1.44</v>
@@ -2435,7 +2435,7 @@
         <v>1.53</v>
       </c>
       <c r="X8" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
         <v>970</v>
@@ -2489,59 +2489,59 @@
         <v>24</v>
       </c>
       <c r="AP8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AR8" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AW8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX8" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="AY8" t="n">
         <v>4.1</v>
       </c>
-      <c r="AY8" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BA8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG8" t="n">
         <v>4.6</v>
       </c>
-      <c r="BB8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH8" t="n">
         <v>1000</v>
       </c>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>1.46</v>
       </c>
       <c r="H9" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
         <v>11</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
         <v>3.55</v>
       </c>
       <c r="L11" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="M11" t="n">
         <v>1.11</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -3421,13 +3421,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.17</v>
       </c>
       <c r="P12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Q12" t="n">
         <v>1.17</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G14" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I14" t="n">
         <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
         <v>1.37</v>
@@ -3989,7 +3989,7 @@
         <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI14" t="n">
         <v>130</v>
@@ -4028,7 +4028,7 @@
         <v>5.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AV14" t="n">
         <v>3.9</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -4162,55 +4162,55 @@
         <v>1.76</v>
       </c>
       <c r="G15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H15" t="n">
         <v>4.3</v>
       </c>
       <c r="I15" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
         <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
         <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
         <v>1.68</v>
       </c>
       <c r="U15" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W15" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X15" t="n">
         <v>22</v>
@@ -4264,7 +4264,7 @@
         <v>970</v>
       </c>
       <c r="AO15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP15" t="n">
         <v>1.01</v>
@@ -4321,68 +4321,68 @@
         <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>2.02</v>
+        <v>7</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.37</v>
+        <v>3.7</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
         <v>1.78</v>
       </c>
       <c r="S16" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="T16" t="n">
         <v>1.44</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
         <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
         <v>1.73</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -4924,13 +4924,13 @@
         <v>2.6</v>
       </c>
       <c r="G18" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H18" t="n">
         <v>2.7</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>3.25</v>
@@ -4942,40 +4942,40 @@
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O18" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P18" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S18" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="V18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y18" t="n">
         <v>1000</v>
@@ -4990,13 +4990,13 @@
         <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD18" t="n">
         <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF18" t="n">
         <v>22</v>
@@ -5014,7 +5014,7 @@
         <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -5029,7 +5029,7 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.03</v>
@@ -5044,7 +5044,7 @@
         <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV18" t="n">
         <v>1.03</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="H19" t="n">
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="J19" t="n">
         <v>3.15</v>
@@ -5196,16 +5196,16 @@
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="O19" t="n">
         <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="Q19" t="n">
         <v>2.1</v>
@@ -5217,58 +5217,58 @@
         <v>3.15</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V19" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL19" t="n">
         <v>1000</v>
@@ -5283,52 +5283,52 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
         <v>1.01</v>
@@ -5346,59 +5346,59 @@
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BN19" t="n">
         <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G20" t="n">
         <v>1.9</v>
@@ -5438,221 +5438,221 @@
         <v>4.4</v>
       </c>
       <c r="I20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
         <v>4.2</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P20" t="n">
         <v>2.32</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5716,7 @@
         <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H2" t="n">
         <v>2.94</v>
@@ -875,7 +875,7 @@
         <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -902,7 +902,7 @@
         <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
         <v>1.41</v>
@@ -938,7 +938,7 @@
         <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
@@ -953,7 +953,7 @@
         <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM2" t="n">
         <v>120</v>
@@ -968,55 +968,55 @@
         <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.85</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2" t="n">
         <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BD2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE2" t="n">
         <v>4.8</v>
       </c>
-      <c r="BE2" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BF2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -1153,10 +1153,10 @@
         <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V3" t="n">
         <v>1.92</v>
@@ -1177,13 +1177,13 @@
         <v>29</v>
       </c>
       <c r="AB3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC3" t="n">
         <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
         <v>24</v>
@@ -1192,7 +1192,7 @@
         <v>40</v>
       </c>
       <c r="AG3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH3" t="n">
         <v>21</v>
@@ -1243,7 +1243,7 @@
         <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -1252,22 +1252,22 @@
         <v>14</v>
       </c>
       <c r="BA3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB3" t="n">
         <v>5.7</v>
       </c>
-      <c r="BB3" t="n">
-        <v>6</v>
-      </c>
       <c r="BC3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE3" t="n">
         <v>5.8</v>
       </c>
-      <c r="BD3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>6</v>
-      </c>
       <c r="BF3" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BG3" t="n">
         <v>12</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>1.74</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
         <v>6.4</v>
@@ -1380,7 +1380,7 @@
         <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
         <v>1.23</v>
@@ -1389,13 +1389,13 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="O4" t="n">
         <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
         <v>1.51</v>
@@ -1404,7 +1404,7 @@
         <v>1.61</v>
       </c>
       <c r="S4" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
         <v>1.6</v>
@@ -1416,7 +1416,7 @@
         <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="X4" t="n">
         <v>34</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="G5" t="n">
         <v>1.62</v>
@@ -1646,7 +1646,7 @@
         <v>2.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P5" t="n">
         <v>2.36</v>
@@ -1655,10 +1655,10 @@
         <v>1.47</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="S5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,7 +1667,7 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
         <v>2.6</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>1.67</v>
       </c>
       <c r="G6" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
@@ -1885,34 +1885,34 @@
         <v>5.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>4.9</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
         <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="Q6" t="n">
         <v>1.66</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T6" t="n">
         <v>1.58</v>
@@ -1921,7 +1921,7 @@
         <v>2.36</v>
       </c>
       <c r="V6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
         <v>2.16</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="H7" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="I7" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="J7" t="n">
         <v>3.25</v>
@@ -2154,7 +2154,7 @@
         <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
         <v>1.96</v>
@@ -2166,7 +2166,7 @@
         <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T7" t="n">
         <v>1.6</v>
@@ -2175,10 +2175,10 @@
         <v>2.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -2187,10 +2187,10 @@
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="n">
         <v>970</v>
@@ -2202,7 +2202,7 @@
         <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF7" t="n">
         <v>970</v>
@@ -2214,7 +2214,7 @@
         <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ7" t="n">
         <v>40</v>
@@ -2232,61 +2232,61 @@
         <v>21</v>
       </c>
       <c r="AO7" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="AR7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>3.7</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="BA7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC7" t="n">
         <v>4</v>
       </c>
-      <c r="AT7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BD7" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BE7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG7" t="n">
         <v>4</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3.8</v>
       </c>
       <c r="BH7" t="n">
         <v>11.5</v>
@@ -2298,7 +2298,7 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2316,7 +2316,7 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
@@ -2328,13 +2328,13 @@
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
@@ -2346,11 +2346,11 @@
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -2381,46 +2381,46 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="I8" t="n">
         <v>3.25</v>
       </c>
       <c r="J8" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K8" t="n">
         <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="T8" t="n">
         <v>1.62</v>
@@ -2432,7 +2432,7 @@
         <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
@@ -2486,31 +2486,31 @@
         <v>970</v>
       </c>
       <c r="AO8" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>4.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT8" t="n">
         <v>4.1</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
         <v>4.5</v>
@@ -2519,29 +2519,29 @@
         <v>4.1</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD8" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC8" t="n">
+      <c r="BE8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG8" t="n">
         <v>4.9</v>
       </c>
-      <c r="BD8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BH8" t="n">
         <v>1000</v>
       </c>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>1.34</v>
       </c>
       <c r="G9" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="H9" t="n">
         <v>6</v>
@@ -2650,7 +2650,7 @@
         <v>4.7</v>
       </c>
       <c r="K9" t="n">
-        <v>8.6</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>1.19</v>
@@ -2659,19 +2659,19 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>1.02</v>
+        <v>2.68</v>
       </c>
       <c r="O9" t="n">
         <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="R9" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="S9" t="n">
         <v>2.04</v>
@@ -2680,7 +2680,7 @@
         <v>1.64</v>
       </c>
       <c r="U9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V9" t="n">
         <v>1.11</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G10" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="H10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="K10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.21</v>
@@ -2913,22 +2913,22 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="O10" t="n">
         <v>1.15</v>
       </c>
       <c r="P10" t="n">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="R10" t="n">
         <v>1.78</v>
       </c>
       <c r="S10" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="T10" t="n">
         <v>1.67</v>
@@ -2940,19 +2940,19 @@
         <v>1.12</v>
       </c>
       <c r="W10" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="X10" t="n">
         <v>38</v>
       </c>
       <c r="Y10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Z10" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB10" t="n">
         <v>970</v>
@@ -2961,10 +2961,10 @@
         <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AE10" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF10" t="n">
         <v>970</v>
@@ -2976,7 +2976,7 @@
         <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ10" t="n">
         <v>970</v>
@@ -2994,7 +2994,7 @@
         <v>5.1</v>
       </c>
       <c r="AO10" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP10" t="n">
         <v>1.01</v>
@@ -3036,16 +3036,16 @@
         <v>10</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
         <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BG10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>5.3</v>
       </c>
       <c r="H11" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="I11" t="n">
         <v>2.12</v>
@@ -3158,7 +3158,7 @@
         <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>1.51</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
         <v>1.32</v>
       </c>
       <c r="O13" t="n">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="P13" t="n">
         <v>1.32</v>
@@ -3690,7 +3690,7 @@
         <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>1.8</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="I14" t="n">
         <v>8</v>
@@ -4070,7 +4070,7 @@
         <v>3.2</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
@@ -4082,25 +4082,25 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="BN14" t="n">
         <v>4.1</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
@@ -4118,17 +4118,17 @@
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>1.76</v>
       </c>
       <c r="G15" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H15" t="n">
         <v>4.3</v>
@@ -4171,7 +4171,7 @@
         <v>5.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K15" t="n">
         <v>5</v>
@@ -4192,25 +4192,25 @@
         <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R15" t="n">
         <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T15" t="n">
         <v>1.68</v>
       </c>
       <c r="U15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V15" t="n">
         <v>1.24</v>
       </c>
       <c r="W15" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X15" t="n">
         <v>22</v>
@@ -4255,7 +4255,7 @@
         <v>21</v>
       </c>
       <c r="AL15" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM15" t="n">
         <v>95</v>
@@ -4279,13 +4279,13 @@
         <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW15" t="n">
         <v>1.01</v>
@@ -4297,13 +4297,13 @@
         <v>8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA15" t="n">
         <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>2.46</v>
       </c>
       <c r="G16" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H16" t="n">
         <v>2.5</v>
@@ -4425,40 +4425,40 @@
         <v>2.74</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="K16" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
         <v>1.2</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O16" t="n">
         <v>1.14</v>
       </c>
       <c r="P16" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="R16" t="n">
         <v>1.78</v>
       </c>
       <c r="S16" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="T16" t="n">
         <v>1.44</v>
       </c>
       <c r="U16" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V16" t="n">
         <v>1.57</v>
@@ -4500,7 +4500,7 @@
         <v>970</v>
       </c>
       <c r="AI16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ16" t="n">
         <v>46</v>
@@ -4524,7 +4524,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
         <v>1.01</v>
@@ -4533,13 +4533,13 @@
         <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW16" t="n">
         <v>1.01</v>
@@ -4548,7 +4548,7 @@
         <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
         <v>1.01</v>
@@ -4569,7 +4569,7 @@
         <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -4960,10 +4960,10 @@
         <v>1.27</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U18" t="n">
         <v>1.9</v>
@@ -4975,7 +4975,7 @@
         <v>1.51</v>
       </c>
       <c r="X18" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y18" t="n">
         <v>1000</v>
@@ -5029,7 +5029,7 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.03</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>2.4</v>
       </c>
       <c r="G19" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="H19" t="n">
         <v>3</v>
@@ -5202,7 +5202,7 @@
         <v>2.86</v>
       </c>
       <c r="O19" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P19" t="n">
         <v>1.73</v>
@@ -5217,16 +5217,16 @@
         <v>3.15</v>
       </c>
       <c r="T19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U19" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
         <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="X19" t="n">
         <v>17</v>
@@ -5319,7 +5319,7 @@
         <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
         <v>19</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.87</v>
       </c>
       <c r="G20" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H20" t="n">
         <v>4.4</v>
@@ -5450,13 +5450,13 @@
         <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P20" t="n">
         <v>2.32</v>
@@ -5468,70 +5468,70 @@
         <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="T20" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="U20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V20" t="n">
         <v>1.27</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y20" t="n">
         <v>21</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>23</v>
       </c>
       <c r="Z20" t="n">
         <v>38</v>
       </c>
       <c r="AA20" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE20" t="n">
         <v>50</v>
       </c>
       <c r="AF20" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI20" t="n">
         <v>55</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM20" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO20" t="n">
         <v>46</v>
@@ -5540,13 +5540,13 @@
         <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AS20" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AT20" t="n">
         <v>9.4</v>
@@ -5555,13 +5555,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW20" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AY20" t="n">
         <v>9</v>
@@ -5570,22 +5570,22 @@
         <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.7</v>
+        <v>46</v>
       </c>
       <c r="BB20" t="n">
         <v>18</v>
       </c>
       <c r="BC20" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE20" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BG20" t="n">
         <v>32</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -5683,230 +5683,230 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="G21" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="H21" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="I21" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P21" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BI21" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BP21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BR21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BT21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BV21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BX21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -5940,227 +5940,227 @@
         <v>1.6</v>
       </c>
       <c r="G22" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="H22" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="K22" t="n">
-        <v>5.2</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
         <v>1.74</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BI22" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -6191,230 +6191,230 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="G23" t="n">
         <v>1.71</v>
       </c>
       <c r="H23" t="n">
-        <v>5.6</v>
+        <v>2.46</v>
       </c>
       <c r="I23" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="J23" t="n">
         <v>3.95</v>
       </c>
       <c r="K23" t="n">
-        <v>5.2</v>
+        <v>950</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CB26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,7 +926,7 @@
         <v>12</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>16</v>
@@ -974,19 +974,19 @@
         <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
         <v>7.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -998,25 +998,25 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF2" t="n">
         <v>4.4</v>
       </c>
-      <c r="BC2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>4.1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H3" t="n">
         <v>1.95</v>
       </c>
       <c r="I3" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J3" t="n">
         <v>3.6</v>
@@ -1153,16 +1153,16 @@
         <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U3" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="W3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X3" t="n">
         <v>15.5</v>
@@ -1276,7 +1276,7 @@
         <v>3.35</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="G4" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1395,34 +1395,34 @@
         <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q4" t="n">
         <v>1.51</v>
       </c>
       <c r="R4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T4" t="n">
         <v>1.61</v>
       </c>
-      <c r="S4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.6</v>
-      </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W4" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X4" t="n">
         <v>34</v>
       </c>
       <c r="Y4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z4" t="n">
         <v>60</v>
@@ -1437,10 +1437,10 @@
         <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF4" t="n">
         <v>970</v>
@@ -1452,10 +1452,10 @@
         <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
         <v>970</v>
@@ -1464,43 +1464,43 @@
         <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN4" t="n">
         <v>970</v>
       </c>
       <c r="AO4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AR4" t="n">
         <v>4</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT4" t="n">
         <v>3.35</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX4" t="n">
         <v>3.35</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AZ4" t="n">
         <v>3.6</v>
@@ -1515,13 +1515,13 @@
         <v>3.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BE4" t="n">
         <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BG4" t="n">
         <v>4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G5" t="n">
         <v>1.62</v>
@@ -1631,7 +1631,7 @@
         <v>970</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="O5" t="n">
         <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="R5" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,7 +1667,7 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
         <v>2.6</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="n">
         <v>2.66</v>
       </c>
       <c r="I8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="O8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="P8" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="T8" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
@@ -2450,7 +2450,7 @@
         <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
         <v>970</v>
@@ -2471,77 +2471,77 @@
         <v>42</v>
       </c>
       <c r="AJ8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM8" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN8" t="n">
         <v>970</v>
       </c>
       <c r="AO8" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ8" t="n">
         <v>4.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AT8" t="n">
         <v>4.1</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AY8" t="n">
         <v>4.1</v>
       </c>
       <c r="AZ8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4.4</v>
       </c>
-      <c r="BA8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF8" t="n">
+      <c r="BG8" t="n">
         <v>4.6</v>
       </c>
-      <c r="BG8" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BH8" t="n">
         <v>1000</v>
       </c>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="G9" t="n">
         <v>1.48</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="J9" t="n">
         <v>4.7</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>7.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.19</v>
@@ -2677,7 +2677,7 @@
         <v>2.04</v>
       </c>
       <c r="T9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U9" t="n">
         <v>2.18</v>
@@ -2689,7 +2689,7 @@
         <v>3.05</v>
       </c>
       <c r="X9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Y9" t="n">
         <v>50</v>
@@ -2758,7 +2758,7 @@
         <v>4.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AV9" t="n">
         <v>5.6</v>
@@ -2767,37 +2767,37 @@
         <v>6.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY9" t="n">
         <v>4.3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB9" t="n">
         <v>4.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF9" t="n">
         <v>2.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
         <v>3.35</v>
@@ -2806,49 +2806,49 @@
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="BN9" t="n">
         <v>4.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>2.52</v>
+        <v>1.67</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
         <v>1.15</v>
       </c>
       <c r="P10" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="Q10" t="n">
         <v>1.44</v>
@@ -2997,16 +2997,16 @@
         <v>85</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -3015,10 +3015,10 @@
         <v>10</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX10" t="n">
         <v>8.800000000000001</v>
@@ -3027,10 +3027,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB10" t="n">
         <v>10</v>
@@ -3039,16 +3039,16 @@
         <v>10.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF10" t="n">
         <v>3.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -3167,16 +3167,16 @@
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P11" t="n">
         <v>1.59</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R11" t="n">
         <v>1.21</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,61 +3896,61 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>FC Arbaer</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sindri</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
         <v>1.08</v>
       </c>
-      <c r="N14" t="n">
-        <v>3.2</v>
-      </c>
       <c r="O14" t="n">
-        <v>1.39</v>
+        <v>1.05</v>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>1.07</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.14</v>
+        <v>1.05</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>1.05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -3959,176 +3959,176 @@
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -4150,127 +4150,127 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.76</v>
+        <v>2.46</v>
       </c>
       <c r="G15" t="n">
-        <v>1.92</v>
+        <v>2.72</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="I15" t="n">
-        <v>5.2</v>
+        <v>2.74</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K15" t="n">
         <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>2.18</v>
+        <v>2.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="R15" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="T15" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="V15" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="W15" t="n">
-        <v>2.08</v>
+        <v>1.58</v>
       </c>
       <c r="X15" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="Y15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Z15" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AA15" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="AB15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC15" t="n">
         <v>970</v>
       </c>
-      <c r="AC15" t="n">
-        <v>11</v>
-      </c>
       <c r="AD15" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AE15" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AF15" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AG15" t="n">
         <v>970</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AI15" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AJ15" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AK15" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AL15" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM15" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AN15" t="n">
         <v>970</v>
       </c>
       <c r="AO15" t="n">
-        <v>60</v>
+        <v>970</v>
       </c>
       <c r="AP15" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
         <v>1.01</v>
@@ -4279,110 +4279,110 @@
         <v>1.01</v>
       </c>
       <c r="AT15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF15" t="n">
         <v>8.4</v>
       </c>
-      <c r="AU15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BG15" t="n">
         <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -4404,127 +4404,127 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.46</v>
+        <v>1.76</v>
       </c>
       <c r="G16" t="n">
-        <v>2.72</v>
+        <v>1.92</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="I16" t="n">
-        <v>2.74</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
         <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="M16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>2.84</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="R16" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="S16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W16" t="n">
         <v>2.08</v>
       </c>
-      <c r="T16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.58</v>
-      </c>
       <c r="X16" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="Y16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Z16" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AA16" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AB16" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AC16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF16" t="n">
         <v>970</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>29</v>
       </c>
       <c r="AG16" t="n">
         <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL16" t="n">
         <v>32</v>
       </c>
-      <c r="AJ16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>36</v>
-      </c>
       <c r="AM16" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AN16" t="n">
         <v>970</v>
       </c>
       <c r="AO16" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AP16" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
         <v>1.01</v>
@@ -4533,31 +4533,31 @@
         <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AW16" t="n">
         <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA16" t="n">
         <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC16" t="n">
         <v>1.01</v>
@@ -4569,81 +4569,81 @@
         <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG16" t="n">
         <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Deportes Copiapo</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="H17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AY17" t="n">
         <v>3.3</v>
       </c>
-      <c r="I17" t="n">
+      <c r="AZ17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD17" t="n">
         <v>4.1</v>
       </c>
-      <c r="J17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="BE17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BN17" t="n">
         <v>4.1</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1000</v>
-      </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,75 +4907,75 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cobreloa Calama</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="G18" t="n">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>2.96</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="P18" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="R18" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>1.11</v>
       </c>
       <c r="T18" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
         <v>1000</v>
@@ -4990,22 +4990,22 @@
         <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
         <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
         <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
@@ -5014,7 +5014,7 @@
         <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -5029,7 +5029,7 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.03</v>
@@ -5044,7 +5044,7 @@
         <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
         <v>1.03</v>
@@ -5083,75 +5083,75 @@
         <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
         <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,36 +5161,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Torque</t>
+          <t>Dalvik/Reynir</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Throttur Vogar</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="I19" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="K19" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5199,76 +5199,76 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="O19" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="P19" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1</v>
+        <v>1.15</v>
       </c>
       <c r="R19" t="n">
         <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>3.15</v>
+        <v>1.15</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
         <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
         <v>1000</v>
@@ -5283,46 +5283,46 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AS19" t="n">
         <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AW19" t="n">
         <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AY19" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BA19" t="n">
         <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
         <v>1.03</v>
@@ -5337,75 +5337,75 @@
         <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BN19" t="n">
         <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,180 +5415,180 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>Deportes Copiapo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="G20" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="H20" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="I20" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P20" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>2.72</v>
+        <v>2.28</v>
       </c>
       <c r="T20" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="W20" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="X20" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR20" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AS20" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU20" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AV20" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AW20" t="n">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA20" t="n">
-        <v>46</v>
+        <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BC20" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD20" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BE20" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF20" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
@@ -5645,21 +5645,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,251 +5669,251 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Cobreloa Calama</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.55</v>
+        <v>2.6</v>
       </c>
       <c r="G21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U21" t="n">
         <v>1.9</v>
       </c>
-      <c r="H21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="V21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X21" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
         <v>1.32</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BH21" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.86</v>
+        <v>2.46</v>
       </c>
       <c r="BJ21" t="n">
         <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BT21" t="n">
         <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,498 +5923,1260 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>Torque</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="G22" t="n">
-        <v>1.79</v>
+        <v>2.7</v>
       </c>
       <c r="H22" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>9.6</v>
       </c>
-      <c r="J22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K22" t="n">
-        <v>950</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>27</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH22" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BN22" t="n">
         <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BT22" t="n">
         <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BZ22" t="n">
         <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Spanish Segunda Division</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CD Castellon</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-06-04 22:43:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Juventud De Las Piedras</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-06-04 22:43:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Canadian Premier League</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Cavalry</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>HFX Wanderers</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X25" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-06-04 22:43:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>FC Supra du Quebec</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Pacific</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F26" t="n">
         <v>1.51</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G26" t="n">
         <v>1.71</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I26" t="n">
+        <v>11</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K26" t="n">
+        <v>950</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S26" t="n">
         <v>2.46</v>
       </c>
-      <c r="I23" t="n">
-        <v>12</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K23" t="n">
-        <v>950</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W23" t="n">
+      <c r="T26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W26" t="n">
         <v>2.4</v>
       </c>
-      <c r="X23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB23" t="inlineStr">
-        <is>
-          <t>2026-06-04 20:34:09</t>
+      <c r="X26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB26"/>
+  <dimension ref="A1:CB28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,7 +875,7 @@
         <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -893,7 +893,7 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
         <v>3.55</v>
@@ -905,7 +905,7 @@
         <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
         <v>1.58</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>4.7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="I3" t="n">
         <v>2.06</v>
@@ -1126,10 +1126,10 @@
         <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
@@ -1174,7 +1174,7 @@
         <v>13</v>
       </c>
       <c r="AA3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AB3" t="n">
         <v>17.5</v>
@@ -1207,7 +1207,7 @@
         <v>65</v>
       </c>
       <c r="AL3" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="n">
         <v>140</v>
@@ -1243,7 +1243,7 @@
         <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -1252,22 +1252,22 @@
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD3" t="n">
         <v>5.7</v>
       </c>
-      <c r="BC3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BE3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG3" t="n">
         <v>12</v>
@@ -1300,10 +1300,10 @@
         <v>40</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
         <v>9</v>
@@ -1318,7 +1318,7 @@
         <v>15.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX3" t="n">
         <v>32</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>1.49</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H4" t="n">
         <v>4.4</v>
@@ -1377,7 +1377,7 @@
         <v>7.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1401,22 +1401,22 @@
         <v>1.51</v>
       </c>
       <c r="R4" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S4" t="n">
         <v>2.08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V4" t="n">
         <v>1.16</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X4" t="n">
         <v>34</v>
@@ -1473,10 +1473,10 @@
         <v>65</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AR4" t="n">
         <v>4</v>
@@ -1494,13 +1494,13 @@
         <v>3.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AX4" t="n">
         <v>3.35</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AZ4" t="n">
         <v>3.6</v>
@@ -1521,7 +1521,7 @@
         <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BG4" t="n">
         <v>4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
         <v>2.6</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>1.67</v>
       </c>
       <c r="G6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
@@ -1885,7 +1885,7 @@
         <v>5.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
@@ -1897,19 +1897,19 @@
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="O6" t="n">
         <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
         <v>1.66</v>
       </c>
       <c r="R6" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S6" t="n">
         <v>2.2</v>
@@ -1918,19 +1918,19 @@
         <v>1.58</v>
       </c>
       <c r="U6" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V6" t="n">
         <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="X6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z6" t="n">
         <v>48</v>
@@ -1957,7 +1957,7 @@
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
         <v>55</v>
@@ -1972,7 +1972,7 @@
         <v>32</v>
       </c>
       <c r="AM6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN6" t="n">
         <v>8.4</v>
@@ -1987,13 +1987,13 @@
         <v>4.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS6" t="n">
         <v>4.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AU6" t="n">
         <v>3.6</v>
@@ -2002,7 +2002,7 @@
         <v>4.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX6" t="n">
         <v>3.8</v>
@@ -2023,10 +2023,10 @@
         <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF6" t="n">
         <v>3.15</v>
@@ -2041,10 +2041,10 @@
         <v>3.1</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,10 +2053,10 @@
         <v>8.4</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP6" t="n">
         <v>11.5</v>
@@ -2089,14 +2089,14 @@
         <v>7.4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="CA6" t="n">
         <v>5.7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>2.64</v>
       </c>
       <c r="G7" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="H7" t="n">
         <v>2.74</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J7" t="n">
         <v>3.25</v>
@@ -2166,7 +2166,7 @@
         <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T7" t="n">
         <v>1.6</v>
@@ -2178,7 +2178,7 @@
         <v>1.48</v>
       </c>
       <c r="W7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -2304,7 +2304,7 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
@@ -2316,13 +2316,13 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
@@ -2334,23 +2334,23 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -2381,31 +2381,31 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="H8" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N8" t="n">
         <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.96</v>
       </c>
       <c r="O8" t="n">
         <v>1.03</v>
@@ -2414,7 +2414,7 @@
         <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R8" t="n">
         <v>1.37</v>
@@ -2429,10 +2429,10 @@
         <v>2.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>1.36</v>
       </c>
       <c r="G9" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H9" t="n">
         <v>4.7</v>
@@ -2659,16 +2659,16 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
         <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R9" t="n">
         <v>1.68</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
         <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V11" t="n">
         <v>1.89</v>
@@ -3224,7 +3224,7 @@
         <v>40</v>
       </c>
       <c r="AG11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH11" t="n">
         <v>28</v>
@@ -3233,13 +3233,13 @@
         <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
         <v>95</v>
       </c>
       <c r="AL11" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -3917,10 +3917,10 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3929,22 +3929,22 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P14" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="R14" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -4013,52 +4013,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,172 +4150,172 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="G15" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="I15" t="n">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>1.02</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>950</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>6.4</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="P15" t="n">
-        <v>2.84</v>
+        <v>1.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.43</v>
+        <v>1.11</v>
       </c>
       <c r="R15" t="n">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="T15" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
         <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
         <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -4404,127 +4404,127 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.76</v>
+        <v>2.46</v>
       </c>
       <c r="G16" t="n">
-        <v>1.92</v>
+        <v>2.7</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>2.74</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
         <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="P16" t="n">
-        <v>2.18</v>
+        <v>2.84</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="T16" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="U16" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="V16" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="W16" t="n">
-        <v>2.08</v>
+        <v>1.58</v>
       </c>
       <c r="X16" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="Y16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Z16" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AA16" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="AB16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC16" t="n">
         <v>970</v>
       </c>
-      <c r="AC16" t="n">
-        <v>11</v>
-      </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AF16" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AG16" t="n">
         <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AI16" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AL16" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM16" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AN16" t="n">
         <v>970</v>
       </c>
       <c r="AO16" t="n">
-        <v>60</v>
+        <v>970</v>
       </c>
       <c r="AP16" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
         <v>1.01</v>
@@ -4533,117 +4533,117 @@
         <v>1.01</v>
       </c>
       <c r="AT16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF16" t="n">
         <v>8.4</v>
       </c>
-      <c r="AU16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BG16" t="n">
         <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,246 +4658,246 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="H17" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY17" t="n">
         <v>8</v>
       </c>
-      <c r="J17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="AZ17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI17" t="n">
         <v>3.2</v>
       </c>
-      <c r="O17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>240</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AQ17" t="n">
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
         <v>3.7</v>
       </c>
-      <c r="AR17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,61 +4912,61 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Fjolnir</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>1.8</v>
       </c>
       <c r="H18" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>1.02</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>1.25</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="P18" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>1.11</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
@@ -4975,176 +4975,176 @@
         <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5199,7 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="O19" t="n">
         <v>1.15</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -5441,10 +5441,10 @@
         <v>4.1</v>
       </c>
       <c r="J20" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -5465,10 +5465,10 @@
         <v>1.73</v>
       </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.28</v>
+        <v>2.84</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -5722,10 +5722,10 @@
         <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
         <v>1.9</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -6099,68 +6099,68 @@
         <v>8</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI22" t="n">
         <v>2.6</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.35</v>
+        <v>2.64</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.35</v>
+        <v>3.2</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.35</v>
+        <v>3.55</v>
       </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.35</v>
+        <v>2.92</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.35</v>
+        <v>3.05</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="BV22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.35</v>
+        <v>2.98</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.35</v>
+        <v>3.05</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.35</v>
+        <v>3</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
         <v>2.72</v>
       </c>
       <c r="T23" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U23" t="n">
         <v>2.28</v>
@@ -6272,7 +6272,7 @@
         <v>13</v>
       </c>
       <c r="AG23" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH23" t="n">
         <v>17</v>
@@ -6284,7 +6284,7 @@
         <v>21</v>
       </c>
       <c r="AK23" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL23" t="n">
         <v>29</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
         <v>3.95</v>
@@ -6484,7 +6484,7 @@
         <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="T24" t="n">
         <v>1.83</v>
@@ -6559,52 +6559,52 @@
         <v>14.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT24" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV24" t="n">
         <v>16</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX24" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY24" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC24" t="n">
-        <v>13</v>
+        <v>3.55</v>
       </c>
       <c r="BD24" t="n">
-        <v>25</v>
+        <v>3.85</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF24" t="n">
         <v>7.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH24" t="n">
         <v>4.5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6747,7 @@
         <v>2.02</v>
       </c>
       <c r="V25" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W25" t="n">
         <v>2.4</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,515 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CSD Rangers</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Club Deportes Santa Cruz</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X27" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Deportes Recoleta</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X28" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB28"/>
+  <dimension ref="A1:CB30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G2" t="n">
         <v>2.74</v>
       </c>
       <c r="H2" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.25</v>
@@ -875,7 +875,7 @@
         <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -896,7 +896,7 @@
         <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
         <v>1.75</v>
@@ -905,7 +905,7 @@
         <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
         <v>1.58</v>
@@ -914,13 +914,13 @@
         <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB2" t="n">
         <v>12</v>
@@ -929,13 +929,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AG2" t="n">
         <v>14</v>
@@ -947,7 +947,7 @@
         <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK2" t="n">
         <v>34</v>
@@ -959,7 +959,7 @@
         <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO2" t="n">
         <v>42</v>
@@ -968,25 +968,25 @@
         <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU2" t="n">
         <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -998,25 +998,25 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB2" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB2" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BC2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF2" t="n">
         <v>4.5</v>
       </c>
-      <c r="BD2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BG2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -1111,25 +1111,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>4.7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="I3" t="n">
         <v>2.06</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
         <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
@@ -1141,7 +1141,7 @@
         <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q3" t="n">
         <v>2.02</v>
@@ -1198,7 +1198,7 @@
         <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ3" t="n">
         <v>120</v>
@@ -1225,7 +1225,7 @@
         <v>6.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
         <v>17.5</v>
@@ -1243,7 +1243,7 @@
         <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -1258,10 +1258,10 @@
         <v>5.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE3" t="n">
         <v>5.9</v>
@@ -1273,7 +1273,7 @@
         <v>12</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI3" t="n">
         <v>2.62</v>
@@ -1282,49 +1282,49 @@
         <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BQ3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
         <v>8.6</v>
       </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>9</v>
-      </c>
       <c r="BT3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BV3" t="n">
         <v>15.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BX3" t="n">
         <v>32</v>
       </c>
       <c r="BY3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="O4" t="n">
         <v>1.17</v>
@@ -1416,7 +1416,7 @@
         <v>1.16</v>
       </c>
       <c r="W4" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="X4" t="n">
         <v>34</v>
@@ -1431,10 +1431,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD4" t="n">
         <v>27</v>
@@ -1443,10 +1443,10 @@
         <v>75</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
         <v>22</v>
@@ -1458,7 +1458,7 @@
         <v>20</v>
       </c>
       <c r="AK4" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AL4" t="n">
         <v>32</v>
@@ -1467,7 +1467,7 @@
         <v>90</v>
       </c>
       <c r="AN4" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AO4" t="n">
         <v>65</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -1619,58 +1619,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H5" t="n">
-        <v>2.68</v>
+        <v>5.7</v>
       </c>
       <c r="I5" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="R5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1727,10 +1727,10 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
         <v>1.03</v>
@@ -1739,37 +1739,37 @@
         <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
         <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
         <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
         <v>1.03</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -1891,25 +1891,25 @@
         <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>2.38</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
         <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q6" t="n">
         <v>1.66</v>
       </c>
       <c r="R6" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="S6" t="n">
         <v>2.2</v>
@@ -1924,7 +1924,7 @@
         <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="X6" t="n">
         <v>30</v>
@@ -1957,7 +1957,7 @@
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI6" t="n">
         <v>55</v>
@@ -1966,7 +1966,7 @@
         <v>22</v>
       </c>
       <c r="AK6" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AL6" t="n">
         <v>32</v>
@@ -1981,58 +1981,58 @@
         <v>46</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV6" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS6" t="n">
+      <c r="AW6" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV6" t="n">
+      <c r="AX6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4</v>
-      </c>
       <c r="BA6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC6" t="n">
         <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH6" t="n">
         <v>4.7</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>2.64</v>
       </c>
       <c r="G7" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H7" t="n">
         <v>2.74</v>
@@ -2181,10 +2181,10 @@
         <v>1.54</v>
       </c>
       <c r="X7" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Z7" t="n">
         <v>27</v>
@@ -2193,25 +2193,25 @@
         <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AE7" t="n">
         <v>40</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH7" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AI7" t="n">
         <v>50</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -2384,88 +2384,88 @@
         <v>2.28</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="H8" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="K8" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="O8" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T8" t="n">
         <v>1.57</v>
       </c>
       <c r="U8" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Z8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA8" t="n">
         <v>50</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AC8" t="n">
         <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AE8" t="n">
         <v>34</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="n">
         <v>42</v>
@@ -2474,74 +2474,74 @@
         <v>42</v>
       </c>
       <c r="AK8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL8" t="n">
         <v>38</v>
       </c>
       <c r="AM8" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN8" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AO8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AT8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG8" t="n">
         <v>4.1</v>
       </c>
-      <c r="AU8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BH8" t="n">
         <v>1000</v>
       </c>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -2638,16 +2638,16 @@
         <v>1.36</v>
       </c>
       <c r="G9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H9" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="I9" t="n">
-        <v>110</v>
+        <v>10.5</v>
       </c>
       <c r="J9" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="K9" t="n">
         <v>7.8</v>
@@ -2656,7 +2656,7 @@
         <v>1.19</v>
       </c>
       <c r="M9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
         <v>2.6</v>
@@ -2668,10 +2668,10 @@
         <v>2.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="R9" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="S9" t="n">
         <v>2.04</v>
@@ -2683,10 +2683,10 @@
         <v>2.18</v>
       </c>
       <c r="V9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X9" t="n">
         <v>44</v>
@@ -2701,10 +2701,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AD9" t="n">
         <v>38</v>
@@ -2713,88 +2713,88 @@
         <v>120</v>
       </c>
       <c r="AF9" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
         <v>90</v>
       </c>
       <c r="AJ9" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AK9" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AL9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM9" t="n">
         <v>95</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AO9" t="n">
         <v>95</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.58</v>
+        <v>4.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -2895,16 +2895,16 @@
         <v>1.48</v>
       </c>
       <c r="H10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J10" t="n">
         <v>5.2</v>
       </c>
       <c r="K10" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="L10" t="n">
         <v>1.21</v>
@@ -2919,13 +2919,13 @@
         <v>1.15</v>
       </c>
       <c r="P10" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="Q10" t="n">
         <v>1.44</v>
       </c>
       <c r="R10" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="S10" t="n">
         <v>2.08</v>
@@ -2955,34 +2955,34 @@
         <v>230</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE10" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
         <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>30</v>
@@ -2997,16 +2997,16 @@
         <v>85</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -3030,25 +3030,25 @@
         <v>4.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB10" t="n">
         <v>10</v>
       </c>
       <c r="BC10" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="BD10" t="n">
         <v>4.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.7</v>
+        <v>2.68</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3069,7 +3069,7 @@
         <v>1.13</v>
       </c>
       <c r="BN10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BO10" t="n">
         <v>3.4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -3167,25 +3167,25 @@
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O11" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="P11" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="R11" t="n">
         <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
         <v>1.75</v>
@@ -3197,25 +3197,25 @@
         <v>1.23</v>
       </c>
       <c r="X11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AA11" t="n">
         <v>29</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AC11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
         <v>32</v>
@@ -3254,13 +3254,13 @@
         <v>7.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
         <v>8.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
         <v>9.800000000000001</v>
@@ -3272,73 +3272,73 @@
         <v>8.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>90</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BT11" t="n">
         <v>4.6</v>
@@ -3350,23 +3350,23 @@
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="O12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3448,7 +3448,7 @@
         <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,12 +3896,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FC Arbaer</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sindri</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3932,19 +3932,19 @@
         <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="P14" t="n">
         <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="R14" t="n">
         <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fjolnir</t>
+          <t>FC Arbaer</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>Sindri</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4183,22 +4183,22 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="O15" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="P15" t="n">
         <v>1.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="R15" t="n">
         <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.46</v>
+        <v>1.76</v>
       </c>
       <c r="G16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S16" t="n">
         <v>2.7</v>
       </c>
-      <c r="H16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="T16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X16" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK16" t="n">
         <v>5</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N16" t="n">
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>18</v>
+      </c>
+      <c r="CA16" t="n">
         <v>6.4</v>
       </c>
-      <c r="O16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X16" t="n">
-        <v>40</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>1.01</v>
-      </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,246 +4658,246 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="G17" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X17" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>230</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD17" t="n">
         <v>5</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH17" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="BI17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO17" t="n">
         <v>3.2</v>
       </c>
-      <c r="BJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU17" t="n">
         <v>5.5</v>
       </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>3.7</v>
+        <v>2.46</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.6</v>
+        <v>1.97</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,246 +4912,246 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.68</v>
+        <v>2.52</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8</v>
+        <v>2.76</v>
       </c>
       <c r="H18" t="n">
-        <v>5.2</v>
+        <v>2.44</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>2.68</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="M18" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="P18" t="n">
-        <v>1.75</v>
+        <v>2.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.77</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.96</v>
+        <v>1.45</v>
       </c>
       <c r="U18" t="n">
-        <v>1.78</v>
+        <v>2.88</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="X18" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO18" t="n">
         <v>14</v>
       </c>
-      <c r="Y18" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>240</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="AP18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG18" t="n">
         <v>8.4</v>
       </c>
-      <c r="AC18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BH18" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Dalvik/Reynir</t>
+          <t>Olympique Akbou</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Throttur Vogar</t>
+          <t>ES Ben Aknoun</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -5187,7 +5187,7 @@
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K19" t="n">
         <v>950</v>
@@ -5199,22 +5199,22 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="P19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="S19" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="T19" t="n">
         <v>1.01</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,36 +5415,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Deportes Copiapo</t>
+          <t>Dalvik/Reynir</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Throttur Vogar</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="I20" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1</v>
+        <v>1.02</v>
       </c>
       <c r="K20" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -5453,22 +5453,22 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>1.05</v>
       </c>
       <c r="O20" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="P20" t="n">
-        <v>2.12</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.73</v>
+        <v>1.15</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>2.84</v>
+        <v>1.15</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -5477,10 +5477,10 @@
         <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5645,14 +5645,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -5674,229 +5674,229 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Deportes Copiapo</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cobreloa Calama</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>2.94</v>
+        <v>2.3</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="I21" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>2.96</v>
+        <v>3.8</v>
       </c>
       <c r="O21" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="P21" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U21" t="n">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="V21" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="W21" t="n">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="X21" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN21" t="n">
         <v>16</v>
       </c>
-      <c r="Y21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.44</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.39</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.44</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.44</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.44</v>
+        <v>10.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21" t="n">
         <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BT21" t="n">
         <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,251 +5923,251 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Torque</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Cobreloa Calama</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="G22" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H22" t="n">
         <v>2.7</v>
       </c>
-      <c r="H22" t="n">
-        <v>3</v>
-      </c>
       <c r="I22" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="J22" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="P22" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S22" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="U22" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W22" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="X22" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="Y22" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
         <v>42</v>
       </c>
       <c r="AF22" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AG22" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI22" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
         <v>40</v>
       </c>
-      <c r="AK22" t="n">
-        <v>32</v>
-      </c>
       <c r="AL22" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AP22" t="n">
-        <v>10.5</v>
+        <v>1.37</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>17.5</v>
+        <v>1.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.6</v>
+        <v>1.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.4</v>
+        <v>1.29</v>
       </c>
       <c r="AV22" t="n">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>8</v>
+        <v>1.45</v>
       </c>
       <c r="AX22" t="n">
-        <v>13.5</v>
+        <v>1.41</v>
       </c>
       <c r="AY22" t="n">
-        <v>10.5</v>
+        <v>1.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16</v>
+        <v>1.41</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.4</v>
+        <v>1.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>27</v>
+        <v>1.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>7.6</v>
+        <v>1.45</v>
       </c>
       <c r="BD22" t="n">
-        <v>8.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>19.5</v>
+        <v>1.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>8</v>
+        <v>1.44</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="BJ22" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>2.64</v>
+        <v>1.36</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>3.2</v>
+        <v>1.36</v>
       </c>
       <c r="BN22" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.55</v>
+        <v>1.36</v>
       </c>
       <c r="BP22" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>2.92</v>
+        <v>1.36</v>
       </c>
       <c r="BR22" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>3.05</v>
+        <v>1.36</v>
       </c>
       <c r="BT22" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>4.1</v>
+        <v>1.36</v>
       </c>
       <c r="BV22" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>2.98</v>
+        <v>1.36</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>3.05</v>
+        <v>1.36</v>
       </c>
       <c r="BZ22" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="CA22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,180 +6177,180 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="G23" t="n">
-        <v>1.89</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="I23" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="K23" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>1.25</v>
       </c>
       <c r="O23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P23" t="n">
         <v>1.24</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.32</v>
-      </c>
       <c r="Q23" t="n">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="R23" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="S23" t="n">
-        <v>2.72</v>
+        <v>1.38</v>
       </c>
       <c r="T23" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU23" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AV23" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>46</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -6431,251 +6431,251 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Torque</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.66</v>
+        <v>2.42</v>
       </c>
       <c r="G24" t="n">
-        <v>1.77</v>
+        <v>2.7</v>
       </c>
       <c r="H24" t="n">
-        <v>5.4</v>
+        <v>3.05</v>
       </c>
       <c r="I24" t="n">
-        <v>7.2</v>
+        <v>3.45</v>
       </c>
       <c r="J24" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="K24" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M24" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="O24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R24" t="n">
         <v>1.28</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.4</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="X24" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="Z24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI24" t="n">
         <v>55</v>
       </c>
-      <c r="AA24" t="n">
-        <v>180</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>90</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="AK24" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AL24" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM24" t="n">
         <v>140</v>
       </c>
       <c r="AN24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV24" t="n">
         <v>12</v>
       </c>
-      <c r="AO24" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP24" t="n">
+      <c r="AW24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
         <v>12</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS24" t="n">
+      <c r="BN24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO24" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT24" t="n">
+      <c r="BP24" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ24" t="n">
         <v>7.8</v>
       </c>
-      <c r="AU24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX24" t="n">
+      <c r="BR24" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>32</v>
+      </c>
+      <c r="CA24" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AY24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BX24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BZ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA24" t="n">
-        <v>1.29</v>
-      </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,36 +6685,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="G25" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="I25" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="K25" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -6723,213 +6723,213 @@
         <v>1.05</v>
       </c>
       <c r="N25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH25" t="n">
         <v>4.1</v>
       </c>
-      <c r="O25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X25" t="n">
+      <c r="BI25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
         <v>21</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="BN25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BR25" t="n">
         <v>25</v>
       </c>
-      <c r="Z25" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>1000</v>
-      </c>
       <c r="BS25" t="n">
-        <v>1.29</v>
+        <v>19.5</v>
       </c>
       <c r="BT25" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.29</v>
+        <v>6.8</v>
       </c>
       <c r="BV25" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.29</v>
+        <v>23</v>
       </c>
       <c r="BX25" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.29</v>
+        <v>32</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.29</v>
+        <v>13</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,251 +6939,251 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FC Supra du Quebec</t>
+          <t>Nacional (Uru)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="G26" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="I26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X26" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB26" t="n">
         <v>11</v>
       </c>
-      <c r="J26" t="n">
+      <c r="AC26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR26" t="n">
         <v>3.95</v>
       </c>
-      <c r="K26" t="n">
-        <v>950</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH26" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BN26" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BP26" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BR26" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BT26" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7193,498 +7193,1006 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CSD Rangers</t>
+          <t>Cavalry</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Club Deportes Santa Cruz</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>2.74</v>
+        <v>1.71</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="J27" t="n">
-        <v>2.94</v>
+        <v>3.7</v>
       </c>
       <c r="K27" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>1.65</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="P27" t="n">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="R27" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="T27" t="n">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
       <c r="U27" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="V27" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="W27" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="X27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y27" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="Z27" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF27" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AG27" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ27" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="AK27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL27" t="n">
         <v>38</v>
       </c>
-      <c r="AL27" t="n">
-        <v>1000</v>
-      </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.91</v>
+        <v>1.03</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.9</v>
+        <v>1.03</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.99</v>
+        <v>1.03</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.84</v>
+        <v>7</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.78</v>
+        <v>7.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.92</v>
+        <v>1.03</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.92</v>
+        <v>8</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.88</v>
+        <v>7.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.95</v>
+        <v>1.03</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB27" t="n">
-        <v>2.02</v>
+        <v>1.03</v>
       </c>
       <c r="BC27" t="n">
-        <v>2</v>
+        <v>1.03</v>
       </c>
       <c r="BD27" t="n">
-        <v>2.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF27" t="n">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="BG27" t="n">
-        <v>2.1</v>
+        <v>65</v>
       </c>
       <c r="BH27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.38</v>
+        <v>2.76</v>
       </c>
       <c r="BJ27" t="n">
         <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BN27" t="n">
         <v>1000</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BP27" t="n">
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BT27" t="n">
         <v>1000</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BZ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FC Supra du Quebec</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I28" t="n">
+        <v>12</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K28" t="n">
+        <v>950</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-06-05 03:04:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Chilean Primera B</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>21:30:00</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CSD Rangers</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Club Deportes Santa Cruz</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G29" t="n">
+        <v>110</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I29" t="n">
+        <v>190</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-06-05 03:04:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Deportes Iquique</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Deportes Recoleta</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F30" t="n">
         <v>1.74</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G30" t="n">
         <v>1.94</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H30" t="n">
         <v>4.4</v>
       </c>
-      <c r="I28" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="I30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J30" t="n">
         <v>3.55</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K30" t="n">
         <v>5</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N28" t="n">
+      <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
         <v>3.5</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O30" t="n">
         <v>1.29</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P30" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q30" t="n">
         <v>1.84</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R30" t="n">
         <v>1.32</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S30" t="n">
         <v>2.86</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T30" t="n">
         <v>1.66</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U30" t="n">
         <v>1.86</v>
       </c>
-      <c r="V28" t="n">
+      <c r="V30" t="n">
         <v>1.2</v>
       </c>
-      <c r="W28" t="n">
+      <c r="W30" t="n">
         <v>2.06</v>
       </c>
-      <c r="X28" t="n">
+      <c r="X30" t="n">
         <v>970</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Y30" t="n">
         <v>22</v>
       </c>
-      <c r="Z28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
         <v>970</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AC30" t="n">
         <v>970</v>
       </c>
-      <c r="AD28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH28" t="n">
+      <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH30" t="n">
         <v>4.3</v>
       </c>
-      <c r="BI28" t="n">
+      <c r="BI30" t="n">
         <v>2.66</v>
       </c>
-      <c r="BJ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ28" t="n">
+      <c r="BJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BZ30" t="n">
         <v>0</v>
       </c>
-      <c r="CA28" t="n">
+      <c r="CA30" t="n">
         <v>0</v>
       </c>
-      <c r="CB28" t="inlineStr">
-        <is>
-          <t>2026-06-05 00:53:58</t>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G2" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H2" t="n">
         <v>2.92</v>
@@ -875,7 +875,7 @@
         <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -893,34 +893,34 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V2" t="n">
         <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X2" t="n">
         <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
         <v>12</v>
@@ -929,13 +929,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
         <v>14</v>
@@ -947,7 +947,7 @@
         <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK2" t="n">
         <v>34</v>
@@ -959,7 +959,7 @@
         <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO2" t="n">
         <v>42</v>
@@ -968,25 +968,25 @@
         <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2" t="n">
         <v>16</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
         <v>8</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -998,25 +998,25 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I3" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
@@ -1153,37 +1153,37 @@
         <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U3" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="W3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X3" t="n">
         <v>15.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AC3" t="n">
         <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE3" t="n">
         <v>24</v>
@@ -1195,28 +1195,28 @@
         <v>22</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AK3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL3" t="n">
         <v>65</v>
       </c>
-      <c r="AL3" t="n">
-        <v>80</v>
-      </c>
       <c r="AM3" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AO3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AP3" t="n">
         <v>9.6</v>
@@ -1228,13 +1228,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AT3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
         <v>7.8</v>
@@ -1243,52 +1243,52 @@
         <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN3" t="n">
         <v>7.8</v>
@@ -1300,31 +1300,31 @@
         <v>38</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3" t="n">
         <v>4.9</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BV3" t="n">
         <v>15.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="BX3" t="n">
         <v>32</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="H4" t="n">
         <v>4.4</v>
@@ -1377,52 +1377,52 @@
         <v>7.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
         <v>1.02</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.66</v>
-      </c>
       <c r="O4" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
         <v>2.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="R4" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="T4" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="U4" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="V4" t="n">
         <v>1.16</v>
       </c>
       <c r="W4" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="X4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Y4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z4" t="n">
         <v>60</v>
@@ -1431,125 +1431,125 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
         <v>27</v>
       </c>
       <c r="AE4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI4" t="n">
         <v>75</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>70</v>
       </c>
       <c r="AJ4" t="n">
         <v>20</v>
       </c>
       <c r="AK4" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AL4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.8</v>
+        <v>2.02</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.8</v>
+        <v>2.02</v>
       </c>
       <c r="AR4" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.2</v>
+        <v>2.14</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="AW4" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.6</v>
+        <v>1.99</v>
       </c>
       <c r="BA4" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BC4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
         <v>3.5</v>
       </c>
-      <c r="BD4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>1.41</v>
       </c>
       <c r="G5" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="H5" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
         <v>6</v>
@@ -1643,151 +1643,151 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="R5" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="T5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
         <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI5" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK5" t="n">
         <v>1.01</v>
@@ -1799,25 +1799,25 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO5" t="n">
         <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BQ5" t="n">
         <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS5" t="n">
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU5" t="n">
         <v>1.01</v>
@@ -1835,14 +1835,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA5" t="n">
         <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>1.86</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I6" t="n">
         <v>5.7</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -2130,61 +2130,61 @@
         <v>2.64</v>
       </c>
       <c r="G7" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H7" t="n">
         <v>2.74</v>
       </c>
       <c r="I7" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K7" t="n">
         <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
         <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
         <v>1.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="U7" t="n">
         <v>2.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X7" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
         <v>27</v>
@@ -2193,28 +2193,28 @@
         <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF7" t="n">
         <v>20</v>
       </c>
       <c r="AG7" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ7" t="n">
         <v>40</v>
@@ -2232,79 +2232,79 @@
         <v>21</v>
       </c>
       <c r="AO7" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>3.75</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS7" t="n">
+      <c r="BA7" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW7" t="n">
+      <c r="BB7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC7" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB7" t="n">
+      <c r="BD7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG7" t="n">
         <v>4.1</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BH7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
         <v>4</v>
       </c>
-      <c r="BD7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
@@ -2316,13 +2316,13 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
@@ -2334,23 +2334,23 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G8" t="n">
         <v>2.92</v>
@@ -2393,40 +2393,40 @@
         <v>3.2</v>
       </c>
       <c r="J8" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="K8" t="n">
         <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q8" t="n">
         <v>1.61</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
         <v>2.42</v>
       </c>
       <c r="T8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V8" t="n">
         <v>1.45</v>
@@ -2438,7 +2438,7 @@
         <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
         <v>25</v>
@@ -2447,13 +2447,13 @@
         <v>50</v>
       </c>
       <c r="AB8" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
         <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
         <v>34</v>
@@ -2462,10 +2462,10 @@
         <v>22</v>
       </c>
       <c r="AG8" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AI8" t="n">
         <v>42</v>
@@ -2474,73 +2474,73 @@
         <v>42</v>
       </c>
       <c r="AK8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL8" t="n">
         <v>38</v>
       </c>
       <c r="AM8" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN8" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AO8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4</v>
-      </c>
       <c r="BG8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -2641,13 +2641,13 @@
         <v>1.47</v>
       </c>
       <c r="H9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
         <v>10.5</v>
       </c>
       <c r="J9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
         <v>7.8</v>
@@ -2656,22 +2656,22 @@
         <v>1.19</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="R9" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="S9" t="n">
         <v>2.04</v>
@@ -2692,7 +2692,7 @@
         <v>44</v>
       </c>
       <c r="Y9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Z9" t="n">
         <v>100</v>
@@ -2701,25 +2701,25 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AE9" t="n">
         <v>120</v>
       </c>
       <c r="AF9" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
         <v>90</v>
@@ -2728,7 +2728,7 @@
         <v>16</v>
       </c>
       <c r="AK9" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AL9" t="n">
         <v>34</v>
@@ -2743,61 +2743,61 @@
         <v>95</v>
       </c>
       <c r="AP9" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AR9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BA9" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BI9" t="n">
         <v>3.35</v>
@@ -2812,7 +2812,7 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.52</v>
+        <v>2.42</v>
       </c>
       <c r="BN9" t="n">
         <v>4.7</v>
@@ -2824,7 +2824,7 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2842,13 +2842,13 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.67</v>
+        <v>4.1</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.08</v>
+        <v>4.1</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
         <v>2.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R10" t="n">
         <v>1.77</v>
@@ -2955,10 +2955,10 @@
         <v>230</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
         <v>34</v>
@@ -2967,10 +2967,10 @@
         <v>100</v>
       </c>
       <c r="AF10" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
         <v>23</v>
@@ -2979,10 +2979,10 @@
         <v>80</v>
       </c>
       <c r="AJ10" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AL10" t="n">
         <v>30</v>
@@ -3036,22 +3036,22 @@
         <v>10</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.7</v>
+        <v>19.5</v>
       </c>
       <c r="BE10" t="n">
         <v>5.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.68</v>
+        <v>3.7</v>
       </c>
       <c r="BG10" t="n">
         <v>5.3</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BI10" t="n">
         <v>3.75</v>
@@ -3060,59 +3060,59 @@
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>2.58</v>
+        <v>7.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="BN10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
         <v>1.29</v>
       </c>
-      <c r="BT10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
         <v>1.27</v>
       </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -3149,31 +3149,31 @@
         <v>5.3</v>
       </c>
       <c r="H11" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="I11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J11" t="n">
         <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="O11" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="P11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q11" t="n">
         <v>2.46</v>
@@ -3185,13 +3185,13 @@
         <v>4.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U11" t="n">
         <v>1.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="W11" t="n">
         <v>1.23</v>
@@ -3200,7 +3200,7 @@
         <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z11" t="n">
         <v>12.5</v>
@@ -3209,7 +3209,7 @@
         <v>29</v>
       </c>
       <c r="AB11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC11" t="n">
         <v>8.800000000000001</v>
@@ -3224,7 +3224,7 @@
         <v>40</v>
       </c>
       <c r="AG11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH11" t="n">
         <v>28</v>
@@ -3248,7 +3248,7 @@
         <v>150</v>
       </c>
       <c r="AO11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
         <v>7.6</v>
@@ -3323,7 +3323,7 @@
         <v>21</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO11" t="n">
         <v>6.2</v>
@@ -3338,7 +3338,7 @@
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BT11" t="n">
         <v>4.6</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="K12" t="n">
         <v>950</v>
@@ -3421,7 +3421,7 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="O12" t="n">
         <v>1.18</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K13" t="n">
         <v>950</v>
@@ -3675,22 +3675,22 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="O13" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="R13" t="n">
         <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -3926,10 +3926,10 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O14" t="n">
         <v>1.11</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -4428,10 +4428,10 @@
         <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
@@ -4479,7 +4479,7 @@
         <v>110</v>
       </c>
       <c r="AB16" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AC16" t="n">
         <v>11</v>
@@ -4491,10 +4491,10 @@
         <v>65</v>
       </c>
       <c r="AF16" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
         <v>21</v>
@@ -4521,16 +4521,16 @@
         <v>60</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT16" t="n">
         <v>8.4</v>
@@ -4539,10 +4539,10 @@
         <v>7.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX16" t="n">
         <v>9.4</v>
@@ -4551,46 +4551,46 @@
         <v>8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF16" t="n">
         <v>7.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>38</v>
+        <v>4.9</v>
       </c>
       <c r="BH16" t="n">
         <v>4.1</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK16" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BN16" t="n">
         <v>4.9</v>
@@ -4602,25 +4602,25 @@
         <v>12.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR16" t="n">
         <v>24</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
@@ -4629,14 +4629,14 @@
         <v>2.08</v>
       </c>
       <c r="BZ16" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CA16" t="n">
         <v>6.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -4673,13 +4673,13 @@
         <v>1.81</v>
       </c>
       <c r="H17" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="I17" t="n">
         <v>8</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
         <v>3.95</v>
@@ -4691,22 +4691,22 @@
         <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O17" t="n">
         <v>1.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q17" t="n">
         <v>2.16</v>
       </c>
       <c r="R17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
         <v>2.02</v>
@@ -4775,122 +4775,122 @@
         <v>190</v>
       </c>
       <c r="AP17" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AT17" t="n">
         <v>5.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.55</v>
+        <v>8.4</v>
       </c>
       <c r="AY17" t="n">
         <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BD17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE17" t="n">
         <v>5</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>5.4</v>
       </c>
       <c r="BF17" t="n">
         <v>10.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU17" t="n">
         <v>6</v>
       </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>2.46</v>
+        <v>1.71</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.97</v>
+        <v>1.21</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -4921,16 +4921,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="G18" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="H18" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="I18" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="J18" t="n">
         <v>4.1</v>
@@ -4942,37 +4942,37 @@
         <v>1.2</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="O18" t="n">
         <v>1.15</v>
       </c>
       <c r="P18" t="n">
-        <v>2.74</v>
+        <v>2.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R18" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T18" t="n">
         <v>1.45</v>
       </c>
       <c r="U18" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.59</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.56</v>
       </c>
       <c r="X18" t="n">
         <v>34</v>
@@ -4993,7 +4993,7 @@
         <v>13.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AE18" t="n">
         <v>28</v>
@@ -5002,19 +5002,19 @@
         <v>29</v>
       </c>
       <c r="AG18" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH18" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AI18" t="n">
         <v>27</v>
       </c>
       <c r="AJ18" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL18" t="n">
         <v>27</v>
@@ -5023,64 +5023,64 @@
         <v>55</v>
       </c>
       <c r="AN18" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO18" t="n">
         <v>14</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="BG18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G19" t="n">
         <v>1000</v>
@@ -5187,7 +5187,7 @@
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K19" t="n">
         <v>950</v>
@@ -5208,13 +5208,13 @@
         <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R19" t="n">
         <v>1.12</v>
       </c>
       <c r="S19" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T19" t="n">
         <v>1.01</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
         <v>2.3</v>
       </c>
       <c r="H21" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="I21" t="n">
         <v>3.8</v>
@@ -5701,28 +5701,28 @@
         <v>4.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
         <v>1.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T21" t="n">
         <v>1.64</v>
@@ -5791,67 +5791,67 @@
         <v>38</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BF21" t="n">
         <v>10.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI21" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK21" t="n">
         <v>1.01</v>
@@ -5863,13 +5863,13 @@
         <v>1.01</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO21" t="n">
         <v>1.01</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ21" t="n">
         <v>1.01</v>
@@ -5881,7 +5881,7 @@
         <v>1.01</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU21" t="n">
         <v>1.01</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -5940,13 +5940,13 @@
         <v>2.6</v>
       </c>
       <c r="G22" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H22" t="n">
         <v>2.7</v>
       </c>
       <c r="I22" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J22" t="n">
         <v>3.25</v>
@@ -5958,10 +5958,10 @@
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="O22" t="n">
         <v>1.33</v>
@@ -5973,130 +5973,130 @@
         <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="U22" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="V22" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W22" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X22" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK22" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO22" t="n">
         <v>36</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.37</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.5</v>
+        <v>8.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.5</v>
+        <v>8.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.29</v>
+        <v>6</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.45</v>
+        <v>4.4</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.41</v>
+        <v>13.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.41</v>
+        <v>13.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.45</v>
+        <v>4.4</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.5</v>
+        <v>21</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.44</v>
+        <v>4.3</v>
       </c>
       <c r="BH22" t="n">
         <v>3.85</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G23" t="n">
         <v>1000</v>
@@ -6203,7 +6203,7 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K23" t="n">
         <v>950</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
         <v>3.15</v>
       </c>
       <c r="K24" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L24" t="n">
         <v>1.37</v>
@@ -6472,13 +6472,13 @@
         <v>3.15</v>
       </c>
       <c r="O24" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P24" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R24" t="n">
         <v>1.28</v>
@@ -6490,7 +6490,7 @@
         <v>1.86</v>
       </c>
       <c r="U24" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
         <v>1.4</v>
@@ -6514,7 +6514,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD24" t="n">
         <v>15</v>
@@ -6562,7 +6562,7 @@
         <v>17.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT24" t="n">
         <v>8.199999999999999</v>
@@ -6574,7 +6574,7 @@
         <v>12</v>
       </c>
       <c r="AW24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX24" t="n">
         <v>13.5</v>
@@ -6586,37 +6586,37 @@
         <v>16</v>
       </c>
       <c r="BA24" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB24" t="n">
         <v>27</v>
       </c>
       <c r="BC24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF24" t="n">
         <v>19.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH24" t="n">
         <v>3.25</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="BJ24" t="n">
         <v>10</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
@@ -6634,7 +6634,7 @@
         <v>20</v>
       </c>
       <c r="BQ24" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR24" t="n">
         <v>36</v>
@@ -6649,7 +6649,7 @@
         <v>4.7</v>
       </c>
       <c r="BV24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BW24" t="n">
         <v>8.800000000000001</v>
@@ -6658,17 +6658,17 @@
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ24" t="n">
         <v>32</v>
       </c>
       <c r="CA24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -6702,10 +6702,10 @@
         <v>1.85</v>
       </c>
       <c r="G25" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I25" t="n">
         <v>4.7</v>
@@ -6717,40 +6717,40 @@
         <v>4.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M25" t="n">
         <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O25" t="n">
         <v>1.24</v>
       </c>
       <c r="P25" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R25" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="T25" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U25" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="V25" t="n">
         <v>1.27</v>
       </c>
       <c r="W25" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X25" t="n">
         <v>19.5</v>
@@ -6774,7 +6774,7 @@
         <v>19</v>
       </c>
       <c r="AE25" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF25" t="n">
         <v>13</v>
@@ -6792,13 +6792,13 @@
         <v>21</v>
       </c>
       <c r="AK25" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL25" t="n">
         <v>29</v>
       </c>
       <c r="AM25" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN25" t="n">
         <v>10</v>
@@ -6816,7 +6816,7 @@
         <v>32</v>
       </c>
       <c r="AS25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT25" t="n">
         <v>9.4</v>
@@ -6882,7 +6882,7 @@
         <v>5</v>
       </c>
       <c r="BO25" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="BP25" t="n">
         <v>13</v>
@@ -6894,13 +6894,13 @@
         <v>25</v>
       </c>
       <c r="BS25" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BT25" t="n">
         <v>8.4</v>
       </c>
       <c r="BU25" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV25" t="n">
         <v>36</v>
@@ -6912,7 +6912,7 @@
         <v>40</v>
       </c>
       <c r="BY25" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BZ25" t="n">
         <v>19</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="G26" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H26" t="n">
         <v>5.4</v>
@@ -6965,19 +6965,19 @@
         <v>7.2</v>
       </c>
       <c r="J26" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M26" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
         <v>1.28</v>
@@ -6986,16 +6986,16 @@
         <v>2.02</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R26" t="n">
         <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T26" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U26" t="n">
         <v>2.02</v>
@@ -7007,16 +7007,16 @@
         <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z26" t="n">
         <v>60</v>
       </c>
       <c r="AA26" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AB26" t="n">
         <v>11</v>
@@ -7040,7 +7040,7 @@
         <v>25</v>
       </c>
       <c r="AI26" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ26" t="n">
         <v>21</v>
@@ -7058,43 +7058,43 @@
         <v>12</v>
       </c>
       <c r="AO26" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP26" t="n">
         <v>12</v>
       </c>
       <c r="AQ26" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW26" t="n">
         <v>3.95</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>4</v>
       </c>
       <c r="AX26" t="n">
         <v>8</v>
       </c>
       <c r="AY26" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AZ26" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BB26" t="n">
         <v>12.5</v>
@@ -7103,37 +7103,37 @@
         <v>13</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.8</v>
+        <v>26</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BH26" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>2.86</v>
+        <v>1.86</v>
       </c>
       <c r="BJ26" t="n">
         <v>15</v>
       </c>
       <c r="BK26" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>3.15</v>
+        <v>1.86</v>
       </c>
       <c r="BN26" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO26" t="n">
         <v>2.92</v>
@@ -7142,41 +7142,41 @@
         <v>16</v>
       </c>
       <c r="BQ26" t="n">
-        <v>2.64</v>
+        <v>1.67</v>
       </c>
       <c r="BR26" t="n">
         <v>38</v>
       </c>
       <c r="BS26" t="n">
-        <v>2.92</v>
+        <v>1.78</v>
       </c>
       <c r="BT26" t="n">
         <v>13</v>
       </c>
       <c r="BU26" t="n">
-        <v>2.54</v>
+        <v>1.63</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>3</v>
+        <v>1.82</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>3</v>
+        <v>1.82</v>
       </c>
       <c r="BZ26" t="n">
         <v>29</v>
       </c>
       <c r="CA26" t="n">
-        <v>2.84</v>
+        <v>1.75</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -7210,19 +7210,19 @@
         <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="I27" t="n">
         <v>7.2</v>
       </c>
       <c r="J27" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K27" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -7246,7 +7246,7 @@
         <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="T27" t="n">
         <v>1.81</v>
@@ -7255,16 +7255,16 @@
         <v>2.02</v>
       </c>
       <c r="V27" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W27" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="X27" t="n">
         <v>21</v>
       </c>
       <c r="Y27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z27" t="n">
         <v>60</v>
@@ -7279,7 +7279,7 @@
         <v>11.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE27" t="n">
         <v>95</v>
@@ -7327,7 +7327,7 @@
         <v>1.03</v>
       </c>
       <c r="AT27" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU27" t="n">
         <v>7.6</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -7461,118 +7461,118 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T28" t="n">
         <v>1.71</v>
       </c>
-      <c r="H28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I28" t="n">
+      <c r="U28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X28" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG28" t="n">
         <v>12</v>
       </c>
-      <c r="J28" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K28" t="n">
-        <v>950</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1000</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AR28" t="n">
         <v>1.03</v>
@@ -7581,34 +7581,34 @@
         <v>1.03</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AW28" t="n">
         <v>1.03</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA28" t="n">
         <v>1.03</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BD28" t="n">
         <v>1.03</v>
@@ -7617,22 +7617,22 @@
         <v>1.03</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BH28" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BJ28" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
@@ -7641,50 +7641,50 @@
         <v>1.01</v>
       </c>
       <c r="BN28" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP28" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR28" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BT28" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BV28" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW28" t="n">
         <v>1.01</v>
       </c>
       <c r="BX28" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY28" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ28" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -7715,19 +7715,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.45</v>
+        <v>2.14</v>
       </c>
       <c r="G29" t="n">
-        <v>110</v>
+        <v>2.74</v>
       </c>
       <c r="H29" t="n">
-        <v>1.45</v>
+        <v>3.05</v>
       </c>
       <c r="I29" t="n">
-        <v>190</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
-        <v>1.02</v>
+        <v>2.94</v>
       </c>
       <c r="K29" t="n">
         <v>3.3</v>
@@ -7736,79 +7736,79 @@
         <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="O29" t="n">
         <v>1.33</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>1.72</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S29" t="n">
-        <v>1.32</v>
+        <v>1.81</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE29" t="n">
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI29" t="n">
         <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL29" t="n">
         <v>1000</v>
@@ -7823,112 +7823,112 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BH29" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BJ29" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BN29" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO29" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BP29" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BR29" t="n">
         <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BT29" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BZ29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -7972,64 +7972,64 @@
         <v>1.74</v>
       </c>
       <c r="G30" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I30" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="J30" t="n">
         <v>3.55</v>
       </c>
       <c r="K30" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O30" t="n">
         <v>1.29</v>
       </c>
       <c r="P30" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q30" t="n">
         <v>1.84</v>
       </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="U30" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W30" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X30" t="n">
         <v>970</v>
       </c>
       <c r="Y30" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
@@ -8041,88 +8041,88 @@
         <v>970</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
         <v>1.01</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB30"/>
+  <dimension ref="A1:CB34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G2" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H2" t="n">
         <v>2.92</v>
@@ -875,7 +875,7 @@
         <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -926,7 +926,7 @@
         <v>12</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
         <v>16</v>
@@ -935,7 +935,7 @@
         <v>44</v>
       </c>
       <c r="AF2" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
         <v>14</v>
@@ -974,19 +974,19 @@
         <v>16</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT2" t="n">
         <v>8</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -998,25 +998,25 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE2" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5</v>
       </c>
       <c r="BF2" t="n">
         <v>18</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -1123,10 +1123,10 @@
         <v>2.16</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
         <v>1.36</v>
@@ -1135,16 +1135,16 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O3" t="n">
         <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="R3" t="n">
         <v>1.3</v>
@@ -1153,10 +1153,10 @@
         <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V3" t="n">
         <v>1.87</v>
@@ -1168,58 +1168,58 @@
         <v>15.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AB3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH3" t="n">
         <v>24</v>
       </c>
-      <c r="AF3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>20</v>
-      </c>
       <c r="AI3" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AJ3" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AK3" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AL3" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN3" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AO3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.4</v>
@@ -1228,7 +1228,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
@@ -1237,13 +1237,13 @@
         <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX3" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="AY3" t="n">
         <v>12.5</v>
@@ -1252,22 +1252,22 @@
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="BG3" t="n">
         <v>12.5</v>
@@ -1276,7 +1276,7 @@
         <v>3.35</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="G4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="H4" t="n">
         <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1398,13 +1398,13 @@
         <v>2.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R4" t="n">
         <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
         <v>1.67</v>
@@ -1413,13 +1413,13 @@
         <v>2.16</v>
       </c>
       <c r="V4" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="X4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y4" t="n">
         <v>30</v>
@@ -1473,58 +1473,58 @@
         <v>75</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.02</v>
+        <v>3.75</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.02</v>
+        <v>3.75</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.14</v>
+        <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.12</v>
+        <v>4.1</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.99</v>
+        <v>3.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.04</v>
+        <v>3.85</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.12</v>
+        <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1548,7 +1548,7 @@
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>1.41</v>
       </c>
       <c r="G5" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I5" t="n">
         <v>9.6</v>
@@ -1655,28 +1655,28 @@
         <v>1.51</v>
       </c>
       <c r="R5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T5" t="n">
         <v>1.6</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.7</v>
-      </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="V5" t="n">
         <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="X5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z5" t="n">
         <v>80</v>
@@ -1691,7 +1691,7 @@
         <v>14.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE5" t="n">
         <v>120</v>
@@ -1709,13 +1709,13 @@
         <v>95</v>
       </c>
       <c r="AJ5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK5" t="n">
         <v>16.5</v>
       </c>
-      <c r="AK5" t="n">
-        <v>18</v>
-      </c>
       <c r="AL5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM5" t="n">
         <v>120</v>
@@ -1727,122 +1727,122 @@
         <v>120</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AR5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>4</v>
       </c>
-      <c r="AS5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW5" t="n">
+      <c r="BA5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BD5" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BE5" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BH5" t="n">
         <v>4.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BJ5" t="n">
         <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BN5" t="n">
         <v>4.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP5" t="n">
         <v>9.6</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BR5" t="n">
         <v>23</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BT5" t="n">
         <v>12</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BZ5" t="n">
         <v>13.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>1.86</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>5.7</v>
@@ -1897,7 +1897,7 @@
         <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="O6" t="n">
         <v>1.18</v>
@@ -1912,7 +1912,7 @@
         <v>1.59</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="T6" t="n">
         <v>1.58</v>
@@ -1969,70 +1969,70 @@
         <v>17.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM6" t="n">
         <v>80</v>
       </c>
       <c r="AN6" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AO6" t="n">
         <v>46</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AR6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD6" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="BE6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG6" t="n">
         <v>5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>4.7</v>
       </c>
       <c r="BH6" t="n">
         <v>4.7</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -2127,31 +2127,31 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G7" t="n">
         <v>2.88</v>
       </c>
       <c r="H7" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="I7" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="n">
         <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>1.02</v>
       </c>
       <c r="O7" t="n">
         <v>1.25</v>
@@ -2160,136 +2160,136 @@
         <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R7" t="n">
         <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="T7" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BI7" t="n">
         <v>2.58</v>
@@ -2322,7 +2322,7 @@
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
@@ -2346,11 +2346,11 @@
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -2384,28 +2384,28 @@
         <v>2.34</v>
       </c>
       <c r="G8" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="H8" t="n">
         <v>2.62</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="J8" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.28</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
         <v>1.24</v>
@@ -2414,7 +2414,7 @@
         <v>2.18</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="R8" t="n">
         <v>1.47</v>
@@ -2423,19 +2423,19 @@
         <v>2.42</v>
       </c>
       <c r="T8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.56</v>
       </c>
-      <c r="U8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.52</v>
-      </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y8" t="n">
         <v>970</v>
@@ -2450,7 +2450,7 @@
         <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
         <v>970</v>
@@ -2492,56 +2492,56 @@
         <v>4.2</v>
       </c>
       <c r="AQ8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4</v>
       </c>
-      <c r="AR8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF8" t="n">
+      <c r="BG8" t="n">
         <v>4.1</v>
       </c>
-      <c r="BG8" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH8" t="n">
         <v>1000</v>
       </c>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="G9" t="n">
         <v>1.47</v>
@@ -2647,31 +2647,31 @@
         <v>10.5</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
         <v>1.19</v>
       </c>
       <c r="M9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
         <v>1.13</v>
       </c>
       <c r="P9" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="Q9" t="n">
         <v>1.39</v>
       </c>
       <c r="R9" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="S9" t="n">
         <v>2.04</v>
@@ -2725,7 +2725,7 @@
         <v>90</v>
       </c>
       <c r="AJ9" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AK9" t="n">
         <v>970</v>
@@ -2737,67 +2737,67 @@
         <v>95</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AO9" t="n">
         <v>95</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AS9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV9" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AW9" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AZ9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB9" t="n">
         <v>4.2</v>
       </c>
-      <c r="BA9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BC9" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BG9" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BH9" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="BI9" t="n">
         <v>3.35</v>
@@ -2824,7 +2824,7 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2848,7 +2848,7 @@
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
         <v>2.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R10" t="n">
         <v>1.77</v>
@@ -2940,10 +2940,10 @@
         <v>1.12</v>
       </c>
       <c r="W10" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="X10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y10" t="n">
         <v>44</v>
@@ -2973,13 +2973,13 @@
         <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
         <v>80</v>
       </c>
       <c r="AJ10" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AK10" t="n">
         <v>970</v>
@@ -2991,22 +2991,22 @@
         <v>90</v>
       </c>
       <c r="AN10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AO10" t="n">
         <v>85</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AR10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS10" t="n">
         <v>5.3</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5.5</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -3015,25 +3015,25 @@
         <v>10</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BB10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC10" t="n">
         <v>10.5</v>
@@ -3042,77 +3042,77 @@
         <v>19.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF10" t="n">
         <v>3.7</v>
       </c>
       <c r="BG10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>5.3</v>
       </c>
-      <c r="BH10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BU10" t="n">
         <v>6.4</v>
       </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.29</v>
+        <v>11</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.27</v>
+        <v>11</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -3149,46 +3149,46 @@
         <v>5.3</v>
       </c>
       <c r="H11" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="I11" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="O11" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="P11" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="V11" t="n">
         <v>1.87</v>
@@ -3197,22 +3197,22 @@
         <v>1.23</v>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AA11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB11" t="n">
         <v>14.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD11" t="n">
         <v>13</v>
@@ -3224,91 +3224,91 @@
         <v>40</v>
       </c>
       <c r="AG11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AH11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI11" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK11" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AL11" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AO11" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AR11" t="n">
         <v>8.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>90</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
@@ -3338,7 +3338,7 @@
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BT11" t="n">
         <v>4.6</v>
@@ -3350,23 +3350,23 @@
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -3400,13 +3400,13 @@
         <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H12" t="n">
         <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J12" t="n">
         <v>1.01</v>
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.26</v>
+        <v>2.46</v>
       </c>
       <c r="O12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -3654,13 +3654,13 @@
         <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="H13" t="n">
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J13" t="n">
         <v>1.01</v>
@@ -3675,13 +3675,13 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.05</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Q13" t="n">
         <v>1.26</v>
@@ -3690,7 +3690,7 @@
         <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,25 +3896,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Fjolnir</t>
+          <t>KA Asvellir</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>Vidir Gardur</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J14" t="n">
         <v>1.02</v>
@@ -3926,25 +3926,25 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
         <v>1.01</v>
       </c>
       <c r="O14" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="P14" t="n">
         <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="R14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -4121,21 +4121,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,25 +4150,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FC Arbaer</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sindri</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J15" t="n">
         <v>1.02</v>
@@ -4180,25 +4180,25 @@
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
         <v>1.05</v>
       </c>
       <c r="O15" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="P15" t="n">
         <v>1.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="R15" t="n">
         <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>FC Arbaer</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>Sindri</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.76</v>
+        <v>1.02</v>
       </c>
       <c r="G16" t="n">
-        <v>1.91</v>
+        <v>110</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3</v>
+        <v>1.02</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>110</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>1.02</v>
       </c>
       <c r="K16" t="n">
-        <v>4.9</v>
+        <v>950</v>
       </c>
       <c r="L16" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N16" t="n">
         <v>1.05</v>
       </c>
-      <c r="N16" t="n">
-        <v>4.4</v>
-      </c>
       <c r="O16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.24</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.47</v>
-      </c>
       <c r="S16" t="n">
-        <v>2.7</v>
+        <v>1.06</v>
       </c>
       <c r="T16" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BP16" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,239 +4658,239 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.68</v>
+        <v>2.46</v>
       </c>
       <c r="G17" t="n">
-        <v>1.81</v>
+        <v>2.66</v>
       </c>
       <c r="H17" t="n">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="K17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X17" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS17" t="n">
         <v>3.95</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="AT17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE17" t="n">
         <v>4</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X17" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>230</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>5</v>
-      </c>
       <c r="BF17" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG17" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -4912,246 +4912,246 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.46</v>
+        <v>1.77</v>
       </c>
       <c r="G18" t="n">
-        <v>2.68</v>
+        <v>1.93</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="I18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S18" t="n">
         <v>2.7</v>
       </c>
-      <c r="J18" t="n">
+      <c r="T18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X18" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH18" t="n">
         <v>4.1</v>
       </c>
-      <c r="K18" t="n">
+      <c r="BI18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU18" t="n">
         <v>4.6</v>
       </c>
-      <c r="L18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="X18" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>19</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,66 +5161,66 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Olympique Akbou</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Ben Aknoun</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>1.81</v>
       </c>
       <c r="H19" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>1.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.34</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>1.37</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
@@ -5229,176 +5229,176 @@
         <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -5415,30 +5415,30 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Dalvik/Reynir</t>
+          <t>KFA Austfjarda</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Throttur Vogar</t>
+          <t>KFG</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J20" t="n">
         <v>1.02</v>
@@ -5453,22 +5453,22 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="P20" t="n">
         <v>1.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="R20" t="n">
         <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -5645,21 +5645,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,189 +5669,189 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Deportes Copiapo</t>
+          <t>Vikingur Olafsvik</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Kari</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.08</v>
+        <v>1.02</v>
       </c>
       <c r="G21" t="n">
-        <v>2.3</v>
+        <v>110</v>
       </c>
       <c r="H21" t="n">
-        <v>3.3</v>
+        <v>1.02</v>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>110</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>1.02</v>
       </c>
       <c r="K21" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>1.25</v>
       </c>
       <c r="O21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P21" t="n">
         <v>1.25</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.12</v>
-      </c>
       <c r="Q21" t="n">
-        <v>1.74</v>
+        <v>1.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>2.72</v>
+        <v>1.1</v>
       </c>
       <c r="T21" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR21" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AY21" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BD21" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ21" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
         <v>1.01</v>
@@ -5863,13 +5863,13 @@
         <v>1.01</v>
       </c>
       <c r="BN21" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
         <v>1.01</v>
       </c>
       <c r="BP21" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
         <v>1.01</v>
@@ -5881,7 +5881,7 @@
         <v>1.01</v>
       </c>
       <c r="BT21" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
         <v>1.01</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,251 +5923,251 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Olympique Akbou</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cobreloa Calama</t>
+          <t>ES Ben Aknoun</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.6</v>
+        <v>1.03</v>
       </c>
       <c r="G22" t="n">
-        <v>2.9</v>
+        <v>110</v>
       </c>
       <c r="H22" t="n">
-        <v>2.7</v>
+        <v>1.02</v>
       </c>
       <c r="I22" t="n">
-        <v>3.05</v>
+        <v>420</v>
       </c>
       <c r="J22" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="K22" t="n">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>3.45</v>
+        <v>1.26</v>
       </c>
       <c r="O22" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P22" t="n">
-        <v>1.84</v>
+        <v>1.26</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="T22" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BN22" t="n">
         <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BT22" t="n">
         <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,33 +6177,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Dalvik/Reynir</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Throttur Vogar</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K23" t="n">
         <v>950</v>
@@ -6215,22 +6215,22 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P23" t="n">
         <v>1.25</v>
       </c>
-      <c r="O23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.12</v>
-      </c>
       <c r="S23" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,251 +6431,251 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Torque</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>UMF Tindstoll</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.42</v>
+        <v>1.02</v>
       </c>
       <c r="G24" t="n">
-        <v>2.7</v>
+        <v>110</v>
       </c>
       <c r="H24" t="n">
-        <v>3.05</v>
+        <v>1.02</v>
       </c>
       <c r="I24" t="n">
-        <v>3.45</v>
+        <v>110</v>
       </c>
       <c r="J24" t="n">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="K24" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L24" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="O24" t="n">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="P24" t="n">
-        <v>1.74</v>
+        <v>1.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.12</v>
+        <v>1.07</v>
       </c>
       <c r="R24" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.85</v>
+        <v>1.07</v>
       </c>
       <c r="T24" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR24" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV24" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW24" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AX24" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY24" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BA24" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB24" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BC24" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD24" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF24" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BN24" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP24" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BR24" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT24" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV24" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA24" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,251 +6685,251 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Cobreloa Calama</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="G25" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="H25" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="I25" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="J25" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="K25" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="L25" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="M25" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="P25" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="T25" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="W25" t="n">
-        <v>2.14</v>
+        <v>1.52</v>
       </c>
       <c r="X25" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y25" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF25" t="n">
         <v>21</v>
       </c>
-      <c r="Z25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>13</v>
-      </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
         <v>55</v>
       </c>
       <c r="AJ25" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="AK25" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="AL25" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AM25" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AN25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ25" t="n">
         <v>10</v>
       </c>
-      <c r="AO25" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU25" t="n">
+      <c r="BK25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>38</v>
+      </c>
+      <c r="BY25" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AV25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>32</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>21</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>13</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>17</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BV25" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW25" t="n">
-        <v>23</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>40</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>27</v>
-      </c>
       <c r="BZ25" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CA25" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,251 +6939,251 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Deportes Copiapo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="G26" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="H26" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="I26" t="n">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
       <c r="J26" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="K26" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L26" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="M26" t="n">
         <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="T26" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="U26" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="X26" t="n">
         <v>21</v>
       </c>
       <c r="Y26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK26" t="n">
         <v>25</v>
       </c>
-      <c r="Z26" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="AL26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF26" t="n">
         <v>11</v>
       </c>
-      <c r="AC26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ26" t="n">
+      <c r="BG26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP26" t="n">
         <v>15.5</v>
       </c>
-      <c r="AR26" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU26" t="n">
+      <c r="BQ26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT26" t="n">
         <v>7.2</v>
       </c>
-      <c r="AV26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI26" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BJ26" t="n">
-        <v>15</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BN26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO26" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BP26" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BR26" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BT26" t="n">
-        <v>13</v>
-      </c>
       <c r="BU26" t="n">
-        <v>1.63</v>
+        <v>5.4</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.82</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.82</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ26" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7193,126 +7193,126 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.6</v>
+        <v>1.03</v>
       </c>
       <c r="G27" t="n">
-        <v>1.69</v>
+        <v>110</v>
       </c>
       <c r="H27" t="n">
-        <v>5.7</v>
+        <v>1.02</v>
       </c>
       <c r="I27" t="n">
-        <v>7.2</v>
+        <v>110</v>
       </c>
       <c r="J27" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>950</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>1.25</v>
       </c>
       <c r="O27" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="P27" t="n">
-        <v>2.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="S27" t="n">
-        <v>2.96</v>
+        <v>1.38</v>
       </c>
       <c r="T27" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="U27" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
         <v>1.03</v>
@@ -7327,10 +7327,10 @@
         <v>1.03</v>
       </c>
       <c r="AT27" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV27" t="n">
         <v>1.03</v>
@@ -7339,10 +7339,10 @@
         <v>1.03</v>
       </c>
       <c r="AX27" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AY27" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ27" t="n">
         <v>1.03</v>
@@ -7363,81 +7363,81 @@
         <v>1.03</v>
       </c>
       <c r="BF27" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27" t="n">
         <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BN27" t="n">
         <v>1000</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BP27" t="n">
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BT27" t="n">
         <v>1000</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27" t="n">
         <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7447,251 +7447,251 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FC Supra du Quebec</t>
+          <t>Torque</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.53</v>
+        <v>2.42</v>
       </c>
       <c r="G28" t="n">
-        <v>1.7</v>
+        <v>2.84</v>
       </c>
       <c r="H28" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>7.4</v>
+        <v>3.65</v>
       </c>
       <c r="J28" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="K28" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="M28" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>4.7</v>
+        <v>3.15</v>
       </c>
       <c r="O28" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="P28" t="n">
-        <v>2.26</v>
+        <v>1.74</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.61</v>
+        <v>2.12</v>
       </c>
       <c r="R28" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>2.54</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="U28" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="W28" t="n">
-        <v>2.44</v>
+        <v>1.56</v>
       </c>
       <c r="X28" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="Y28" t="n">
-        <v>28</v>
+        <v>13.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AA28" t="n">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="AB28" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AF28" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AH28" t="n">
         <v>23</v>
       </c>
       <c r="AI28" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ28" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR28" t="n">
         <v>18</v>
       </c>
-      <c r="AK28" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AS28" t="n">
-        <v>1.03</v>
+        <v>40</v>
       </c>
       <c r="AT28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU28" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX28" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AY28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>29</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ28" t="n">
         <v>8</v>
       </c>
-      <c r="AZ28" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>55</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ28" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BR28" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BS28" t="n">
-        <v>16.5</v>
+        <v>9.6</v>
       </c>
       <c r="BT28" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="BU28" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="BV28" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX28" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ28" t="n">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="CA28" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7701,251 +7701,251 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CSD Rangers</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Club Deportes Santa Cruz</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="G29" t="n">
-        <v>2.74</v>
+        <v>1.88</v>
       </c>
       <c r="H29" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="J29" t="n">
-        <v>2.94</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M29" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="O29" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="P29" t="n">
-        <v>1.72</v>
+        <v>2.34</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="R29" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="S29" t="n">
-        <v>1.81</v>
+        <v>2.8</v>
       </c>
       <c r="T29" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="V29" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W29" t="n">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y29" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD29" t="n">
         <v>19</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AE29" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV29" t="n">
         <v>36</v>
       </c>
-      <c r="AA29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI29" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BJ29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK29" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BL29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM29" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BN29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BO29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BP29" t="n">
-        <v>25</v>
-      </c>
-      <c r="BQ29" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BR29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BT29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BU29" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BV29" t="n">
-        <v>1000</v>
-      </c>
       <c r="BW29" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="BX29" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY29" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="CA29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7955,111 +7955,111 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Nacional (Uru)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportes Recoleta</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F30" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G30" t="n">
         <v>1.74</v>
       </c>
-      <c r="G30" t="n">
-        <v>1.92</v>
-      </c>
       <c r="H30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K30" t="n">
         <v>4.5</v>
       </c>
-      <c r="I30" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K30" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M30" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P30" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T30" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V30" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Y30" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="Z30" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB30" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC30" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF30" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AG30" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI30" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ30" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK30" t="n">
         <v>22</v>
@@ -8068,131 +8068,1147 @@
         <v>42</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:26:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Cavalry</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>HFX Wanderers</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X31" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:26:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>FC Supra du Quebec</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X32" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="CA32" t="n">
+        <v>11</v>
+      </c>
+      <c r="CB32" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:26:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CSD Rangers</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Club Deportes Santa Cruz</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X33" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB33" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:26:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Deportes Recoleta</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X34" t="n">
         <v>970</v>
       </c>
-      <c r="AO30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI30" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BJ30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK30" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM30" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BN30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO30" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BP30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ30" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BR30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS30" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BT30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU30" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BV30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW30" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BX30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY30" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BZ30" t="n">
+      <c r="Y34" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BZ34" t="n">
         <v>0</v>
       </c>
-      <c r="CA30" t="n">
+      <c r="CA34" t="n">
         <v>0</v>
       </c>
-      <c r="CB30" t="inlineStr">
-        <is>
-          <t>2026-06-05 05:15:24</t>
+      <c r="CB34" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -860,7 +860,7 @@
         <v>2.46</v>
       </c>
       <c r="G2" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H2" t="n">
         <v>2.92</v>
@@ -869,13 +869,13 @@
         <v>3.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
         <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -884,7 +884,7 @@
         <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
         <v>1.84</v>
@@ -905,7 +905,7 @@
         <v>2.06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W2" t="n">
         <v>1.57</v>
@@ -947,7 +947,7 @@
         <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK2" t="n">
         <v>34</v>
@@ -974,7 +974,7 @@
         <v>16</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AT2" t="n">
         <v>8</v>
@@ -986,7 +986,7 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -1001,19 +1001,19 @@
         <v>4.6</v>
       </c>
       <c r="BB2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD2" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BE2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF2" t="n">
-        <v>18</v>
+        <v>4.2</v>
       </c>
       <c r="BG2" t="n">
         <v>4.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         <v>4.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
         <v>3.7</v>
@@ -1135,34 +1135,34 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
         <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="R3" t="n">
         <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T3" t="n">
         <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="W3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X3" t="n">
         <v>15.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>1.58</v>
       </c>
       <c r="G4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H4" t="n">
         <v>4.4</v>
@@ -1377,7 +1377,7 @@
         <v>7.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1404,7 +1404,7 @@
         <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="T4" t="n">
         <v>1.67</v>
@@ -1416,7 +1416,7 @@
         <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X4" t="n">
         <v>28</v>
@@ -1485,10 +1485,10 @@
         <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AV4" t="n">
         <v>3.7</v>
@@ -1503,16 +1503,16 @@
         <v>3.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BA4" t="n">
         <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BD4" t="n">
         <v>3.85</v>
@@ -1521,7 +1521,7 @@
         <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BG4" t="n">
         <v>4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>1.41</v>
       </c>
       <c r="G5" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="H5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I5" t="n">
         <v>9.6</v>
@@ -1634,7 +1634,7 @@
         <v>1.09</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L5" t="n">
         <v>1.24</v>
@@ -1655,28 +1655,28 @@
         <v>1.51</v>
       </c>
       <c r="R5" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="U5" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
         <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="X5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y5" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Z5" t="n">
         <v>80</v>
@@ -1691,7 +1691,7 @@
         <v>14.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE5" t="n">
         <v>120</v>
@@ -1709,13 +1709,13 @@
         <v>95</v>
       </c>
       <c r="AJ5" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AL5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM5" t="n">
         <v>120</v>
@@ -1724,61 +1724,61 @@
         <v>6.8</v>
       </c>
       <c r="AO5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP5" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AQ5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR5" t="n">
         <v>4.1</v>
       </c>
-      <c r="AR5" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AS5" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AV5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW5" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW5" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AX5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BC5" t="n">
         <v>3.45</v>
       </c>
-      <c r="AY5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BD5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE5" t="n">
         <v>4.1</v>
       </c>
-      <c r="BE5" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BF5" t="n">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BH5" t="n">
         <v>4.8</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>1.86</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I6" t="n">
         <v>5.7</v>
@@ -1897,13 +1897,13 @@
         <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
         <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q6" t="n">
         <v>1.66</v>
@@ -1966,73 +1966,73 @@
         <v>22</v>
       </c>
       <c r="AK6" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AL6" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AM6" t="n">
         <v>80</v>
       </c>
       <c r="AN6" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AO6" t="n">
         <v>46</v>
       </c>
       <c r="AP6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW6" t="n">
         <v>4.7</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AX6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BG6" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>5</v>
       </c>
       <c r="BH6" t="n">
         <v>4.7</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -2127,37 +2127,37 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G7" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H7" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J7" t="n">
         <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.02</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
         <v>1.73</v>
@@ -2166,127 +2166,127 @@
         <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
         <v>1.53</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BH7" t="n">
         <v>11.5</v>
@@ -2298,31 +2298,31 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
@@ -2340,17 +2340,17 @@
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G8" t="n">
         <v>2.78</v>
@@ -2390,19 +2390,19 @@
         <v>2.62</v>
       </c>
       <c r="I8" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="J8" t="n">
         <v>3.05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
         <v>1.28</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
         <v>4.2</v>
@@ -2411,25 +2411,25 @@
         <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q8" t="n">
         <v>1.58</v>
       </c>
       <c r="R8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S8" t="n">
         <v>2.42</v>
       </c>
       <c r="T8" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="U8" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="V8" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W8" t="n">
         <v>1.56</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G9" t="n">
         <v>1.47</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I9" t="n">
         <v>10.5</v>
@@ -2659,19 +2659,19 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>5.5</v>
+        <v>1.02</v>
       </c>
       <c r="O9" t="n">
         <v>1.13</v>
       </c>
       <c r="P9" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="R9" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="S9" t="n">
         <v>2.04</v>
@@ -2680,7 +2680,7 @@
         <v>1.65</v>
       </c>
       <c r="U9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V9" t="n">
         <v>1.1</v>
@@ -2695,7 +2695,7 @@
         <v>48</v>
       </c>
       <c r="Z9" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
@@ -2743,106 +2743,106 @@
         <v>95</v>
       </c>
       <c r="AP9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS9" t="n">
         <v>5.3</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AT9" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AV9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA9" t="n">
         <v>5.1</v>
       </c>
-      <c r="AW9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BB9" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BD9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE9" t="n">
         <v>5.1</v>
       </c>
-      <c r="BE9" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BF9" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH9" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.42</v>
+        <v>1.56</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.7</v>
+        <v>9.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>5.9</v>
+        <v>2.96</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.1</v>
+        <v>1.55</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
@@ -2854,11 +2854,11 @@
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G10" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I10" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>5.2</v>
@@ -2928,19 +2928,19 @@
         <v>1.77</v>
       </c>
       <c r="S10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U10" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V10" t="n">
         <v>1.12</v>
       </c>
       <c r="W10" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="X10" t="n">
         <v>40</v>
@@ -2949,10 +2949,10 @@
         <v>44</v>
       </c>
       <c r="Z10" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AA10" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AB10" t="n">
         <v>970</v>
@@ -2961,10 +2961,10 @@
         <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE10" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF10" t="n">
         <v>970</v>
@@ -2976,37 +2976,37 @@
         <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK10" t="n">
         <v>970</v>
       </c>
       <c r="AL10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM10" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AO10" t="n">
         <v>90</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>85</v>
       </c>
       <c r="AP10" t="n">
         <v>4.7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -3018,37 +3018,37 @@
         <v>4.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY10" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
         <v>5</v>
       </c>
       <c r="BB10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC10" t="n">
         <v>10.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH10" t="n">
         <v>5.1</v>
@@ -3060,59 +3060,59 @@
         <v>10</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BN10" t="n">
         <v>4.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP10" t="n">
         <v>8.4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT10" t="n">
         <v>11.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>11</v>
+        <v>4.8</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>970</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
         <v>1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T11" t="n">
         <v>2.16</v>
@@ -3209,13 +3209,13 @@
         <v>30</v>
       </c>
       <c r="AB11" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
         <v>8.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
         <v>32</v>
@@ -3314,31 +3314,31 @@
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BO11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
         <v>4.6</v>
@@ -3350,23 +3350,23 @@
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -3397,175 +3397,175 @@
         </is>
       </c>
       <c r="F12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M12" t="n">
         <v>1.04</v>
       </c>
-      <c r="G12" t="n">
+      <c r="N12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X12" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>110</v>
       </c>
-      <c r="H12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I12" t="n">
-        <v>110</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K12" t="n">
-        <v>950</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1000</v>
-      </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI12" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK12" t="n">
         <v>1.01</v>
@@ -3577,7 +3577,7 @@
         <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BO12" t="n">
         <v>1.01</v>
@@ -3595,32 +3595,32 @@
         <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU12" t="n">
         <v>1.01</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BW12" t="n">
         <v>1.01</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY12" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA12" t="n">
         <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -3651,175 +3651,175 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="G13" t="n">
-        <v>970</v>
+        <v>2.06</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X13" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM13" t="n">
         <v>110</v>
       </c>
-      <c r="J13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K13" t="n">
-        <v>950</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="AN13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP13" t="n">
         <v>4</v>
       </c>
-      <c r="O13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI13" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK13" t="n">
         <v>1.01</v>
@@ -3831,31 +3831,31 @@
         <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO13" t="n">
         <v>1.01</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ13" t="n">
         <v>1.01</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS13" t="n">
         <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU13" t="n">
         <v>1.01</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -4667,16 +4667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="G17" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J17" t="n">
         <v>4.1</v>
@@ -4691,49 +4691,49 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="O17" t="n">
         <v>1.15</v>
       </c>
       <c r="P17" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="S17" t="n">
         <v>2.08</v>
       </c>
       <c r="T17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="U17" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="V17" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W17" t="n">
         <v>1.6</v>
       </c>
       <c r="X17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y17" t="n">
         <v>25</v>
       </c>
       <c r="Z17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA17" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC17" t="n">
         <v>13.5</v>
@@ -4742,10 +4742,10 @@
         <v>16.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG17" t="n">
         <v>16</v>
@@ -4754,10 +4754,10 @@
         <v>17.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK17" t="n">
         <v>28</v>
@@ -4772,10 +4772,10 @@
         <v>13.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AQ17" t="n">
         <v>14.5</v>
@@ -4787,31 +4787,31 @@
         <v>3.95</v>
       </c>
       <c r="AT17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW17" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
         <v>10.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BC17" t="n">
         <v>16.5</v>
@@ -4820,13 +4820,13 @@
         <v>19</v>
       </c>
       <c r="BE17" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BF17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
         <v>1.67</v>
       </c>
       <c r="U18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V18" t="n">
         <v>1.25</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -5175,19 +5175,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G19" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="H19" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="I19" t="n">
         <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
         <v>3.95</v>
@@ -5214,7 +5214,7 @@
         <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T19" t="n">
         <v>2.02</v>
@@ -5241,10 +5241,10 @@
         <v>240</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
         <v>30</v>
@@ -5253,7 +5253,7 @@
         <v>130</v>
       </c>
       <c r="AF19" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG19" t="n">
         <v>12.5</v>
@@ -5265,10 +5265,10 @@
         <v>130</v>
       </c>
       <c r="AJ19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>60</v>
@@ -5277,64 +5277,64 @@
         <v>200</v>
       </c>
       <c r="AN19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO19" t="n">
         <v>200</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.4</v>
+        <v>3.85</v>
       </c>
       <c r="AQ19" t="n">
         <v>12.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT19" t="n">
         <v>5.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="AV19" t="n">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="AW19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB19" t="n">
         <v>4.2</v>
       </c>
-      <c r="AX19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>13</v>
-      </c>
       <c r="BC19" t="n">
-        <v>15</v>
+        <v>4.3</v>
       </c>
       <c r="BD19" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BF19" t="n">
         <v>10</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BH19" t="n">
         <v>3.15</v>
@@ -5352,28 +5352,28 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>3.9</v>
+        <v>2.12</v>
       </c>
       <c r="BN19" t="n">
         <v>4.1</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU19" t="n">
         <v>6</v>
@@ -5382,23 +5382,23 @@
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5453,7 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O20" t="n">
         <v>1.07</v>
@@ -5468,7 +5468,7 @@
         <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5707,7 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O21" t="n">
         <v>1.1</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -5958,16 +5958,16 @@
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O22" t="n">
         <v>1.35</v>
       </c>
       <c r="P22" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q22" t="n">
         <v>1.92</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -6699,16 +6699,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="G25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H25" t="n">
         <v>2.9</v>
       </c>
-      <c r="H25" t="n">
-        <v>2.7</v>
-      </c>
       <c r="I25" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>3.35</v>
@@ -6735,52 +6735,52 @@
         <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
         <v>3.55</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V25" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="X25" t="n">
         <v>15.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA25" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC25" t="n">
         <v>9</v>
       </c>
       <c r="AD25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE25" t="n">
         <v>40</v>
       </c>
       <c r="AF25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG25" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH25" t="n">
         <v>21</v>
@@ -6789,76 +6789,76 @@
         <v>55</v>
       </c>
       <c r="AJ25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL25" t="n">
         <v>50</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>55</v>
       </c>
       <c r="AM25" t="n">
         <v>120</v>
       </c>
       <c r="AN25" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AO25" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP25" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX25" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AY25" t="n">
-        <v>3.7</v>
+        <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>4</v>
+        <v>13.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH25" t="n">
         <v>3.4</v>
@@ -6870,7 +6870,7 @@
         <v>10</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
@@ -6879,16 +6879,16 @@
         <v>9.6</v>
       </c>
       <c r="BN25" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BO25" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BP25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ25" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR25" t="n">
         <v>36</v>
@@ -6897,19 +6897,19 @@
         <v>8</v>
       </c>
       <c r="BT25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU25" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BV25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BW25" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX25" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY25" t="n">
         <v>8.199999999999999</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -6953,58 +6953,58 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="G26" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="H26" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J26" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M26" t="n">
         <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S26" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="T26" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U26" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V26" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W26" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="X26" t="n">
         <v>21</v>
@@ -7019,7 +7019,7 @@
         <v>75</v>
       </c>
       <c r="AB26" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC26" t="n">
         <v>10.5</v>
@@ -7031,10 +7031,10 @@
         <v>44</v>
       </c>
       <c r="AF26" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AG26" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH26" t="n">
         <v>19</v>
@@ -7043,22 +7043,22 @@
         <v>50</v>
       </c>
       <c r="AJ26" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AK26" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM26" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AN26" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AO26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP26" t="n">
         <v>14</v>
@@ -7070,19 +7070,19 @@
         <v>20</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT26" t="n">
         <v>9</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV26" t="n">
         <v>11.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX26" t="n">
         <v>11.5</v>
@@ -7094,7 +7094,7 @@
         <v>12.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB26" t="n">
         <v>20</v>
@@ -7103,43 +7103,43 @@
         <v>16.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF26" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BH26" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="BJ26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK26" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN26" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BO26" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP26" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ26" t="n">
         <v>6.6</v>
@@ -7148,25 +7148,25 @@
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT26" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BU26" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -7231,13 +7231,13 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O27" t="n">
         <v>1.38</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q27" t="n">
         <v>1.38</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -7464,13 +7464,13 @@
         <v>2.42</v>
       </c>
       <c r="G28" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="H28" t="n">
         <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="J28" t="n">
         <v>3.2</v>
@@ -7500,7 +7500,7 @@
         <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="T28" t="n">
         <v>1.86</v>
@@ -7509,10 +7509,10 @@
         <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W28" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X28" t="n">
         <v>15</v>
@@ -7521,7 +7521,7 @@
         <v>13.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA28" t="n">
         <v>70</v>
@@ -7530,7 +7530,7 @@
         <v>11.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD28" t="n">
         <v>17.5</v>
@@ -7539,7 +7539,7 @@
         <v>50</v>
       </c>
       <c r="AF28" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AG28" t="n">
         <v>15</v>
@@ -7578,7 +7578,7 @@
         <v>18</v>
       </c>
       <c r="AS28" t="n">
-        <v>40</v>
+        <v>4.4</v>
       </c>
       <c r="AT28" t="n">
         <v>8.199999999999999</v>
@@ -7587,10 +7587,10 @@
         <v>6.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AX28" t="n">
         <v>13.5</v>
@@ -7602,25 +7602,25 @@
         <v>16</v>
       </c>
       <c r="BA28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF28" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB28" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE28" t="n">
+      <c r="BG28" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>29</v>
       </c>
       <c r="BH28" t="n">
         <v>3.25</v>
@@ -7644,7 +7644,7 @@
         <v>5.5</v>
       </c>
       <c r="BO28" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BP28" t="n">
         <v>20</v>
@@ -7662,7 +7662,7 @@
         <v>6.4</v>
       </c>
       <c r="BU28" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BV28" t="n">
         <v>26</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -7724,13 +7724,13 @@
         <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J29" t="n">
         <v>4</v>
       </c>
       <c r="K29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L29" t="n">
         <v>1.29</v>
@@ -7880,16 +7880,16 @@
         <v>4.1</v>
       </c>
       <c r="BI29" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BJ29" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL29" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM29" t="n">
         <v>1.01</v>
@@ -7898,7 +7898,7 @@
         <v>4.9</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP29" t="n">
         <v>13</v>
@@ -7916,7 +7916,7 @@
         <v>8.4</v>
       </c>
       <c r="BU29" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV29" t="n">
         <v>36</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -7969,52 +7969,52 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="G30" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="H30" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I30" t="n">
         <v>7.2</v>
       </c>
       <c r="J30" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="K30" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L30" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M30" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="P30" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="T30" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="U30" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="V30" t="n">
         <v>1.01</v>
@@ -8023,7 +8023,7 @@
         <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Y30" t="n">
         <v>25</v>
@@ -8032,7 +8032,7 @@
         <v>60</v>
       </c>
       <c r="AA30" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AB30" t="n">
         <v>11</v>
@@ -8041,10 +8041,10 @@
         <v>11.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE30" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AF30" t="n">
         <v>13</v>
@@ -8053,118 +8053,118 @@
         <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI30" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AJ30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL30" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM30" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AN30" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AP30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AT30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU30" t="n">
         <v>7.8</v>
       </c>
-      <c r="AU30" t="n">
-        <v>7</v>
-      </c>
       <c r="AV30" t="n">
-        <v>16</v>
+        <v>3.3</v>
       </c>
       <c r="AW30" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AX30" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY30" t="n">
         <v>7.4</v>
       </c>
       <c r="AZ30" t="n">
-        <v>15</v>
+        <v>3.3</v>
       </c>
       <c r="BA30" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BB30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP30" t="n">
         <v>12</v>
       </c>
-      <c r="BC30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BI30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK30" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BN30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BO30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP30" t="n">
-        <v>11</v>
-      </c>
       <c r="BQ30" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT30" t="n">
         <v>9.199999999999999</v>
@@ -8182,17 +8182,17 @@
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8235,7 @@
         <v>7.2</v>
       </c>
       <c r="J31" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K31" t="n">
         <v>5</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -8480,13 +8480,13 @@
         <v>1.53</v>
       </c>
       <c r="G32" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H32" t="n">
         <v>5.5</v>
       </c>
       <c r="I32" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J32" t="n">
         <v>4.2</v>
@@ -8519,16 +8519,16 @@
         <v>2.54</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V32" t="n">
         <v>1.17</v>
       </c>
       <c r="W32" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="X32" t="n">
         <v>26</v>
@@ -8579,16 +8579,16 @@
         <v>110</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO32" t="n">
         <v>85</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AR32" t="n">
         <v>1.03</v>
@@ -8597,34 +8597,34 @@
         <v>1.03</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AW32" t="n">
         <v>1.03</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA32" t="n">
         <v>1.03</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BD32" t="n">
         <v>1.03</v>
@@ -8633,10 +8633,10 @@
         <v>1.03</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BH32" t="n">
         <v>4.4</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -8731,37 +8731,37 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="G33" t="n">
-        <v>7.6</v>
+        <v>2.58</v>
       </c>
       <c r="H33" t="n">
-        <v>1.77</v>
+        <v>3.05</v>
       </c>
       <c r="I33" t="n">
-        <v>14.5</v>
+        <v>3.95</v>
       </c>
       <c r="J33" t="n">
         <v>3.25</v>
       </c>
       <c r="K33" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="L33" t="n">
         <v>1.34</v>
       </c>
       <c r="M33" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N33" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="O33" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P33" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Q33" t="n">
         <v>1.81</v>
@@ -8773,178 +8773,178 @@
         <v>3.05</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V33" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="W33" t="n">
-        <v>1.15</v>
+        <v>1.63</v>
       </c>
       <c r="X33" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Y33" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="Z33" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC33" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD33" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF33" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AG33" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AH33" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ33" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AK33" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.69</v>
+        <v>4.3</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.77</v>
+        <v>4.8</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.86</v>
+        <v>5.5</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.86</v>
+        <v>3.85</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.6</v>
+        <v>3.55</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.71</v>
+        <v>4.3</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.86</v>
+        <v>5.3</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.71</v>
+        <v>4.3</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.68</v>
+        <v>4</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.74</v>
+        <v>4.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.86</v>
+        <v>5.4</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.79</v>
+        <v>5</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.78</v>
+        <v>4.9</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.86</v>
+        <v>5.2</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.86</v>
+        <v>5.6</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.86</v>
+        <v>4.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.86</v>
+        <v>5.3</v>
       </c>
       <c r="BH33" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI33" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BJ33" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK33" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BN33" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO33" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP33" t="n">
         <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BT33" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU33" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BV33" t="n">
         <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BZ33" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>
@@ -9003,13 +9003,13 @@
         <v>4.8</v>
       </c>
       <c r="L34" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="M34" t="n">
         <v>1.06</v>
       </c>
       <c r="N34" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O34" t="n">
         <v>1.29</v>
@@ -9150,7 +9150,7 @@
         <v>6.8</v>
       </c>
       <c r="BI34" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ34" t="n">
         <v>1000</v>
@@ -9165,7 +9165,7 @@
         <v>1.05</v>
       </c>
       <c r="BN34" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BO34" t="n">
         <v>3.6</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-05 07:26:36</t>
+          <t>2026-06-05 09:38:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -881,22 +881,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
         <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.32</v>
+        <v>1.84</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.32</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
         <v>1.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R3" t="n">
         <v>1.32</v>
@@ -1153,13 +1153,13 @@
         <v>3.55</v>
       </c>
       <c r="T3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U3" t="n">
         <v>2.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
         <v>1.58</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>1.99</v>
       </c>
       <c r="I4" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J4" t="n">
         <v>3.5</v>
@@ -1389,19 +1389,19 @@
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
         <v>3.7</v>
@@ -1413,7 +1413,7 @@
         <v>2.06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="W4" t="n">
         <v>1.29</v>
@@ -1470,10 +1470,10 @@
         <v>80</v>
       </c>
       <c r="AO4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ4" t="n">
         <v>6.4</v>
@@ -1488,7 +1488,7 @@
         <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV4" t="n">
         <v>8</v>
@@ -1509,10 +1509,10 @@
         <v>4</v>
       </c>
       <c r="BB4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC4" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4</v>
       </c>
       <c r="BD4" t="n">
         <v>4.1</v>
@@ -1530,37 +1530,37 @@
         <v>3.35</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
         <v>7.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP4" t="n">
         <v>38</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR4" t="n">
         <v>50</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT4" t="n">
         <v>4.9</v>
@@ -1569,16 +1569,16 @@
         <v>3.65</v>
       </c>
       <c r="BV4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX4" t="n">
         <v>32</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G5" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="H5" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J5" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="K5" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.59</v>
+        <v>2.68</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q5" t="n">
         <v>2.2</v>
@@ -1658,7 +1658,7 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="W5" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1790,49 +1790,49 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="G6" t="n">
         <v>1.73</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
         <v>7.4</v>
@@ -1888,7 +1888,7 @@
         <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.25</v>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>
@@ -1909,10 +1909,10 @@
         <v>1.59</v>
       </c>
       <c r="R6" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T6" t="n">
         <v>1.67</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>1.41</v>
       </c>
       <c r="G7" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="H7" t="n">
         <v>5.7</v>
@@ -2139,7 +2139,7 @@
         <v>9.6</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="K7" t="n">
         <v>5.9</v>
@@ -2151,7 +2151,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
         <v>1.18</v>
@@ -2178,7 +2178,7 @@
         <v>1.11</v>
       </c>
       <c r="W7" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="X7" t="n">
         <v>32</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -2405,13 +2405,13 @@
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
         <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
         <v>1.66</v>
@@ -2432,7 +2432,7 @@
         <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X8" t="n">
         <v>30</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -2635,55 +2635,55 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G9" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H9" t="n">
         <v>2.7</v>
       </c>
       <c r="I9" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O9" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="U9" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V9" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
         <v>1.54</v>
@@ -2722,7 +2722,7 @@
         <v>970</v>
       </c>
       <c r="AI9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ9" t="n">
         <v>44</v>
@@ -2731,76 +2731,76 @@
         <v>32</v>
       </c>
       <c r="AL9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM9" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT9" t="n">
         <v>3.5</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AR9" t="n">
+      <c r="AU9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX9" t="n">
         <v>3.7</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AY9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA9" t="n">
         <v>4</v>
       </c>
-      <c r="AT9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW9" t="n">
+      <c r="BB9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG9" t="n">
         <v>3.85</v>
       </c>
-      <c r="AX9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BH9" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
@@ -2812,7 +2812,7 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.98</v>
+        <v>1.27</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
@@ -2824,41 +2824,41 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>1.02</v>
       </c>
       <c r="O10" t="n">
         <v>1.24</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
         <v>1.35</v>
       </c>
       <c r="R11" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="S11" t="n">
         <v>2.04</v>
@@ -3236,7 +3236,7 @@
         <v>970</v>
       </c>
       <c r="AK11" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AL11" t="n">
         <v>34</v>
@@ -3245,64 +3245,64 @@
         <v>95</v>
       </c>
       <c r="AN11" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AO11" t="n">
         <v>95</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AS11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD11" t="n">
         <v>4.5</v>
       </c>
-      <c r="AT11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BE11" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3323,16 +3323,16 @@
         <v>1.56</v>
       </c>
       <c r="BN11" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
@@ -3362,18 +3362,18 @@
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,246 +3388,246 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IF Vestri</t>
+          <t>Central Espanol</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>Racing Club (Uru)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="G12" t="n">
-        <v>1.47</v>
+        <v>5.2</v>
       </c>
       <c r="H12" t="n">
-        <v>7.4</v>
+        <v>1.95</v>
       </c>
       <c r="I12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>160</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="J12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>40</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>240</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV12" t="n">
+      <c r="BT12" t="n">
         <v>4.6</v>
       </c>
-      <c r="AW12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX12" t="n">
+      <c r="BU12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BZ12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,244 +3637,244 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Gefle</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing Club (Uru)</t>
+          <t>Hammarby TFF</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
         <v>4.4</v>
       </c>
-      <c r="G13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L13" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>2.68</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.51</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>1.54</v>
+        <v>2.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.54</v>
+        <v>1.7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>5.1</v>
+        <v>2.72</v>
       </c>
       <c r="T13" t="n">
-        <v>2.16</v>
+        <v>1.71</v>
       </c>
       <c r="U13" t="n">
-        <v>1.71</v>
+        <v>2.18</v>
       </c>
       <c r="V13" t="n">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="W13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AC13" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="AF13" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AG13" t="n">
         <v>24</v>
       </c>
       <c r="AH13" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL13" t="n">
         <v>70</v>
       </c>
-      <c r="AJ13" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK13" t="n">
+      <c r="AM13" t="n">
         <v>100</v>
       </c>
-      <c r="AL13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>240</v>
-      </c>
       <c r="AN13" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AO13" t="n">
-        <v>29</v>
+        <v>9.6</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.2</v>
+        <v>15</v>
       </c>
       <c r="AQ13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BW13" t="n">
         <v>5.8</v>
       </c>
-      <c r="AR13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="CA13" t="n">
         <v>7</v>
       </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -3896,31 +3896,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Gefle</t>
+          <t>Jonkopings Sodra</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby TFF</t>
+          <t>FC Trollhattan</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
         <v>4.9</v>
-      </c>
-      <c r="G14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.33</v>
@@ -3929,213 +3929,213 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
         <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
-        <v>2.28</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>1.22</v>
+        <v>2.38</v>
       </c>
       <c r="X14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y14" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG14" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AH14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR14" t="n">
         <v>25</v>
       </c>
-      <c r="AC14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>140</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA14" t="n">
+      <c r="BS14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU14" t="n">
         <v>5</v>
       </c>
-      <c r="BB14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BV14" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ14" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,229 +4150,229 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Jonkopings Sodra</t>
+          <t>KA Asvellir</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FC Trollhattan</t>
+          <t>Vidir Gardur</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.57</v>
+        <v>3.05</v>
       </c>
       <c r="G15" t="n">
-        <v>1.75</v>
+        <v>4.2</v>
       </c>
       <c r="H15" t="n">
-        <v>5.5</v>
+        <v>1.82</v>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>2.24</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.71</v>
+        <v>1.35</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.97</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>1.87</v>
       </c>
       <c r="T15" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="U15" t="n">
-        <v>2.02</v>
+        <v>2.84</v>
       </c>
       <c r="V15" t="n">
-        <v>1.16</v>
+        <v>1.81</v>
       </c>
       <c r="W15" t="n">
-        <v>2.34</v>
+        <v>1.31</v>
       </c>
       <c r="X15" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y15" t="n">
         <v>22</v>
       </c>
-      <c r="Y15" t="n">
-        <v>26</v>
-      </c>
       <c r="Z15" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AA15" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI15" t="n">
         <v>27</v>
       </c>
-      <c r="AE15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>85</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="AK15" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="AL15" t="n">
         <v>38</v>
       </c>
       <c r="AM15" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AN15" t="n">
-        <v>9.4</v>
+        <v>22</v>
       </c>
       <c r="AO15" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="AP15" t="n">
-        <v>14.5</v>
+        <v>4.1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>3.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>36</v>
+        <v>3.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.8</v>
+        <v>3.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>18</v>
+        <v>3.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.4</v>
+        <v>4.1</v>
       </c>
       <c r="AY15" t="n">
-        <v>8</v>
+        <v>3.75</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16</v>
+        <v>3.65</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="BB15" t="n">
-        <v>12.5</v>
+        <v>4.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>13</v>
+        <v>4.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>24</v>
+        <v>4.1</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.5</v>
+        <v>2.92</v>
       </c>
       <c r="BH15" t="n">
-        <v>4</v>
+        <v>970</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="BJ15" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
         <v>5.1</v>
       </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>11</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,169 +4404,169 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FC Arbaer</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sindri</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.52</v>
+        <v>2.02</v>
       </c>
       <c r="G16" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="R16" t="n">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="S16" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
         <v>1.01</v>
@@ -4575,75 +4575,75 @@
         <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BR16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,169 +4658,169 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fjolnir</t>
+          <t>FC Arbaer</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>Sindri</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="G17" t="n">
-        <v>2.66</v>
+        <v>2.18</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="I17" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>1.09</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>4.9</v>
+        <v>950</v>
       </c>
       <c r="L17" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="P17" t="n">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.36</v>
+        <v>1.06</v>
       </c>
       <c r="R17" t="n">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="T17" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="X17" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
         <v>1.01</v>
@@ -4829,13 +4829,13 @@
         <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
         <v>1.01</v>
@@ -4847,25 +4847,25 @@
         <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
         <v>1.01</v>
       </c>
       <c r="BP17" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
         <v>1.01</v>
       </c>
       <c r="BR17" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
         <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
         <v>1.01</v>
@@ -4883,21 +4883,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
         <v>1.01</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,178 +4912,178 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KA Asvellir</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vidir Gardur</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="G18" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="H18" t="n">
-        <v>1.83</v>
+        <v>2.56</v>
       </c>
       <c r="I18" t="n">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P18" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="R18" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="S18" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="T18" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="U18" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="W18" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="X18" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>44</v>
       </c>
-      <c r="Y18" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="AK18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL18" t="n">
         <v>32</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AM18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>14.5</v>
       </c>
-      <c r="AD18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BH18" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
         <v>1.01</v>
@@ -5137,14 +5137,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -5166,246 +5166,246 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="H19" t="n">
-        <v>2.56</v>
+        <v>3.4</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>3.85</v>
       </c>
       <c r="J19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K19" t="n">
         <v>4.1</v>
       </c>
-      <c r="K19" t="n">
-        <v>4.6</v>
-      </c>
       <c r="L19" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="M19" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.92</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="R19" t="n">
-        <v>1.79</v>
+        <v>1.46</v>
       </c>
       <c r="S19" t="n">
-        <v>2.08</v>
+        <v>2.72</v>
       </c>
       <c r="T19" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>2.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="W19" t="n">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="X19" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="Y19" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="Z19" t="n">
         <v>30</v>
       </c>
       <c r="AA19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI19" t="n">
         <v>48</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AJ19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK19" t="n">
         <v>24</v>
       </c>
-      <c r="AC19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>28</v>
-      </c>
       <c r="AL19" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AM19" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AN19" t="n">
         <v>13.5</v>
       </c>
       <c r="AO19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP19" t="n">
         <v>15</v>
       </c>
-      <c r="AP19" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AQ19" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>17.5</v>
+        <v>5</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="AT19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP19" t="n">
         <v>14</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BQ19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AV19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD19" t="n">
+      <c r="BZ19" t="n">
         <v>19</v>
       </c>
-      <c r="BE19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>9</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA19" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5420,246 +5420,246 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="G20" t="n">
-        <v>2.22</v>
+        <v>1.76</v>
       </c>
       <c r="H20" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="I20" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>220</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>3.95</v>
       </c>
-      <c r="J20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="X20" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="AR20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV20" t="n">
         <v>19</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>11.5</v>
       </c>
       <c r="AW20" t="n">
         <v>4.6</v>
       </c>
       <c r="AX20" t="n">
-        <v>11</v>
+        <v>3.2</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.6</v>
+        <v>3.45</v>
       </c>
       <c r="AZ20" t="n">
-        <v>12.5</v>
+        <v>4.1</v>
       </c>
       <c r="BA20" t="n">
         <v>4.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="BC20" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BN20" t="n">
         <v>4.1</v>
       </c>
-      <c r="BI20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BO20" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="BP20" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BR20" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BT20" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BV20" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.6</v>
+        <v>1.71</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>8</v>
+        <v>1.72</v>
       </c>
       <c r="BZ20" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,246 +5674,246 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>KFA Austfjarda</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>KFG</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="G21" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="H21" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="K21" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="O21" t="n">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="P21" t="n">
-        <v>1.72</v>
+        <v>3.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.18</v>
+        <v>1.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>2.26</v>
       </c>
       <c r="S21" t="n">
-        <v>4.1</v>
+        <v>1.56</v>
       </c>
       <c r="T21" t="n">
-        <v>2.04</v>
+        <v>1.33</v>
       </c>
       <c r="U21" t="n">
-        <v>1.76</v>
+        <v>3.3</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="X21" t="n">
-        <v>13.5</v>
+        <v>85</v>
       </c>
       <c r="Y21" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="Z21" t="n">
         <v>70</v>
       </c>
       <c r="AA21" t="n">
-        <v>270</v>
+        <v>120</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="AC21" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AD21" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AE21" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="AF21" t="n">
-        <v>9.6</v>
+        <v>26</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>15</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV21" t="n">
         <v>29</v>
       </c>
-      <c r="AI21" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK21" t="n">
+      <c r="BW21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX21" t="n">
         <v>25</v>
       </c>
-      <c r="AL21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>230</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY21" t="n">
-        <v>2.08</v>
+        <v>7</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA21" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,244 +5923,244 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KFA Austfjarda</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KFG</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="G22" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="H22" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="I22" t="n">
-        <v>5.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP22" t="n">
         <v>4.6</v>
       </c>
-      <c r="K22" t="n">
+      <c r="AQ22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BU22" t="n">
         <v>6.2</v>
       </c>
-      <c r="L22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X22" t="n">
-        <v>85</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP22" t="n">
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
         <v>10.5</v>
       </c>
-      <c r="BQ22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>15</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>29</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>25</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -6191,46 +6191,46 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>110</v>
+        <v>3.5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.02</v>
+        <v>1.92</v>
       </c>
       <c r="I23" t="n">
-        <v>110</v>
+        <v>2.12</v>
       </c>
       <c r="J23" t="n">
-        <v>1.02</v>
+        <v>4.7</v>
       </c>
       <c r="K23" t="n">
-        <v>950</v>
+        <v>5.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M23" t="n">
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P23" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="R23" t="n">
-        <v>1.24</v>
+        <v>1.84</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -6239,118 +6239,118 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -6448,16 +6448,16 @@
         <v>1.03</v>
       </c>
       <c r="G24" t="n">
-        <v>110</v>
+        <v>1.65</v>
       </c>
       <c r="H24" t="n">
-        <v>1.02</v>
+        <v>2.6</v>
       </c>
       <c r="I24" t="n">
-        <v>420</v>
+        <v>140</v>
       </c>
       <c r="J24" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="K24" t="n">
         <v>950</v>
@@ -6466,25 +6466,25 @@
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>1.31</v>
+        <v>2.68</v>
       </c>
       <c r="O24" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P24" t="n">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="R24" t="n">
         <v>1.12</v>
       </c>
       <c r="S24" t="n">
-        <v>2.88</v>
+        <v>2.08</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -6496,7 +6496,7 @@
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -6699,19 +6699,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.02</v>
+        <v>2.2</v>
       </c>
       <c r="G25" t="n">
-        <v>110</v>
+        <v>2.7</v>
       </c>
       <c r="H25" t="n">
-        <v>1.02</v>
+        <v>1.61</v>
       </c>
       <c r="I25" t="n">
-        <v>110</v>
+        <v>3.45</v>
       </c>
       <c r="J25" t="n">
-        <v>1.02</v>
+        <v>2.94</v>
       </c>
       <c r="K25" t="n">
         <v>950</v>
@@ -6723,22 +6723,22 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.05</v>
+        <v>2.78</v>
       </c>
       <c r="O25" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="S25" t="n">
-        <v>1.15</v>
+        <v>2.26</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.02</v>
+        <v>2.18</v>
       </c>
       <c r="G26" t="n">
-        <v>110</v>
+        <v>2.86</v>
       </c>
       <c r="H26" t="n">
-        <v>1.02</v>
+        <v>2.46</v>
       </c>
       <c r="I26" t="n">
-        <v>110</v>
+        <v>3.05</v>
       </c>
       <c r="J26" t="n">
-        <v>1.02</v>
+        <v>3.1</v>
       </c>
       <c r="K26" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6977,22 +6977,22 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="P26" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
         <v>1.07</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="S26" t="n">
-        <v>1.07</v>
+        <v>1.66</v>
       </c>
       <c r="T26" t="n">
         <v>1.01</v>
@@ -7001,10 +7001,10 @@
         <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -7198,229 +7198,229 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Deportes Copiapo</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa Calama</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="G27" t="n">
-        <v>2.28</v>
+        <v>2.72</v>
       </c>
       <c r="H27" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="I27" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="J27" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="K27" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="L27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O27" t="n">
         <v>1.34</v>
       </c>
-      <c r="M27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.26</v>
-      </c>
       <c r="P27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U27" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.22</v>
-      </c>
       <c r="V27" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="W27" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="X27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH27" t="n">
         <v>21</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>19.5</v>
       </c>
       <c r="AI27" t="n">
         <v>55</v>
       </c>
       <c r="AJ27" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AK27" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AL27" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AM27" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AN27" t="n">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="AO27" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP27" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AR27" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT27" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX27" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AY27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
         <v>13</v>
       </c>
       <c r="BA27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB27" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB27" t="n">
-        <v>19</v>
-      </c>
       <c r="BC27" t="n">
-        <v>16</v>
+        <v>4.6</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE27" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="BG27" t="n">
         <v>4.7</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="BJ27" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BK27" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN27" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BO27" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BP27" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BQ27" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR27" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BS27" t="n">
         <v>7.8</v>
       </c>
       <c r="BT27" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BU27" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV27" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW27" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BX27" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY27" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BZ27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -7452,229 +7452,229 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Deportes Copiapo</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cobreloa Calama</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="G28" t="n">
-        <v>2.68</v>
+        <v>2.28</v>
       </c>
       <c r="H28" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="I28" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="J28" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K28" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="P28" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>3.55</v>
+        <v>2.96</v>
       </c>
       <c r="T28" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="U28" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="V28" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="W28" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="X28" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="Y28" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK28" t="n">
         <v>25</v>
       </c>
-      <c r="AA28" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>34</v>
-      </c>
       <c r="AL28" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AM28" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AN28" t="n">
-        <v>28</v>
+        <v>14.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP28" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AR28" t="n">
-        <v>16</v>
+        <v>4.7</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT28" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AX28" t="n">
         <v>12.5</v>
       </c>
       <c r="AY28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY28" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR28" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS28" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU28" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV28" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX28" t="n">
-        <v>40</v>
-      </c>
-      <c r="BY28" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -7739,13 +7739,13 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="O29" t="n">
         <v>1.38</v>
       </c>
       <c r="P29" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q29" t="n">
         <v>1.38</v>
@@ -7754,7 +7754,7 @@
         <v>1.12</v>
       </c>
       <c r="S29" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T29" t="n">
         <v>1.01</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -7978,10 +7978,10 @@
         <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="J30" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K30" t="n">
         <v>3.6</v>
@@ -8038,7 +8038,7 @@
         <v>11.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AD30" t="n">
         <v>17.5</v>
@@ -8086,10 +8086,10 @@
         <v>15</v>
       </c>
       <c r="AS30" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="AT30" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU30" t="n">
         <v>5.6</v>
@@ -8098,7 +8098,7 @@
         <v>10.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AX30" t="n">
         <v>11.5</v>
@@ -8110,31 +8110,31 @@
         <v>16</v>
       </c>
       <c r="BA30" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BB30" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BC30" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BD30" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BF30" t="n">
         <v>19.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BH30" t="n">
         <v>3.25</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="BJ30" t="n">
         <v>10</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -8223,16 +8223,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="G31" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H31" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I31" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J31" t="n">
         <v>4</v>
@@ -8241,19 +8241,19 @@
         <v>4.1</v>
       </c>
       <c r="L31" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M31" t="n">
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O31" t="n">
         <v>1.24</v>
       </c>
       <c r="P31" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q31" t="n">
         <v>1.74</v>
@@ -8265,22 +8265,22 @@
         <v>2.8</v>
       </c>
       <c r="T31" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U31" t="n">
         <v>2.3</v>
       </c>
       <c r="V31" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W31" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X31" t="n">
         <v>19.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z31" t="n">
         <v>38</v>
@@ -8289,13 +8289,13 @@
         <v>95</v>
       </c>
       <c r="AB31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC31" t="n">
         <v>9.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="n">
         <v>50</v>
@@ -8325,7 +8325,7 @@
         <v>80</v>
       </c>
       <c r="AN31" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO31" t="n">
         <v>46</v>
@@ -8340,10 +8340,10 @@
         <v>32</v>
       </c>
       <c r="AS31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT31" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU31" t="n">
         <v>8.199999999999999</v>
@@ -8358,7 +8358,7 @@
         <v>11</v>
       </c>
       <c r="AY31" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ31" t="n">
         <v>14.5</v>
@@ -8376,16 +8376,16 @@
         <v>25</v>
       </c>
       <c r="BE31" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG31" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BH31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI31" t="n">
         <v>3.4</v>
@@ -8394,13 +8394,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK31" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BL31" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN31" t="n">
         <v>4.9</v>
@@ -8412,41 +8412,41 @@
         <v>13</v>
       </c>
       <c r="BQ31" t="n">
-        <v>9</v>
+        <v>5.9</v>
       </c>
       <c r="BR31" t="n">
         <v>25</v>
       </c>
       <c r="BS31" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT31" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU31" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV31" t="n">
         <v>36</v>
       </c>
       <c r="BW31" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BX31" t="n">
         <v>42</v>
       </c>
       <c r="BY31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ31" t="n">
         <v>19</v>
       </c>
       <c r="CA31" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -8477,22 +8477,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="G32" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="H32" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="I32" t="n">
         <v>7.2</v>
       </c>
       <c r="J32" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K32" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L32" t="n">
         <v>1.35</v>
@@ -8501,13 +8501,13 @@
         <v>1.07</v>
       </c>
       <c r="N32" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O32" t="n">
         <v>1.34</v>
       </c>
       <c r="P32" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q32" t="n">
         <v>1.98</v>
@@ -8519,7 +8519,7 @@
         <v>3.55</v>
       </c>
       <c r="T32" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U32" t="n">
         <v>1.91</v>
@@ -8567,7 +8567,7 @@
         <v>110</v>
       </c>
       <c r="AJ32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK32" t="n">
         <v>24</v>
@@ -8579,22 +8579,22 @@
         <v>170</v>
       </c>
       <c r="AN32" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO32" t="n">
         <v>150</v>
       </c>
       <c r="AP32" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ32" t="n">
         <v>13.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AT32" t="n">
         <v>5.9</v>
@@ -8603,10 +8603,10 @@
         <v>7.8</v>
       </c>
       <c r="AV32" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AW32" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AX32" t="n">
         <v>7.4</v>
@@ -8618,10 +8618,10 @@
         <v>15.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BB32" t="n">
-        <v>3.25</v>
+        <v>12.5</v>
       </c>
       <c r="BC32" t="n">
         <v>13.5</v>
@@ -8630,13 +8630,13 @@
         <v>28</v>
       </c>
       <c r="BE32" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BF32" t="n">
         <v>8.6</v>
       </c>
       <c r="BG32" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BH32" t="n">
         <v>3.35</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
         <v>5.9</v>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J33" t="n">
         <v>3.75</v>
@@ -8752,19 +8752,19 @@
         <v>1.31</v>
       </c>
       <c r="M33" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N33" t="n">
         <v>4.1</v>
       </c>
       <c r="O33" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P33" t="n">
         <v>2.06</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="R33" t="n">
         <v>1.42</v>
@@ -8779,7 +8779,7 @@
         <v>2.02</v>
       </c>
       <c r="V33" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W33" t="n">
         <v>2.38</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -9120,7 +9120,7 @@
         <v>8.4</v>
       </c>
       <c r="AY34" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AZ34" t="n">
         <v>15</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
         <v>4.8</v>
       </c>
       <c r="L36" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="M36" t="n">
         <v>1.06</v>
@@ -9589,7 +9589,7 @@
         <v>22</v>
       </c>
       <c r="AL36" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM36" t="n">
         <v>1000</v>
@@ -9658,7 +9658,7 @@
         <v>6.8</v>
       </c>
       <c r="BI36" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="BJ36" t="n">
         <v>1000</v>
@@ -9673,7 +9673,7 @@
         <v>1.05</v>
       </c>
       <c r="BN36" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BO36" t="n">
         <v>3.6</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -860,19 +860,19 @@
         <v>1.02</v>
       </c>
       <c r="G2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
         <v>1.02</v>
       </c>
       <c r="I2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
         <v>1.02</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="O2" t="n">
         <v>1.32</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -1129,10 +1129,10 @@
         <v>3.55</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
         <v>3.45</v>
@@ -1153,7 +1153,7 @@
         <v>3.55</v>
       </c>
       <c r="T3" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U3" t="n">
         <v>2.04</v>
@@ -1231,7 +1231,7 @@
         <v>4.7</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU3" t="n">
         <v>6</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>4.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>2.14</v>
@@ -1383,7 +1383,7 @@
         <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
@@ -1395,10 +1395,10 @@
         <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="R4" t="n">
         <v>1.3</v>
@@ -1530,7 +1530,7 @@
         <v>3.35</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -2635,58 +2635,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G9" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J9" t="n">
         <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O9" t="n">
         <v>1.28</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.24</v>
-      </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="U9" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W9" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="X9" t="n">
         <v>970</v>
@@ -2695,10 +2695,10 @@
         <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB9" t="n">
         <v>970</v>
@@ -2713,7 +2713,7 @@
         <v>38</v>
       </c>
       <c r="AF9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG9" t="n">
         <v>970</v>
@@ -2722,37 +2722,37 @@
         <v>970</v>
       </c>
       <c r="AI9" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AL9" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AQ9" t="n">
         <v>3.55</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT9" t="n">
         <v>3.5</v>
@@ -2761,58 +2761,58 @@
         <v>3.05</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BA9" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
         <v>4.2</v>
       </c>
-      <c r="BF9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>970</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
@@ -2824,41 +2824,41 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.03</v>
+        <v>1.71</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>1.02</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
         <v>1.24</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.13</v>
@@ -3176,7 +3176,7 @@
         <v>2.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="R11" t="n">
         <v>1.8</v>
@@ -3185,7 +3185,7 @@
         <v>2.04</v>
       </c>
       <c r="T11" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U11" t="n">
         <v>2.2</v>
@@ -3215,7 +3215,7 @@
         <v>970</v>
       </c>
       <c r="AD11" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AE11" t="n">
         <v>120</v>
@@ -3254,7 +3254,7 @@
         <v>4.7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AR11" t="n">
         <v>5</v>
@@ -3272,28 +3272,28 @@
         <v>4.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AY11" t="n">
         <v>3.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BC11" t="n">
         <v>3.9</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
         <v>5</v>
@@ -3323,7 +3323,7 @@
         <v>1.56</v>
       </c>
       <c r="BN11" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="BO11" t="n">
         <v>3.1</v>
@@ -3332,7 +3332,7 @@
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -3424,22 +3424,22 @@
         <v>2.64</v>
       </c>
       <c r="O12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P12" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Q12" t="n">
         <v>2.56</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S12" t="n">
         <v>5.1</v>
       </c>
       <c r="T12" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U12" t="n">
         <v>1.73</v>
@@ -3568,7 +3568,7 @@
         <v>12.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3580,7 +3580,7 @@
         <v>8.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
@@ -3598,7 +3598,7 @@
         <v>4.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>4.9</v>
       </c>
       <c r="G13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H13" t="n">
         <v>1.74</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="O15" t="n">
         <v>1.12</v>
@@ -4201,7 +4201,7 @@
         <v>1.87</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="U15" t="n">
         <v>2.84</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
         <v>2.32</v>
@@ -4464,7 +4464,7 @@
         <v>1.38</v>
       </c>
       <c r="W16" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="X16" t="n">
         <v>48</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
         <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4691,7 +4691,7 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>1.02</v>
       </c>
       <c r="O17" t="n">
         <v>1.05</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -4924,13 +4924,13 @@
         <v>2.4</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H18" t="n">
         <v>2.56</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J18" t="n">
         <v>4.1</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -5178,13 +5178,13 @@
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I19" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J19" t="n">
         <v>3.65</v>
@@ -5205,7 +5205,7 @@
         <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
         <v>1.69</v>
@@ -5223,10 +5223,10 @@
         <v>2.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W19" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="X19" t="n">
         <v>22</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5435,7 @@
         <v>1.76</v>
       </c>
       <c r="H20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I20" t="n">
         <v>8</v>
@@ -5459,7 +5459,7 @@
         <v>1.4</v>
       </c>
       <c r="P20" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q20" t="n">
         <v>2.18</v>
@@ -5489,7 +5489,7 @@
         <v>23</v>
       </c>
       <c r="Z20" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA20" t="n">
         <v>270</v>
@@ -5504,7 +5504,7 @@
         <v>32</v>
       </c>
       <c r="AE20" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF20" t="n">
         <v>9.6</v>
@@ -5540,7 +5540,7 @@
         <v>3.55</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR20" t="n">
         <v>4.5</v>
@@ -5564,7 +5564,7 @@
         <v>3.2</v>
       </c>
       <c r="AY20" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AZ20" t="n">
         <v>4.1</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5716,7 @@
         <v>3.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="R21" t="n">
         <v>2.26</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -6039,22 +6039,22 @@
         <v>95</v>
       </c>
       <c r="AN22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AO22" t="n">
         <v>90</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT22" t="n">
         <v>10</v>
@@ -6063,10 +6063,10 @@
         <v>10</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX22" t="n">
         <v>8.800000000000001</v>
@@ -6078,7 +6078,7 @@
         <v>16</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB22" t="n">
         <v>10</v>
@@ -6090,13 +6090,13 @@
         <v>20</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH22" t="n">
         <v>5.1</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H23" t="n">
         <v>1.92</v>
@@ -6212,22 +6212,22 @@
         <v>1.19</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>6.2</v>
+        <v>1.06</v>
       </c>
       <c r="O23" t="n">
         <v>1.09</v>
       </c>
       <c r="P23" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
         <v>1.8</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="G24" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="H24" t="n">
-        <v>2.6</v>
+        <v>1.09</v>
       </c>
       <c r="I24" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="K24" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -6469,13 +6469,13 @@
         <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="P24" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="Q24" t="n">
         <v>2.08</v>
@@ -6484,7 +6484,7 @@
         <v>1.12</v>
       </c>
       <c r="S24" t="n">
-        <v>2.08</v>
+        <v>2.44</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -6493,10 +6493,10 @@
         <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W24" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
         <v>2.94</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>3.1</v>
       </c>
       <c r="K26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
         <v>3.45</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="BJ27" t="n">
         <v>10</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -7497,7 +7497,7 @@
         <v>1.78</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
         <v>2.96</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -7715,46 +7715,46 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="G29" t="n">
-        <v>110</v>
+        <v>2.24</v>
       </c>
       <c r="H29" t="n">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="I29" t="n">
-        <v>110</v>
+        <v>6.2</v>
       </c>
       <c r="J29" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="K29" t="n">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M29" t="n">
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.24</v>
+        <v>2.46</v>
       </c>
       <c r="O29" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.38</v>
+        <v>2.28</v>
       </c>
       <c r="R29" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S29" t="n">
-        <v>1.38</v>
+        <v>2.64</v>
       </c>
       <c r="T29" t="n">
         <v>1.01</v>
@@ -7763,10 +7763,10 @@
         <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -7972,28 +7972,28 @@
         <v>2.42</v>
       </c>
       <c r="G30" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H30" t="n">
         <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J30" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
         <v>3.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="M30" t="n">
         <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O30" t="n">
         <v>1.38</v>
@@ -8008,7 +8008,7 @@
         <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T30" t="n">
         <v>1.84</v>
@@ -8017,43 +8017,43 @@
         <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W30" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X30" t="n">
         <v>15</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA30" t="n">
         <v>70</v>
       </c>
       <c r="AB30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC30" t="n">
         <v>7.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE30" t="n">
         <v>50</v>
       </c>
       <c r="AF30" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI30" t="n">
         <v>65</v>
@@ -8098,7 +8098,7 @@
         <v>10.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AX30" t="n">
         <v>11.5</v>
@@ -8110,34 +8110,34 @@
         <v>16</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB30" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BC30" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BF30" t="n">
         <v>19.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BH30" t="n">
         <v>3.25</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ30" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK30" t="n">
         <v>5.7</v>
@@ -8146,7 +8146,7 @@
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN30" t="n">
         <v>5.5</v>
@@ -8164,7 +8164,7 @@
         <v>36</v>
       </c>
       <c r="BS30" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT30" t="n">
         <v>6.4</v>
@@ -8176,7 +8176,7 @@
         <v>26</v>
       </c>
       <c r="BW30" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
@@ -8188,11 +8188,11 @@
         <v>32</v>
       </c>
       <c r="CA30" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -8223,16 +8223,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="G31" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="H31" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I31" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J31" t="n">
         <v>4</v>
@@ -8253,7 +8253,7 @@
         <v>1.24</v>
       </c>
       <c r="P31" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q31" t="n">
         <v>1.74</v>
@@ -8262,19 +8262,19 @@
         <v>1.51</v>
       </c>
       <c r="S31" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="T31" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U31" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V31" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W31" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X31" t="n">
         <v>19.5</v>
@@ -8286,7 +8286,7 @@
         <v>38</v>
       </c>
       <c r="AA31" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB31" t="n">
         <v>11.5</v>
@@ -8298,7 +8298,7 @@
         <v>18</v>
       </c>
       <c r="AE31" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AF31" t="n">
         <v>13</v>
@@ -8316,34 +8316,34 @@
         <v>21</v>
       </c>
       <c r="AK31" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM31" t="n">
         <v>80</v>
       </c>
       <c r="AN31" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO31" t="n">
         <v>46</v>
       </c>
       <c r="AP31" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ31" t="n">
         <v>18.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS31" t="n">
         <v>13</v>
       </c>
       <c r="AT31" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU31" t="n">
         <v>8.199999999999999</v>
@@ -8376,13 +8376,13 @@
         <v>25</v>
       </c>
       <c r="BE31" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG31" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="BH31" t="n">
         <v>4</v>
@@ -8394,13 +8394,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN31" t="n">
         <v>4.9</v>
@@ -8412,13 +8412,13 @@
         <v>13</v>
       </c>
       <c r="BQ31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR31" t="n">
         <v>25</v>
       </c>
       <c r="BS31" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT31" t="n">
         <v>8.199999999999999</v>
@@ -8427,26 +8427,26 @@
         <v>4.7</v>
       </c>
       <c r="BV31" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW31" t="n">
         <v>8.4</v>
       </c>
       <c r="BX31" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY31" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ31" t="n">
         <v>19</v>
       </c>
       <c r="CA31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8603,7 @@
         <v>7.8</v>
       </c>
       <c r="AV32" t="n">
-        <v>3.4</v>
+        <v>20</v>
       </c>
       <c r="AW32" t="n">
         <v>3.75</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -8731,19 +8731,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="G33" t="n">
         <v>1.72</v>
       </c>
       <c r="H33" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I33" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J33" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K33" t="n">
         <v>4.5</v>
@@ -8764,7 +8764,7 @@
         <v>2.06</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="R33" t="n">
         <v>1.42</v>
@@ -8779,10 +8779,10 @@
         <v>2.02</v>
       </c>
       <c r="V33" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W33" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X33" t="n">
         <v>20</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
         <v>4.8</v>
       </c>
       <c r="L36" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M36" t="n">
         <v>1.06</v>
@@ -9577,7 +9577,7 @@
         <v>970</v>
       </c>
       <c r="AH36" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI36" t="n">
         <v>80</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-05 14:02:16</t>
+          <t>2026-06-05 16:14:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="G2" t="n">
-        <v>1.56</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="K2" t="n">
         <v>15</v>
@@ -878,37 +878,37 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
         <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.89</v>
+        <v>1.33</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>90</v>
@@ -923,10 +923,10 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -938,7 +938,7 @@
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AH2" t="n">
         <v>1000</v>
@@ -947,10 +947,10 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -959,64 +959,64 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G3" t="n">
         <v>2.72</v>
       </c>
       <c r="H3" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J3" t="n">
         <v>3.3</v>
@@ -1144,7 +1144,7 @@
         <v>1.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R3" t="n">
         <v>1.32</v>
@@ -1156,7 +1156,7 @@
         <v>1.79</v>
       </c>
       <c r="U3" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V3" t="n">
         <v>1.43</v>
@@ -1165,82 +1165,82 @@
         <v>1.58</v>
       </c>
       <c r="X3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="AA3" t="n">
-        <v>65</v>
+        <v>280</v>
       </c>
       <c r="AB3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="AF3" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="AJ3" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AK3" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AL3" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AM3" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>29</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>42</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
         <v>12.5</v>
@@ -1252,25 +1252,25 @@
         <v>13.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G4" t="n">
         <v>4.5</v>
@@ -1395,10 +1395,10 @@
         <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="R4" t="n">
         <v>1.3</v>
@@ -1419,7 +1419,7 @@
         <v>1.29</v>
       </c>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y4" t="n">
         <v>9</v>
@@ -1446,7 +1446,7 @@
         <v>38</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AH4" t="n">
         <v>21</v>
@@ -1461,22 +1461,22 @@
         <v>70</v>
       </c>
       <c r="AL4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM4" t="n">
         <v>140</v>
       </c>
       <c r="AN4" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AO4" t="n">
         <v>20</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR4" t="n">
         <v>9.199999999999999</v>
@@ -1488,10 +1488,10 @@
         <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW4" t="n">
         <v>17</v>
@@ -1503,25 +1503,25 @@
         <v>12.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC4" t="n">
         <v>40</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG4" t="n">
         <v>13</v>
@@ -1578,7 +1578,7 @@
         <v>32</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -1619,220 +1619,220 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="H5" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X5" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>220</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>300</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW5" t="n">
         <v>2.74</v>
       </c>
-      <c r="K5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="AX5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BB5" t="n">
         <v>2.68</v>
       </c>
-      <c r="O5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>2.68</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>2.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>2.36</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.05</v>
+        <v>2.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.05</v>
+        <v>2.76</v>
       </c>
       <c r="BH5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
         <v>3.6</v>
       </c>
-      <c r="BI5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>1.54</v>
       </c>
       <c r="G6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H6" t="n">
         <v>4.4</v>
@@ -1885,10 +1885,10 @@
         <v>7.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
         <v>1.25</v>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>
@@ -1924,16 +1924,16 @@
         <v>1.18</v>
       </c>
       <c r="W6" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X6" t="n">
         <v>90</v>
       </c>
       <c r="Y6" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="Z6" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1942,10 +1942,10 @@
         <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AE6" t="n">
         <v>80</v>
@@ -1957,82 +1957,82 @@
         <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AI6" t="n">
         <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AK6" t="n">
         <v>970</v>
       </c>
       <c r="AL6" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AO6" t="n">
         <v>75</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>4</v>
+        <v>2.26</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.2</v>
+        <v>2.26</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.1</v>
+        <v>2.24</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="BA6" t="n">
-        <v>4</v>
+        <v>2.24</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="BC6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BF6" t="n">
         <v>3.5</v>
       </c>
-      <c r="BD6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>2.88</v>
-      </c>
       <c r="BG6" t="n">
-        <v>4</v>
+        <v>2.24</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -2136,10 +2136,10 @@
         <v>5.7</v>
       </c>
       <c r="I7" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
         <v>5.9</v>
@@ -2175,19 +2175,19 @@
         <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W7" t="n">
         <v>2.74</v>
       </c>
       <c r="X7" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z7" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AA7" t="n">
         <v>240</v>
@@ -2196,97 +2196,97 @@
         <v>13.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE7" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AF7" t="n">
         <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
         <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AJ7" t="n">
         <v>16.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AL7" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AO7" t="n">
         <v>110</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="AQ7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT7" t="n">
         <v>4</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AU7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB7" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BC7" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH7" t="n">
         <v>4.9</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -2390,10 +2390,10 @@
         <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
         <v>5</v>
@@ -2420,7 +2420,7 @@
         <v>1.61</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T8" t="n">
         <v>1.59</v>
@@ -2429,118 +2429,118 @@
         <v>2.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
         <v>2.16</v>
       </c>
       <c r="X8" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Y8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Z8" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA8" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF8" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="n">
         <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK8" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM8" t="n">
         <v>75</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="AS8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT8" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT8" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AU8" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AX8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4</v>
       </c>
-      <c r="AY8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.25</v>
-      </c>
       <c r="BG8" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH8" t="n">
         <v>4.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G9" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="H9" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
         <v>3.7</v>
@@ -2683,10 +2683,10 @@
         <v>2.16</v>
       </c>
       <c r="V9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X9" t="n">
         <v>970</v>
@@ -2695,106 +2695,106 @@
         <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="AA9" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
         <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD9" t="n">
         <v>970</v>
       </c>
       <c r="AE9" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AF9" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
         <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AJ9" t="n">
-        <v>42</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AL9" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AO9" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="AQ9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD9" t="n">
         <v>3.55</v>
       </c>
-      <c r="AR9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY9" t="n">
+      <c r="BE9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG9" t="n">
         <v>3.55</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.1</v>
       </c>
       <c r="BH9" t="n">
         <v>8.6</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>2.36</v>
       </c>
       <c r="G10" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H10" t="n">
         <v>2.66</v>
@@ -2913,7 +2913,7 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.24</v>
@@ -2922,13 +2922,13 @@
         <v>2.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="R10" t="n">
         <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="T10" t="n">
         <v>1.57</v>
@@ -2940,7 +2940,7 @@
         <v>1.46</v>
       </c>
       <c r="W10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X10" t="n">
         <v>90</v>
@@ -2949,106 +2949,106 @@
         <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="AA10" t="n">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
         <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
         <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AG10" t="n">
         <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI10" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AJ10" t="n">
-        <v>42</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AL10" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AM10" t="n">
-        <v>75</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BE10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BF10" t="n">
         <v>4.7</v>
       </c>
-      <c r="BF10" t="n">
-        <v>4</v>
-      </c>
       <c r="BG10" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="G11" t="n">
         <v>1.47</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I11" t="n">
         <v>10.5</v>
       </c>
       <c r="J11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>500</v>
+        <v>7.8</v>
       </c>
       <c r="L11" t="n">
         <v>1.18</v>
@@ -3182,7 +3182,7 @@
         <v>1.81</v>
       </c>
       <c r="S11" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T11" t="n">
         <v>1.66</v>
@@ -3197,10 +3197,10 @@
         <v>3.1</v>
       </c>
       <c r="X11" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Y11" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="Z11" t="n">
         <v>95</v>
@@ -3209,16 +3209,16 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AC11" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD11" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AE11" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AF11" t="n">
         <v>970</v>
@@ -3230,79 +3230,79 @@
         <v>26</v>
       </c>
       <c r="AI11" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ11" t="n">
-        <v>970</v>
+        <v>180</v>
       </c>
       <c r="AK11" t="n">
         <v>970</v>
       </c>
       <c r="AL11" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AM11" t="n">
         <v>95</v>
       </c>
       <c r="AN11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AO11" t="n">
         <v>90</v>
       </c>
       <c r="AP11" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AR11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV11" t="n">
         <v>5.3</v>
       </c>
-      <c r="AS11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT11" t="n">
+      <c r="AW11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX11" t="n">
         <v>4.2</v>
       </c>
-      <c r="AU11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW11" t="n">
+      <c r="AY11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD11" t="n">
         <v>5.3</v>
       </c>
-      <c r="AX11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE11" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -3400,13 +3400,13 @@
         <v>2.3</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H12" t="n">
         <v>3.15</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="n">
         <v>3.1</v>
@@ -3415,7 +3415,7 @@
         <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
@@ -3433,130 +3433,130 @@
         <v>2.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U12" t="n">
         <v>1.96</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
         <v>1.63</v>
       </c>
       <c r="X12" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>2.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>2.36</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -3663,10 +3663,10 @@
         <v>2.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K13" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
         <v>1.55</v>
@@ -3705,16 +3705,16 @@
         <v>1.24</v>
       </c>
       <c r="X13" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="n">
         <v>7</v>
       </c>
       <c r="Z13" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AA13" t="n">
-        <v>26</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
         <v>970</v>
@@ -3723,31 +3723,31 @@
         <v>8</v>
       </c>
       <c r="AD13" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AG13" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AH13" t="n">
         <v>27</v>
       </c>
       <c r="AI13" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ13" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="AL13" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AM13" t="n">
         <v>240</v>
@@ -3768,7 +3768,7 @@
         <v>8.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT13" t="n">
         <v>9.6</v>
@@ -3780,49 +3780,49 @@
         <v>8.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH13" t="n">
         <v>2.82</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BJ13" t="n">
         <v>12.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>9</v>
+        <v>5.9</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3834,19 +3834,19 @@
         <v>8.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT13" t="n">
         <v>4.6</v>
@@ -3858,7 +3858,7 @@
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -3914,10 +3914,10 @@
         <v>6.4</v>
       </c>
       <c r="I14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
         <v>3.95</v>
@@ -3926,22 +3926,22 @@
         <v>1.38</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
         <v>1.39</v>
       </c>
       <c r="P14" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
         <v>4.1</v>
@@ -3965,10 +3965,10 @@
         <v>23</v>
       </c>
       <c r="Z14" t="n">
-        <v>65</v>
+        <v>270</v>
       </c>
       <c r="AA14" t="n">
-        <v>270</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
         <v>8.4</v>
@@ -3977,7 +3977,7 @@
         <v>10</v>
       </c>
       <c r="AD14" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AE14" t="n">
         <v>140</v>
@@ -3986,13 +3986,13 @@
         <v>11</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="AH14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI14" t="n">
-        <v>140</v>
+        <v>450</v>
       </c>
       <c r="AJ14" t="n">
         <v>21</v>
@@ -4001,70 +4001,70 @@
         <v>25</v>
       </c>
       <c r="AL14" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="AM14" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP14" t="n">
         <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AT14" t="n">
         <v>6.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="AV14" t="n">
-        <v>19</v>
+        <v>4.5</v>
       </c>
       <c r="AW14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ14" t="n">
+      <c r="BA14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF14" t="n">
         <v>3.95</v>
       </c>
-      <c r="BA14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>10</v>
-      </c>
       <c r="BG14" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BH14" t="n">
         <v>3.15</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G15" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K15" t="n">
         <v>4.1</v>
@@ -4192,7 +4192,7 @@
         <v>2.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R15" t="n">
         <v>1.48</v>
@@ -4207,22 +4207,22 @@
         <v>2.32</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X15" t="n">
         <v>22</v>
       </c>
       <c r="Y15" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AA15" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AB15" t="n">
         <v>13.5</v>
@@ -4234,37 +4234,37 @@
         <v>15.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="AF15" t="n">
         <v>16</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK15" t="n">
         <v>46</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>22</v>
-      </c>
       <c r="AL15" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AM15" t="n">
-        <v>80</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO15" t="n">
-        <v>36</v>
+        <v>220</v>
       </c>
       <c r="AP15" t="n">
         <v>15</v>
@@ -4273,13 +4273,13 @@
         <v>12.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU15" t="n">
         <v>7.2</v>
@@ -4288,7 +4288,7 @@
         <v>11.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AX15" t="n">
         <v>13</v>
@@ -4300,7 +4300,7 @@
         <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BB15" t="n">
         <v>20</v>
@@ -4312,13 +4312,13 @@
         <v>24</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BH15" t="n">
         <v>4.2</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G16" t="n">
         <v>2.64</v>
       </c>
       <c r="H16" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I16" t="n">
         <v>2.82</v>
@@ -4449,7 +4449,7 @@
         <v>1.44</v>
       </c>
       <c r="R16" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="S16" t="n">
         <v>2.08</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -4667,196 +4667,196 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="G17" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="H17" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="I17" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="J17" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="K17" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="M17" t="n">
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="P17" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="R17" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="S17" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="T17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="U17" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W17" t="n">
         <v>3.15</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.68</v>
       </c>
       <c r="X17" t="n">
         <v>90</v>
       </c>
       <c r="Y17" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="Z17" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AA17" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="AB17" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AC17" t="n">
         <v>22</v>
       </c>
       <c r="AD17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE17" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF17" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH17" t="n">
         <v>20</v>
       </c>
       <c r="AI17" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AK17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AM17" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AN17" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="AO17" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.1</v>
+        <v>2.62</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.7</v>
+        <v>2.46</v>
       </c>
       <c r="AU17" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AY17" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BE17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK17" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF17" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BL17" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BM17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BO17" t="n">
         <v>3.7</v>
       </c>
       <c r="BP17" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BR17" t="n">
         <v>14.5</v>
@@ -4865,22 +4865,22 @@
         <v>6</v>
       </c>
       <c r="BT17" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV17" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BW17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY17" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>28</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>7.4</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -4921,25 +4921,25 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G18" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H18" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="I18" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K18" t="n">
         <v>5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M18" t="n">
         <v>1.02</v>
@@ -4948,28 +4948,28 @@
         <v>1.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P18" t="n">
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R18" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V18" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
         <v>1.76</v>
@@ -4978,115 +4978,115 @@
         <v>48</v>
       </c>
       <c r="Y18" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="Z18" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AA18" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="AB18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AC18" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AF18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH18" t="n">
         <v>15</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>16.5</v>
       </c>
       <c r="AI18" t="n">
         <v>32</v>
       </c>
       <c r="AJ18" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AK18" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL18" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AM18" t="n">
-        <v>46</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AO18" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.75</v>
+        <v>5.3</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.85</v>
+        <v>5.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF18" t="n">
         <v>4.1</v>
       </c>
-      <c r="BD18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BG18" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="BH18" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ18" t="n">
         <v>8.4</v>
@@ -5104,7 +5104,7 @@
         <v>6.4</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP18" t="n">
         <v>14</v>
@@ -5137,14 +5137,14 @@
         <v>7</v>
       </c>
       <c r="BZ18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA18" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="G19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H19" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>3.6</v>
@@ -5199,7 +5199,7 @@
         <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>6.8</v>
+        <v>1.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.12</v>
@@ -5223,37 +5223,37 @@
         <v>2.84</v>
       </c>
       <c r="V19" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X19" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="Y19" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="Z19" t="n">
         <v>22</v>
       </c>
       <c r="AA19" t="n">
-        <v>30</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AC19" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AD19" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AE19" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="AF19" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AG19" t="n">
         <v>21</v>
@@ -5265,76 +5265,76 @@
         <v>27</v>
       </c>
       <c r="AJ19" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AK19" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AL19" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AM19" t="n">
         <v>55</v>
       </c>
       <c r="AN19" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AO19" t="n">
         <v>8</v>
       </c>
       <c r="AP19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF19" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BG19" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="BH19" t="n">
         <v>970</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -5432,19 +5432,19 @@
         <v>1.6</v>
       </c>
       <c r="G20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H20" t="n">
         <v>3.2</v>
       </c>
       <c r="I20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J20" t="n">
         <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -5456,7 +5456,7 @@
         <v>1.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="P20" t="n">
         <v>2.4</v>
@@ -5480,7 +5480,7 @@
         <v>1.21</v>
       </c>
       <c r="W20" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5498,7 +5498,7 @@
         <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD20" t="n">
         <v>1000</v>
@@ -5519,10 +5519,10 @@
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL20" t="n">
         <v>1000</v>
@@ -5582,13 +5582,13 @@
         <v>1.03</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
         <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -5737,19 +5737,19 @@
         <v>2.38</v>
       </c>
       <c r="X21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y21" t="n">
         <v>24</v>
       </c>
       <c r="Z21" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AA21" t="n">
         <v>180</v>
       </c>
       <c r="AB21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC21" t="n">
         <v>10.5</v>
@@ -5758,19 +5758,19 @@
         <v>27</v>
       </c>
       <c r="AE21" t="n">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AF21" t="n">
         <v>11</v>
       </c>
       <c r="AG21" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH21" t="n">
         <v>22</v>
       </c>
       <c r="AI21" t="n">
-        <v>85</v>
+        <v>250</v>
       </c>
       <c r="AJ21" t="n">
         <v>17</v>
@@ -5779,16 +5779,16 @@
         <v>17.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AM21" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AO21" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AP21" t="n">
         <v>14.5</v>
@@ -5797,10 +5797,10 @@
         <v>17</v>
       </c>
       <c r="AR21" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AT21" t="n">
         <v>7.4</v>
@@ -5812,19 +5812,19 @@
         <v>17.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ21" t="n">
         <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB21" t="n">
         <v>12</v>
@@ -5833,16 +5833,16 @@
         <v>14</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.8</v>
+        <v>16</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF21" t="n">
         <v>7</v>
       </c>
       <c r="BG21" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH21" t="n">
         <v>4</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -5946,13 +5946,13 @@
         <v>1.7</v>
       </c>
       <c r="I22" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L22" t="n">
         <v>1.28</v>
@@ -5997,7 +5997,7 @@
         <v>11.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA22" t="n">
         <v>20</v>
@@ -6015,31 +6015,31 @@
         <v>17</v>
       </c>
       <c r="AF22" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AG22" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI22" t="n">
         <v>34</v>
       </c>
       <c r="AJ22" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AK22" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AL22" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="AM22" t="n">
-        <v>95</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>65</v>
+        <v>310</v>
       </c>
       <c r="AO22" t="n">
         <v>9.6</v>
@@ -6069,7 +6069,7 @@
         <v>12.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AY22" t="n">
         <v>17</v>
@@ -6078,22 +6078,22 @@
         <v>14.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC22" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG22" t="n">
         <v>7</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -6248,67 +6248,67 @@
         <v>38</v>
       </c>
       <c r="Y23" t="n">
-        <v>44</v>
+        <v>160</v>
       </c>
       <c r="Z23" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="AA23" t="n">
         <v>240</v>
       </c>
       <c r="AB23" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AD23" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AE23" t="n">
-        <v>110</v>
+        <v>400</v>
       </c>
       <c r="AF23" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AG23" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH23" t="n">
         <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="AJ23" t="n">
         <v>15.5</v>
       </c>
       <c r="AK23" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AL23" t="n">
         <v>32</v>
       </c>
       <c r="AM23" t="n">
-        <v>95</v>
+        <v>260</v>
       </c>
       <c r="AN23" t="n">
         <v>5.1</v>
       </c>
       <c r="AO23" t="n">
-        <v>90</v>
+        <v>330</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4.7</v>
+        <v>18</v>
       </c>
       <c r="AR23" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT23" t="n">
         <v>10</v>
@@ -6317,10 +6317,10 @@
         <v>10</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AX23" t="n">
         <v>8.800000000000001</v>
@@ -6332,7 +6332,7 @@
         <v>16</v>
       </c>
       <c r="BA23" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BB23" t="n">
         <v>10</v>
@@ -6344,13 +6344,13 @@
         <v>20</v>
       </c>
       <c r="BE23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BF23" t="n">
         <v>4</v>
       </c>
       <c r="BG23" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="BH23" t="n">
         <v>5.1</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -6451,13 +6451,13 @@
         <v>3.55</v>
       </c>
       <c r="H24" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="I24" t="n">
         <v>2.12</v>
       </c>
       <c r="J24" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="K24" t="n">
         <v>5.4</v>
@@ -6472,7 +6472,7 @@
         <v>1.1</v>
       </c>
       <c r="O24" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P24" t="n">
         <v>1.25</v>
@@ -6481,7 +6481,7 @@
         <v>1.3</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="S24" t="n">
         <v>1.8</v>
@@ -6502,13 +6502,13 @@
         <v>55</v>
       </c>
       <c r="Y24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z24" t="n">
         <v>23</v>
       </c>
       <c r="AA24" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AB24" t="n">
         <v>27</v>
@@ -6517,10 +6517,10 @@
         <v>16</v>
       </c>
       <c r="AD24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AF24" t="n">
         <v>38</v>
@@ -6553,58 +6553,58 @@
         <v>7.8</v>
       </c>
       <c r="AP24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD24" t="n">
         <v>5</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BE24" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -6699,37 +6699,37 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G25" t="n">
         <v>1.59</v>
       </c>
       <c r="H25" t="n">
-        <v>1.09</v>
+        <v>4.5</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M25" t="n">
         <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O25" t="n">
         <v>1.41</v>
       </c>
       <c r="P25" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="Q25" t="n">
         <v>2.08</v>
@@ -6741,13 +6741,13 @@
         <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W25" t="n">
         <v>2.68</v>
@@ -6765,7 +6765,7 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC25" t="n">
         <v>1000</v>
@@ -6777,10 +6777,10 @@
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH25" t="n">
         <v>1000</v>
@@ -6789,10 +6789,10 @@
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -6953,13 +6953,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="G26" t="n">
         <v>2.7</v>
       </c>
       <c r="H26" t="n">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="I26" t="n">
         <v>3.45</v>
@@ -7016,7 +7016,7 @@
         <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB26" t="n">
         <v>1000</v>
@@ -7043,7 +7043,7 @@
         <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7213,7 @@
         <v>2.78</v>
       </c>
       <c r="H27" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="I27" t="n">
         <v>3.05</v>
@@ -7222,7 +7222,7 @@
         <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -7231,22 +7231,22 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q27" t="n">
         <v>1.07</v>
       </c>
       <c r="R27" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="S27" t="n">
-        <v>1.66</v>
+        <v>1.07</v>
       </c>
       <c r="T27" t="n">
         <v>1.11</v>
@@ -7258,7 +7258,7 @@
         <v>1.49</v>
       </c>
       <c r="W27" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -7270,7 +7270,7 @@
         <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB27" t="n">
         <v>1000</v>
@@ -7297,7 +7297,7 @@
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -7497,7 +7497,7 @@
         <v>1.78</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S28" t="n">
         <v>2.96</v>
@@ -7506,7 +7506,7 @@
         <v>1.67</v>
       </c>
       <c r="U28" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="V28" t="n">
         <v>1.35</v>
@@ -7524,7 +7524,7 @@
         <v>30</v>
       </c>
       <c r="AA28" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AB28" t="n">
         <v>13</v>
@@ -7542,7 +7542,7 @@
         <v>16.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
         <v>19</v>
@@ -7575,10 +7575,10 @@
         <v>13</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT28" t="n">
         <v>9.6</v>
@@ -7590,7 +7590,7 @@
         <v>12.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX28" t="n">
         <v>12.5</v>
@@ -7602,25 +7602,25 @@
         <v>12.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BC28" t="n">
         <v>19</v>
       </c>
       <c r="BD28" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF28" t="n">
         <v>11.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH28" t="n">
         <v>3.9</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
         <v>24</v>
       </c>
       <c r="AA29" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB29" t="n">
         <v>12</v>
@@ -7805,7 +7805,7 @@
         <v>55</v>
       </c>
       <c r="AJ29" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK29" t="n">
         <v>32</v>
@@ -7844,7 +7844,7 @@
         <v>10</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX29" t="n">
         <v>13</v>
@@ -7856,25 +7856,25 @@
         <v>13</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB29" t="n">
         <v>4.8</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD29" t="n">
         <v>4.9</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF29" t="n">
         <v>18.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH29" t="n">
         <v>3.45</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
         <v>2.24</v>
       </c>
       <c r="H30" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
         <v>6.2</v>
@@ -7993,10 +7993,10 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O30" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P30" t="n">
         <v>1.5</v>
@@ -8023,7 +8023,7 @@
         <v>1.81</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y30" t="n">
         <v>1000</v>
@@ -8032,7 +8032,7 @@
         <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB30" t="n">
         <v>1000</v>
@@ -8059,7 +8059,7 @@
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -8226,163 +8226,163 @@
         <v>1.73</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K31" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="O31" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="P31" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="R31" t="n">
         <v>1.12</v>
       </c>
       <c r="S31" t="n">
-        <v>2.92</v>
+        <v>1.05</v>
       </c>
       <c r="T31" t="n">
-        <v>1.11</v>
+        <v>2.62</v>
       </c>
       <c r="U31" t="n">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="V31" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="W31" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.03</v>
+        <v>2.8</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.05</v>
+        <v>4.9</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.05</v>
+        <v>5.7</v>
       </c>
       <c r="BH31" t="n">
         <v>2.8</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
         <v>2.42</v>
       </c>
       <c r="K32" t="n">
-        <v>5.2</v>
+        <v>950</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -8501,13 +8501,13 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="O32" t="n">
         <v>1.34</v>
       </c>
       <c r="P32" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="Q32" t="n">
         <v>2.66</v>
@@ -8516,7 +8516,7 @@
         <v>1.12</v>
       </c>
       <c r="S32" t="n">
-        <v>2.66</v>
+        <v>1.05</v>
       </c>
       <c r="T32" t="n">
         <v>1.11</v>
@@ -8531,58 +8531,58 @@
         <v>1.38</v>
       </c>
       <c r="X32" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP32" t="n">
         <v>1.03</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -8731,19 +8731,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G33" t="n">
         <v>2.64</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I33" t="n">
         <v>3.35</v>
       </c>
       <c r="J33" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K33" t="n">
         <v>3.75</v>
@@ -8755,13 +8755,13 @@
         <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O33" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P33" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q33" t="n">
         <v>2.12</v>
@@ -8773,10 +8773,10 @@
         <v>3.9</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V33" t="n">
         <v>1.42</v>
@@ -8794,7 +8794,7 @@
         <v>25</v>
       </c>
       <c r="AA33" t="n">
-        <v>60</v>
+        <v>900</v>
       </c>
       <c r="AB33" t="n">
         <v>11</v>
@@ -8926,13 +8926,13 @@
         <v>36</v>
       </c>
       <c r="BS33" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT33" t="n">
         <v>6.4</v>
       </c>
       <c r="BU33" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV33" t="n">
         <v>26</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -8985,22 +8985,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G34" t="n">
         <v>2.08</v>
       </c>
       <c r="H34" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I34" t="n">
         <v>6.2</v>
       </c>
       <c r="J34" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K34" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -9009,7 +9009,7 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="O34" t="n">
         <v>1.01</v>
@@ -9039,7 +9039,7 @@
         <v>1.92</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y34" t="n">
         <v>1000</v>
@@ -9048,10 +9048,10 @@
         <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC34" t="n">
         <v>1000</v>
@@ -9063,10 +9063,10 @@
         <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH34" t="n">
         <v>1000</v>
@@ -9075,10 +9075,10 @@
         <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -9239,22 +9239,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="G35" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H35" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I35" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="J35" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="K35" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -9287,13 +9287,13 @@
         <v>1.11</v>
       </c>
       <c r="V35" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W35" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y35" t="n">
         <v>1000</v>
@@ -9302,10 +9302,10 @@
         <v>1000</v>
       </c>
       <c r="AA35" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC35" t="n">
         <v>1000</v>
@@ -9317,10 +9317,10 @@
         <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH35" t="n">
         <v>1000</v>
@@ -9329,10 +9329,10 @@
         <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -9493,166 +9493,166 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="G36" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="H36" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I36" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="J36" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="K36" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N36" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="O36" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="P36" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="R36" t="n">
         <v>1.12</v>
       </c>
       <c r="S36" t="n">
-        <v>2.38</v>
+        <v>1.05</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="U36" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="V36" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W36" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE36" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI36" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.05</v>
+        <v>6.2</v>
       </c>
       <c r="BH36" t="n">
         <v>2.82</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -9747,22 +9747,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="G37" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H37" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I37" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J37" t="n">
         <v>2.8</v>
       </c>
       <c r="K37" t="n">
-        <v>4.2</v>
+        <v>500</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -9771,10 +9771,10 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="O37" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="P37" t="n">
         <v>1.39</v>
@@ -9795,13 +9795,13 @@
         <v>1.11</v>
       </c>
       <c r="V37" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W37" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X37" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y37" t="n">
         <v>1000</v>
@@ -9840,7 +9840,7 @@
         <v>1000</v>
       </c>
       <c r="AK37" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL37" t="n">
         <v>1000</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -10007,7 +10007,7 @@
         <v>2.96</v>
       </c>
       <c r="H38" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="I38" t="n">
         <v>4.3</v>
@@ -10016,13 +10016,13 @@
         <v>2.6</v>
       </c>
       <c r="K38" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N38" t="n">
         <v>2.02</v>
@@ -10031,16 +10031,16 @@
         <v>1.44</v>
       </c>
       <c r="P38" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="R38" t="n">
         <v>1.12</v>
       </c>
       <c r="S38" t="n">
-        <v>2.96</v>
+        <v>1.05</v>
       </c>
       <c r="T38" t="n">
         <v>1.11</v>
@@ -10055,7 +10055,7 @@
         <v>1.51</v>
       </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -10255,22 +10255,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="G39" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H39" t="n">
         <v>2.66</v>
       </c>
       <c r="I39" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J39" t="n">
         <v>2.58</v>
       </c>
       <c r="K39" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -10279,7 +10279,7 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.86</v>
+        <v>1.1</v>
       </c>
       <c r="O39" t="n">
         <v>1.34</v>
@@ -10303,13 +10303,13 @@
         <v>1.11</v>
       </c>
       <c r="V39" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W39" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -10509,16 +10509,16 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G40" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="H40" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I40" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J40" t="n">
         <v>4</v>
@@ -10536,34 +10536,34 @@
         <v>4.7</v>
       </c>
       <c r="O40" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P40" t="n">
         <v>2.28</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R40" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S40" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T40" t="n">
         <v>1.7</v>
       </c>
       <c r="U40" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V40" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W40" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X40" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y40" t="n">
         <v>21</v>
@@ -10572,7 +10572,7 @@
         <v>38</v>
       </c>
       <c r="AA40" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB40" t="n">
         <v>11.5</v>
@@ -10581,7 +10581,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD40" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE40" t="n">
         <v>55</v>
@@ -10590,7 +10590,7 @@
         <v>13</v>
       </c>
       <c r="AG40" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH40" t="n">
         <v>17</v>
@@ -10608,28 +10608,28 @@
         <v>29</v>
       </c>
       <c r="AM40" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN40" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AO40" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP40" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ40" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR40" t="n">
         <v>30</v>
       </c>
       <c r="AS40" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT40" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU40" t="n">
         <v>8.199999999999999</v>
@@ -10662,13 +10662,13 @@
         <v>25</v>
       </c>
       <c r="BE40" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="BF40" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG40" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BH40" t="n">
         <v>4</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -10763,166 +10763,166 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="G41" t="n">
-        <v>1000</v>
+        <v>1.98</v>
       </c>
       <c r="H41" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="I41" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="J41" t="n">
-        <v>1.02</v>
+        <v>3.25</v>
       </c>
       <c r="K41" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L41" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M41" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N41" t="n">
-        <v>1.24</v>
+        <v>2.84</v>
       </c>
       <c r="O41" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="P41" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="R41" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="S41" t="n">
-        <v>1.05</v>
+        <v>3.1</v>
       </c>
       <c r="T41" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="U41" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W41" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X41" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y41" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z41" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA41" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB41" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC41" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD41" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE41" t="n">
         <v>1000</v>
       </c>
       <c r="AF41" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG41" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH41" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI41" t="n">
         <v>1000</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK41" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL41" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM41" t="n">
         <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO41" t="n">
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.03</v>
+        <v>2.12</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.03</v>
+        <v>2.16</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.03</v>
+        <v>2.24</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.05</v>
+        <v>2.16</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.05</v>
+        <v>2.4</v>
       </c>
       <c r="BH41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -11017,19 +11017,19 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="G42" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="H42" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I42" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J42" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K42" t="n">
         <v>4.3</v>
@@ -11041,19 +11041,19 @@
         <v>1.07</v>
       </c>
       <c r="N42" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O42" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P42" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R42" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S42" t="n">
         <v>3.55</v>
@@ -11080,7 +11080,7 @@
         <v>60</v>
       </c>
       <c r="AA42" t="n">
-        <v>190</v>
+        <v>900</v>
       </c>
       <c r="AB42" t="n">
         <v>11</v>
@@ -11092,7 +11092,7 @@
         <v>28</v>
       </c>
       <c r="AE42" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AF42" t="n">
         <v>13</v>
@@ -11104,7 +11104,7 @@
         <v>27</v>
       </c>
       <c r="AI42" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AJ42" t="n">
         <v>21</v>
@@ -11116,13 +11116,13 @@
         <v>44</v>
       </c>
       <c r="AM42" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AN42" t="n">
         <v>13.5</v>
       </c>
       <c r="AO42" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AP42" t="n">
         <v>10.5</v>
@@ -11182,7 +11182,7 @@
         <v>3.35</v>
       </c>
       <c r="BI42" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="BJ42" t="n">
         <v>11</v>
@@ -11194,7 +11194,7 @@
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN42" t="n">
         <v>4.2</v>
@@ -11203,10 +11203,10 @@
         <v>3.3</v>
       </c>
       <c r="BP42" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ42" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR42" t="n">
         <v>1000</v>
@@ -11224,23 +11224,23 @@
         <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX42" t="n">
         <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ42" t="n">
         <v>1000</v>
       </c>
       <c r="CA42" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G43" t="n">
         <v>1.72</v>
@@ -11283,7 +11283,7 @@
         <v>7</v>
       </c>
       <c r="J43" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K43" t="n">
         <v>4.5</v>
@@ -11316,13 +11316,13 @@
         <v>1.8</v>
       </c>
       <c r="U43" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V43" t="n">
         <v>1.16</v>
       </c>
       <c r="W43" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X43" t="n">
         <v>20</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G44" t="n">
         <v>1.69</v>
@@ -11555,10 +11555,10 @@
         <v>1.21</v>
       </c>
       <c r="P44" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R44" t="n">
         <v>1.5</v>
@@ -11567,10 +11567,10 @@
         <v>2.54</v>
       </c>
       <c r="T44" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U44" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V44" t="n">
         <v>1.17</v>
@@ -11687,68 +11687,68 @@
         <v>55</v>
       </c>
       <c r="BH44" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI44" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ44" t="n">
         <v>10.5</v>
       </c>
       <c r="BK44" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BL44" t="n">
         <v>1000</v>
       </c>
       <c r="BM44" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BN44" t="n">
         <v>4.6</v>
       </c>
       <c r="BO44" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP44" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ44" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BR44" t="n">
         <v>23</v>
       </c>
       <c r="BS44" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BT44" t="n">
         <v>10.5</v>
       </c>
       <c r="BU44" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV44" t="n">
         <v>50</v>
       </c>
       <c r="BW44" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX44" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY44" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ44" t="n">
         <v>15.5</v>
       </c>
       <c r="CA44" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -11779,13 +11779,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="G45" t="n">
         <v>2.56</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I45" t="n">
         <v>3.95</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -860,7 +860,7 @@
         <v>1.17</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>1.85</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
         <v>15</v>
@@ -893,7 +893,7 @@
         <v>1.33</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
         <v>1.05</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>2.46</v>
       </c>
       <c r="G3" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="H3" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="I3" t="n">
         <v>3.3</v>
@@ -1129,13 +1129,13 @@
         <v>3.55</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.34</v>
@@ -1153,16 +1153,16 @@
         <v>3.55</v>
       </c>
       <c r="T3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
         <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X3" t="n">
         <v>21</v>
@@ -1177,13 +1177,13 @@
         <v>280</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="AE3" t="n">
         <v>90</v>
@@ -1195,7 +1195,7 @@
         <v>17.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AI3" t="n">
         <v>250</v>
@@ -1219,58 +1219,58 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AX3" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="AY3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BA3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC3" t="n">
         <v>13.5</v>
       </c>
-      <c r="BA3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>13</v>
-      </c>
       <c r="BD3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>4.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I4" t="n">
         <v>2.14</v>
@@ -1383,7 +1383,7 @@
         <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
@@ -1398,7 +1398,7 @@
         <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
         <v>1.3</v>
@@ -1431,13 +1431,13 @@
         <v>27</v>
       </c>
       <c r="AB4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
         <v>25</v>
@@ -1446,7 +1446,7 @@
         <v>38</v>
       </c>
       <c r="AG4" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH4" t="n">
         <v>21</v>
@@ -1479,52 +1479,52 @@
         <v>7.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AS4" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AT4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>17</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="BA4" t="n">
         <v>21</v>
       </c>
-      <c r="AY4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BB4" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC4" t="n">
         <v>40</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>9.800000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BH4" t="n">
         <v>3.35</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -1637,13 +1637,13 @@
         <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O5" t="n">
         <v>1.43</v>
@@ -1652,19 +1652,19 @@
         <v>1.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>1.05</v>
+        <v>3.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U5" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V5" t="n">
         <v>1.6</v>
@@ -1673,10 +1673,10 @@
         <v>1.36</v>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>44</v>
       </c>
       <c r="Z5" t="n">
         <v>970</v>
@@ -1685,10 +1685,10 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AC5" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
         <v>970</v>
@@ -1736,10 +1736,10 @@
         <v>5.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.88</v>
+        <v>5.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AU5" t="n">
         <v>3.8</v>
@@ -1748,37 +1748,37 @@
         <v>4.7</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.74</v>
+        <v>4.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.96</v>
+        <v>5.9</v>
       </c>
       <c r="AY5" t="n">
         <v>5.1</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.58</v>
+        <v>4.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.68</v>
+        <v>3.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.36</v>
+        <v>2.94</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.76</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="n">
         <v>3.05</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G6" t="n">
         <v>1.72</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
         <v>7.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.25</v>
@@ -1912,7 +1912,7 @@
         <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="T6" t="n">
         <v>1.67</v>
@@ -1921,7 +1921,7 @@
         <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W6" t="n">
         <v>2.38</v>
@@ -1951,7 +1951,7 @@
         <v>80</v>
       </c>
       <c r="AF6" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG6" t="n">
         <v>970</v>
@@ -1987,10 +1987,10 @@
         <v>5.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.26</v>
+        <v>4.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="AT6" t="n">
         <v>6.2</v>
@@ -2002,7 +2002,7 @@
         <v>5.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.24</v>
+        <v>2.56</v>
       </c>
       <c r="AX6" t="n">
         <v>6.2</v>
@@ -2014,7 +2014,7 @@
         <v>5.1</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.24</v>
+        <v>2.54</v>
       </c>
       <c r="BB6" t="n">
         <v>4.8</v>
@@ -2023,22 +2023,22 @@
         <v>4.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.78</v>
+        <v>5.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.38</v>
+        <v>4.5</v>
       </c>
       <c r="BF6" t="n">
         <v>3.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.24</v>
+        <v>2.54</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
         <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R7" t="n">
         <v>1.57</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.67</v>
       </c>
       <c r="G8" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H8" t="n">
         <v>4</v>
@@ -2420,7 +2420,7 @@
         <v>1.61</v>
       </c>
       <c r="S8" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T8" t="n">
         <v>1.59</v>
@@ -2501,7 +2501,7 @@
         <v>7.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
         <v>5.8</v>
@@ -2513,7 +2513,7 @@
         <v>7</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AY8" t="n">
         <v>6.2</v>
@@ -2540,7 +2540,7 @@
         <v>4</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH8" t="n">
         <v>4.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -2638,16 +2638,16 @@
         <v>2.66</v>
       </c>
       <c r="G9" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="H9" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K9" t="n">
         <v>3.7</v>
@@ -2677,19 +2677,19 @@
         <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U9" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X9" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y9" t="n">
         <v>970</v>
@@ -2704,7 +2704,7 @@
         <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD9" t="n">
         <v>970</v>
@@ -2737,61 +2737,61 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="AO9" t="n">
-        <v>46</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AR9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT9" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>4.4</v>
       </c>
       <c r="AU9" t="n">
         <v>5.1</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AW9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC9" t="n">
         <v>5.7</v>
       </c>
-      <c r="AX9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY9" t="n">
+      <c r="BD9" t="n">
         <v>4.5</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BE9" t="n">
-        <v>2.58</v>
+        <v>4.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="BG9" t="n">
         <v>3.55</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         <v>2.66</v>
       </c>
       <c r="I10" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
         <v>3.55</v>
@@ -2937,7 +2937,7 @@
         <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W10" t="n">
         <v>1.57</v>
@@ -3006,16 +3006,16 @@
         <v>6</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AU10" t="n">
         <v>4.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AW10" t="n">
         <v>6.6</v>
@@ -3024,7 +3024,7 @@
         <v>5.9</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AZ10" t="n">
         <v>5.5</v>
@@ -3042,13 +3042,13 @@
         <v>6.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.96</v>
+        <v>4.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -3143,73 +3143,73 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="G11" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="H11" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="I11" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K11" t="n">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N11" t="n">
         <v>1.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P11" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="R11" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="S11" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="U11" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="W11" t="n">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="X11" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Y11" t="n">
         <v>110</v>
       </c>
       <c r="Z11" t="n">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
         <v>42</v>
@@ -3227,103 +3227,103 @@
         <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AI11" t="n">
         <v>190</v>
       </c>
       <c r="AJ11" t="n">
-        <v>180</v>
+        <v>970</v>
       </c>
       <c r="AK11" t="n">
         <v>970</v>
       </c>
       <c r="AL11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM11" t="n">
         <v>75</v>
       </c>
-      <c r="AM11" t="n">
-        <v>95</v>
-      </c>
       <c r="AN11" t="n">
-        <v>4.3</v>
+        <v>15</v>
       </c>
       <c r="AO11" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AS11" t="n">
         <v>4.2</v>
       </c>
       <c r="AT11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY11" t="n">
         <v>4.6</v>
       </c>
-      <c r="AU11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC11" t="n">
         <v>5.3</v>
       </c>
-      <c r="AW11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD11" t="n">
-        <v>5.3</v>
+        <v>3.05</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.9</v>
+        <v>2.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.7</v>
+        <v>17</v>
       </c>
       <c r="BO11" t="n">
         <v>3.15</v>
@@ -3332,25 +3332,25 @@
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.79</v>
+        <v>2.74</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.92</v>
+        <v>2.98</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
@@ -3362,11 +3362,11 @@
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>2.3</v>
       </c>
       <c r="G12" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H12" t="n">
         <v>3.15</v>
@@ -3415,7 +3415,7 @@
         <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
@@ -3424,7 +3424,7 @@
         <v>3.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P12" t="n">
         <v>1.71</v>
@@ -3499,10 +3499,10 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="AO12" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
         <v>9</v>
@@ -3559,10 +3559,10 @@
         <v>2.58</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
@@ -3577,10 +3577,10 @@
         <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
@@ -3595,10 +3595,10 @@
         <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -3654,19 +3654,19 @@
         <v>4.4</v>
       </c>
       <c r="G13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H13" t="n">
         <v>1.95</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L13" t="n">
         <v>1.55</v>
@@ -3675,16 +3675,16 @@
         <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O13" t="n">
         <v>1.52</v>
       </c>
       <c r="P13" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R13" t="n">
         <v>1.19</v>
@@ -3699,7 +3699,7 @@
         <v>1.73</v>
       </c>
       <c r="V13" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W13" t="n">
         <v>1.24</v>
@@ -3717,7 +3717,7 @@
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC13" t="n">
         <v>8</v>
@@ -3753,31 +3753,31 @@
         <v>240</v>
       </c>
       <c r="AN13" t="n">
-        <v>160</v>
+        <v>600</v>
       </c>
       <c r="AO13" t="n">
-        <v>26</v>
+        <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>5.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="AS13" t="n">
         <v>6.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU13" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="AW13" t="n">
         <v>7</v>
@@ -3786,37 +3786,37 @@
         <v>7.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.8</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC13" t="n">
         <v>8.6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>8.4</v>
       </c>
       <c r="BD13" t="n">
         <v>8.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.8</v>
+        <v>18.5</v>
       </c>
       <c r="BH13" t="n">
         <v>2.82</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ13" t="n">
         <v>12.5</v>
@@ -3840,19 +3840,19 @@
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT13" t="n">
         <v>4.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G14" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="H14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I14" t="n">
         <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K14" t="n">
         <v>3.95</v>
@@ -3932,7 +3932,7 @@
         <v>3.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P14" t="n">
         <v>1.77</v>
@@ -3959,31 +3959,31 @@
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z14" t="n">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="AA14" t="n">
-        <v>900</v>
+        <v>260</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AE14" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF14" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AG14" t="n">
         <v>19</v>
@@ -3992,79 +3992,79 @@
         <v>28</v>
       </c>
       <c r="AI14" t="n">
-        <v>450</v>
+        <v>160</v>
       </c>
       <c r="AJ14" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL14" t="n">
-        <v>290</v>
+        <v>50</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP14" t="n">
         <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AT14" t="n">
         <v>6.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.5</v>
+        <v>22</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AX14" t="n">
         <v>4.9</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB14" t="n">
         <v>8.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.8</v>
+        <v>38</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH14" t="n">
         <v>3.15</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -4159,91 +4159,91 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G15" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="H15" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.28</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P15" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="R15" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S15" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="T15" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="U15" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="X15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y15" t="n">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="Z15" t="n">
         <v>65</v>
       </c>
       <c r="AA15" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC15" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AF15" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG15" t="n">
         <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI15" t="n">
         <v>150</v>
@@ -4258,10 +4258,10 @@
         <v>85</v>
       </c>
       <c r="AM15" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO15" t="n">
         <v>220</v>
@@ -4270,85 +4270,85 @@
         <v>15</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT15" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV15" t="n">
         <v>11.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BB15" t="n">
         <v>20</v>
       </c>
       <c r="BC15" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH15" t="n">
         <v>4.2</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ15" t="n">
         <v>9.4</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR15" t="n">
         <v>25</v>
@@ -4357,13 +4357,13 @@
         <v>7.2</v>
       </c>
       <c r="BT15" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BV15" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
         <v>7.6</v>
@@ -4378,11 +4378,11 @@
         <v>18.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G16" t="n">
         <v>2.64</v>
@@ -4521,7 +4521,7 @@
         <v>15</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AQ16" t="n">
         <v>14.5</v>
@@ -4530,7 +4530,7 @@
         <v>17.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AT16" t="n">
         <v>14</v>
@@ -4551,13 +4551,13 @@
         <v>9.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="BA16" t="n">
         <v>19.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BC16" t="n">
         <v>16.5</v>
@@ -4566,7 +4566,7 @@
         <v>19</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BF16" t="n">
         <v>8.199999999999999</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -4667,25 +4667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="H17" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="J17" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="K17" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="M17" t="n">
         <v>1.01</v>
@@ -4694,91 +4694,91 @@
         <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P17" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="R17" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="S17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="W17" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="X17" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Y17" t="n">
         <v>160</v>
       </c>
       <c r="Z17" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AA17" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="AB17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF17" t="n">
         <v>22</v>
       </c>
-      <c r="AD17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>21</v>
-      </c>
       <c r="AG17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL17" t="n">
         <v>20</v>
       </c>
-      <c r="AI17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>21</v>
-      </c>
       <c r="AM17" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AN17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP17" t="n">
         <v>3.05</v>
       </c>
-      <c r="AO17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR17" t="n">
         <v>4.2</v>
@@ -4787,28 +4787,28 @@
         <v>4.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.46</v>
+        <v>6.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB17" t="n">
         <v>6.2</v>
@@ -4817,70 +4817,70 @@
         <v>5.7</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.56</v>
+        <v>7.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH17" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BI17" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BJ17" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL17" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BM17" t="n">
         <v>8.6</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BP17" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BR17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BS17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BT17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV17" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BX17" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BY17" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -4954,13 +4954,13 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="R18" t="n">
         <v>1.94</v>
       </c>
       <c r="S18" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="T18" t="n">
         <v>1.39</v>
@@ -5020,7 +5020,7 @@
         <v>24</v>
       </c>
       <c r="AM18" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
         <v>7.8</v>
@@ -5035,13 +5035,13 @@
         <v>6.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU18" t="n">
         <v>5.8</v>
@@ -5050,10 +5050,10 @@
         <v>5.7</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY18" t="n">
         <v>5.3</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -5184,16 +5184,16 @@
         <v>1.83</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J19" t="n">
         <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M19" t="n">
         <v>1.02</v>
@@ -5202,28 +5202,28 @@
         <v>1.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="R19" t="n">
         <v>1.97</v>
       </c>
       <c r="S19" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="T19" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="U19" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W19" t="n">
         <v>1.32</v>
@@ -5247,10 +5247,10 @@
         <v>24</v>
       </c>
       <c r="AD19" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AE19" t="n">
-        <v>65</v>
+        <v>970</v>
       </c>
       <c r="AF19" t="n">
         <v>95</v>
@@ -5262,7 +5262,7 @@
         <v>970</v>
       </c>
       <c r="AI19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ19" t="n">
         <v>900</v>
@@ -5274,121 +5274,121 @@
         <v>85</v>
       </c>
       <c r="AM19" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AN19" t="n">
         <v>970</v>
       </c>
       <c r="AO19" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="AP19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>4.7</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU19" t="n">
+      <c r="BA19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ19" t="n">
         <v>3.85</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
         <v>3.85</v>
       </c>
-      <c r="AW19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB19" t="n">
+      <c r="BT19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW19" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>970</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
         <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q21" t="n">
         <v>1.71</v>
@@ -5734,7 +5734,7 @@
         <v>1.17</v>
       </c>
       <c r="W21" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="X21" t="n">
         <v>20</v>
@@ -5755,7 +5755,7 @@
         <v>10.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE21" t="n">
         <v>320</v>
@@ -5797,10 +5797,10 @@
         <v>17</v>
       </c>
       <c r="AR21" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="AS21" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT21" t="n">
         <v>7.4</v>
@@ -5809,10 +5809,10 @@
         <v>8.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
         <v>8.800000000000001</v>
@@ -5824,25 +5824,25 @@
         <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BC21" t="n">
         <v>14</v>
       </c>
       <c r="BD21" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF21" t="n">
         <v>7</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BH21" t="n">
         <v>4</v>
@@ -5866,7 +5866,7 @@
         <v>4.5</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP21" t="n">
         <v>11</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -6069,7 +6069,7 @@
         <v>12.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AY22" t="n">
         <v>17</v>
@@ -6084,7 +6084,7 @@
         <v>6.6</v>
       </c>
       <c r="BC22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD22" t="n">
         <v>6.2</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -6194,13 +6194,13 @@
         <v>1.4</v>
       </c>
       <c r="G23" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="H23" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="I23" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J23" t="n">
         <v>5.2</v>
@@ -6242,7 +6242,7 @@
         <v>1.12</v>
       </c>
       <c r="W23" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="X23" t="n">
         <v>38</v>
@@ -6260,7 +6260,7 @@
         <v>13.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>26</v>
+        <v>16.5</v>
       </c>
       <c r="AD23" t="n">
         <v>80</v>
@@ -6281,10 +6281,10 @@
         <v>320</v>
       </c>
       <c r="AJ23" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AK23" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AL23" t="n">
         <v>32</v>
@@ -6305,10 +6305,10 @@
         <v>18</v>
       </c>
       <c r="AR23" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT23" t="n">
         <v>10</v>
@@ -6320,7 +6320,7 @@
         <v>14.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX23" t="n">
         <v>8.800000000000001</v>
@@ -6332,7 +6332,7 @@
         <v>16</v>
       </c>
       <c r="BA23" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB23" t="n">
         <v>10</v>
@@ -6344,7 +6344,7 @@
         <v>20</v>
       </c>
       <c r="BE23" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF23" t="n">
         <v>4</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G24" t="n">
         <v>3.55</v>
@@ -6457,7 +6457,7 @@
         <v>2.12</v>
       </c>
       <c r="J24" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="K24" t="n">
         <v>5.4</v>
@@ -6466,31 +6466,31 @@
         <v>1.19</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N24" t="n">
         <v>1.1</v>
       </c>
       <c r="O24" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="P24" t="n">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="R24" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="S24" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="T24" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="U24" t="n">
-        <v>1.11</v>
+        <v>2.88</v>
       </c>
       <c r="V24" t="n">
         <v>1.89</v>
@@ -6499,13 +6499,13 @@
         <v>1.4</v>
       </c>
       <c r="X24" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Y24" t="n">
         <v>22</v>
       </c>
       <c r="Z24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA24" t="n">
         <v>28</v>
@@ -6514,7 +6514,7 @@
         <v>27</v>
       </c>
       <c r="AC24" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AD24" t="n">
         <v>13</v>
@@ -6523,139 +6523,139 @@
         <v>19</v>
       </c>
       <c r="AF24" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG24" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AH24" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ24" t="n">
         <v>65</v>
       </c>
       <c r="AK24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL24" t="n">
         <v>32</v>
       </c>
       <c r="AM24" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AN24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO24" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AP24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY24" t="n">
         <v>5.4</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AZ24" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BB24" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF24" t="n">
         <v>5.3</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI24" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK24" t="n">
         <v>1.01</v>
       </c>
       <c r="BL24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BM24" t="n">
         <v>1.01</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO24" t="n">
         <v>1.01</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ24" t="n">
         <v>1.01</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS24" t="n">
         <v>1.01</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU24" t="n">
         <v>1.01</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW24" t="n">
         <v>1.01</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BY24" t="n">
         <v>1.01</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -6702,16 +6702,16 @@
         <v>1.43</v>
       </c>
       <c r="G25" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H25" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="J25" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K25" t="n">
         <v>7</v>
@@ -6720,10 +6720,10 @@
         <v>1.37</v>
       </c>
       <c r="M25" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
         <v>1.41</v>
@@ -6732,46 +6732,46 @@
         <v>1.54</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R25" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T25" t="n">
-        <v>1.11</v>
+        <v>2.34</v>
       </c>
       <c r="U25" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="V25" t="n">
         <v>1.1</v>
       </c>
       <c r="W25" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="X25" t="n">
         <v>90</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
@@ -6783,10 +6783,10 @@
         <v>36</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AJ25" t="n">
         <v>900</v>
@@ -6795,70 +6795,70 @@
         <v>65</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>2.94</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>2.48</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.19</v>
+        <v>4.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.76</v>
+        <v>2.26</v>
       </c>
       <c r="G26" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="H26" t="n">
-        <v>1.93</v>
+        <v>2.74</v>
       </c>
       <c r="I26" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="J26" t="n">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6977,28 +6977,28 @@
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>2.78</v>
+        <v>1.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q26" t="n">
         <v>1.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="S26" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T26" t="n">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="U26" t="n">
-        <v>1.11</v>
+        <v>2.52</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
@@ -7007,112 +7007,112 @@
         <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA26" t="n">
         <v>900</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ26" t="n">
         <v>900</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="G27" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="H27" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="I27" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="J27" t="n">
         <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -7234,139 +7234,139 @@
         <v>1.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="P27" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="R27" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S27" t="n">
-        <v>1.07</v>
+        <v>1.54</v>
       </c>
       <c r="T27" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="U27" t="n">
-        <v>1.11</v>
+        <v>3.55</v>
       </c>
       <c r="V27" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="W27" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA27" t="n">
-        <v>900</v>
+        <v>46</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AJ27" t="n">
-        <v>900</v>
+        <v>44</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.05</v>
+        <v>3.8</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -7485,7 +7485,7 @@
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
         <v>1.26</v>
@@ -7518,7 +7518,7 @@
         <v>21</v>
       </c>
       <c r="Y28" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z28" t="n">
         <v>30</v>
@@ -7557,10 +7557,10 @@
         <v>25</v>
       </c>
       <c r="AL28" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AM28" t="n">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AN28" t="n">
         <v>14.5</v>
@@ -7575,10 +7575,10 @@
         <v>13</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT28" t="n">
         <v>9.6</v>
@@ -7590,7 +7590,7 @@
         <v>12.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX28" t="n">
         <v>12.5</v>
@@ -7602,25 +7602,25 @@
         <v>12.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="BC28" t="n">
         <v>19</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF28" t="n">
         <v>11.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BH28" t="n">
         <v>3.9</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
         <v>2.46</v>
       </c>
       <c r="G29" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H29" t="n">
         <v>2.9</v>
@@ -7769,13 +7769,13 @@
         <v>1.58</v>
       </c>
       <c r="X29" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y29" t="n">
         <v>13.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA29" t="n">
         <v>55</v>
@@ -7787,19 +7787,19 @@
         <v>9</v>
       </c>
       <c r="AD29" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE29" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG29" t="n">
         <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI29" t="n">
         <v>55</v>
@@ -7808,16 +7808,16 @@
         <v>40</v>
       </c>
       <c r="AK29" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL29" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM29" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO29" t="n">
         <v>38</v>
@@ -7832,7 +7832,7 @@
         <v>15.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT29" t="n">
         <v>8.199999999999999</v>
@@ -7844,7 +7844,7 @@
         <v>10</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="AX29" t="n">
         <v>13</v>
@@ -7856,25 +7856,25 @@
         <v>13</v>
       </c>
       <c r="BA29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF29" t="n">
         <v>18.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH29" t="n">
         <v>3.45</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -7969,166 +7969,166 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="G30" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I30" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J30" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K30" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="L30" t="n">
         <v>1.42</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="O30" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="P30" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R30" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T30" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="U30" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V30" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W30" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="X30" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA30" t="n">
         <v>900</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AJ30" t="n">
         <v>900</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.03</v>
+        <v>2.12</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.03</v>
+        <v>2.28</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.05</v>
+        <v>4.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.05</v>
+        <v>1.92</v>
       </c>
       <c r="BH30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
         <v>1.95</v>
       </c>
       <c r="H31" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I31" t="n">
         <v>7.8</v>
@@ -8241,7 +8241,7 @@
         <v>3.55</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M31" t="n">
         <v>1.15</v>
@@ -8277,13 +8277,13 @@
         <v>2.04</v>
       </c>
       <c r="X31" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z31" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AA31" t="n">
         <v>340</v>
@@ -8292,13 +8292,13 @@
         <v>5.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD31" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AE31" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AF31" t="n">
         <v>9.4</v>
@@ -8307,10 +8307,10 @@
         <v>13.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AI31" t="n">
-        <v>300</v>
+        <v>540</v>
       </c>
       <c r="AJ31" t="n">
         <v>23</v>
@@ -8319,134 +8319,134 @@
         <v>36</v>
       </c>
       <c r="AL31" t="n">
-        <v>120</v>
+        <v>460</v>
       </c>
       <c r="AM31" t="n">
         <v>570</v>
       </c>
       <c r="AN31" t="n">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="AO31" t="n">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="AP31" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AQ31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>16</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BN31" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC31" t="n">
+      <c r="BO31" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU31" t="n">
         <v>5</v>
       </c>
-      <c r="BD31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI31" t="n">
+      <c r="BV31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW31" t="n">
         <v>1.96</v>
       </c>
-      <c r="BJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BP31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BR31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BT31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BV31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW31" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -8477,88 +8477,88 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.36</v>
+        <v>2.74</v>
       </c>
       <c r="G32" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="H32" t="n">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="I32" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="J32" t="n">
-        <v>2.42</v>
+        <v>2.68</v>
       </c>
       <c r="K32" t="n">
-        <v>950</v>
+        <v>3.1</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N32" t="n">
-        <v>1.94</v>
+        <v>2.24</v>
       </c>
       <c r="O32" t="n">
-        <v>1.34</v>
+        <v>1.64</v>
       </c>
       <c r="P32" t="n">
         <v>1.41</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R32" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S32" t="n">
-        <v>1.05</v>
+        <v>6.4</v>
       </c>
       <c r="T32" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="U32" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="V32" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="W32" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="X32" t="n">
-        <v>500</v>
+        <v>7.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>500</v>
+        <v>8.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AA32" t="n">
         <v>500</v>
       </c>
       <c r="AB32" t="n">
-        <v>500</v>
+        <v>8</v>
       </c>
       <c r="AC32" t="n">
-        <v>500</v>
+        <v>7.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="AE32" t="n">
         <v>500</v>
       </c>
       <c r="AF32" t="n">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="AH32" t="n">
         <v>500</v>
@@ -8570,7 +8570,7 @@
         <v>500</v>
       </c>
       <c r="AK32" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AL32" t="n">
         <v>500</v>
@@ -8585,122 +8585,122 @@
         <v>500</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH32" t="n">
-        <v>2.82</v>
+        <v>2.54</v>
       </c>
       <c r="BI32" t="n">
-        <v>1.97</v>
+        <v>2.24</v>
       </c>
       <c r="BJ32" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK32" t="n">
-        <v>1.56</v>
+        <v>6</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>1.56</v>
+        <v>2.08</v>
       </c>
       <c r="BN32" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO32" t="n">
-        <v>1.56</v>
+        <v>3.95</v>
       </c>
       <c r="BP32" t="n">
         <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>1.56</v>
+        <v>1.96</v>
       </c>
       <c r="BR32" t="n">
         <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="BT32" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU32" t="n">
-        <v>1.56</v>
+        <v>4</v>
       </c>
       <c r="BV32" t="n">
         <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="BZ32" t="n">
         <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.56</v>
+        <v>2.04</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
         <v>3.75</v>
       </c>
       <c r="L33" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="M33" t="n">
         <v>1.08</v>
@@ -8761,10 +8761,10 @@
         <v>1.37</v>
       </c>
       <c r="P33" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R33" t="n">
         <v>1.29</v>
@@ -8776,7 +8776,7 @@
         <v>1.85</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V33" t="n">
         <v>1.42</v>
@@ -8794,7 +8794,7 @@
         <v>25</v>
       </c>
       <c r="AA33" t="n">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="AB33" t="n">
         <v>11</v>
@@ -8842,13 +8842,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR33" t="n">
         <v>15</v>
       </c>
       <c r="AS33" t="n">
-        <v>40</v>
+        <v>4.9</v>
       </c>
       <c r="AT33" t="n">
         <v>8.199999999999999</v>
@@ -8860,7 +8860,7 @@
         <v>10.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX33" t="n">
         <v>11.5</v>
@@ -8872,25 +8872,25 @@
         <v>17</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF33" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BG33" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH33" t="n">
         <v>3.25</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -8985,230 +8985,230 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G34" t="n">
         <v>2.08</v>
       </c>
       <c r="H34" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="I34" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J34" t="n">
         <v>3.15</v>
       </c>
       <c r="K34" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="O34" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="P34" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="R34" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="S34" t="n">
-        <v>2.96</v>
+        <v>4.6</v>
       </c>
       <c r="T34" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="U34" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="V34" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W34" t="n">
         <v>1.92</v>
       </c>
       <c r="X34" t="n">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA34" t="n">
         <v>900</v>
       </c>
       <c r="AB34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD34" t="n">
         <v>27</v>
       </c>
-      <c r="AC34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF34" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="AG34" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ34" t="n">
         <v>900</v>
       </c>
       <c r="AK34" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.05</v>
+        <v>5.5</v>
       </c>
       <c r="BH34" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="BI34" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="BJ34" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK34" t="n">
-        <v>1.47</v>
+        <v>5.9</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>1.47</v>
+        <v>10.5</v>
       </c>
       <c r="BN34" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO34" t="n">
-        <v>1.47</v>
+        <v>3.35</v>
       </c>
       <c r="BP34" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ34" t="n">
-        <v>1.47</v>
+        <v>6.6</v>
       </c>
       <c r="BR34" t="n">
         <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>1.47</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT34" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU34" t="n">
-        <v>1.47</v>
+        <v>4.9</v>
       </c>
       <c r="BV34" t="n">
         <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>1.47</v>
+        <v>9.4</v>
       </c>
       <c r="BX34" t="n">
         <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>1.47</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ34" t="n">
         <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>1.47</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
         <v>1.99</v>
       </c>
       <c r="H35" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I35" t="n">
         <v>6.4</v>
@@ -9257,212 +9257,212 @@
         <v>3.55</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N35" t="n">
-        <v>1.1</v>
+        <v>2.38</v>
       </c>
       <c r="O35" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="P35" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="R35" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="S35" t="n">
-        <v>3.05</v>
+        <v>5.7</v>
       </c>
       <c r="T35" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="V35" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W35" t="n">
         <v>2</v>
       </c>
       <c r="X35" t="n">
-        <v>90</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA35" t="n">
         <v>900</v>
       </c>
       <c r="AB35" t="n">
-        <v>27</v>
+        <v>6.2</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE35" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF35" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AG35" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI35" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ35" t="n">
-        <v>900</v>
+        <v>24</v>
       </c>
       <c r="AK35" t="n">
         <v>65</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO35" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.05</v>
+        <v>7.6</v>
       </c>
       <c r="BH35" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="BI35" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="BJ35" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.49</v>
+        <v>6.4</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.49</v>
+        <v>2.22</v>
       </c>
       <c r="BN35" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO35" t="n">
-        <v>1.49</v>
+        <v>3.2</v>
       </c>
       <c r="BP35" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="BR35" t="n">
         <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.49</v>
+        <v>2.12</v>
       </c>
       <c r="BT35" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU35" t="n">
-        <v>1.49</v>
+        <v>5.4</v>
       </c>
       <c r="BV35" t="n">
         <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.49</v>
+        <v>2.16</v>
       </c>
       <c r="BX35" t="n">
         <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.49</v>
+        <v>2.18</v>
       </c>
       <c r="BZ35" t="n">
         <v>1000</v>
       </c>
       <c r="CA35" t="n">
-        <v>1.49</v>
+        <v>2.14</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
         <v>3.1</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="M36" t="n">
         <v>1.16</v>
@@ -9655,68 +9655,68 @@
         <v>6.2</v>
       </c>
       <c r="BH36" t="n">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="BI36" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="BJ36" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK36" t="n">
-        <v>1.56</v>
+        <v>5.8</v>
       </c>
       <c r="BL36" t="n">
         <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="BN36" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO36" t="n">
-        <v>1.56</v>
+        <v>3.35</v>
       </c>
       <c r="BP36" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ36" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="BR36" t="n">
         <v>1000</v>
       </c>
       <c r="BS36" t="n">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="BT36" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU36" t="n">
-        <v>1.56</v>
+        <v>4.3</v>
       </c>
       <c r="BV36" t="n">
         <v>1000</v>
       </c>
       <c r="BW36" t="n">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="BX36" t="n">
         <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="BZ36" t="n">
         <v>1000</v>
       </c>
       <c r="CA36" t="n">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -9747,230 +9747,230 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H37" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I37" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J37" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K37" t="n">
-        <v>500</v>
+        <v>3.8</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M37" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N37" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="O37" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="P37" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S37" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="T37" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U37" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="V37" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W37" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X37" t="n">
         <v>90</v>
       </c>
       <c r="Y37" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z37" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA37" t="n">
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC37" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD37" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE37" t="n">
         <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG37" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH37" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI37" t="n">
         <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK37" t="n">
         <v>65</v>
       </c>
       <c r="AL37" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO37" t="n">
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.05</v>
+        <v>3.3</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.05</v>
+        <v>3.5</v>
       </c>
       <c r="BH37" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="BI37" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="BJ37" t="n">
         <v>1000</v>
       </c>
       <c r="BK37" t="n">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN37" t="n">
         <v>1000</v>
       </c>
       <c r="BO37" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="BP37" t="n">
         <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>1.5</v>
+        <v>1.02</v>
       </c>
       <c r="BR37" t="n">
         <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>1.5</v>
+        <v>1.02</v>
       </c>
       <c r="BT37" t="n">
         <v>1000</v>
       </c>
       <c r="BU37" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="BV37" t="n">
         <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>1.5</v>
+        <v>1.02</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.5</v>
+        <v>1.02</v>
       </c>
       <c r="BZ37" t="n">
         <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -10001,34 +10001,34 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G38" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="H38" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="I38" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="K38" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M38" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="N38" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="O38" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="P38" t="n">
         <v>1.37</v>
@@ -10040,191 +10040,191 @@
         <v>1.12</v>
       </c>
       <c r="S38" t="n">
-        <v>1.05</v>
+        <v>3.95</v>
       </c>
       <c r="T38" t="n">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="U38" t="n">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="V38" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W38" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X38" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE38" t="n">
         <v>90</v>
       </c>
-      <c r="Y38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1000</v>
-      </c>
       <c r="AF38" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH38" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI38" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK38" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL38" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM38" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AN38" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO38" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.03</v>
+        <v>2.84</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.03</v>
+        <v>2.9</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.05</v>
+        <v>4.1</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH38" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="BI38" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="BJ38" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK38" t="n">
-        <v>1.57</v>
+        <v>5.6</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="BN38" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO38" t="n">
-        <v>1.57</v>
+        <v>3.5</v>
       </c>
       <c r="BP38" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="BR38" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS38" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="BT38" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.57</v>
+        <v>4</v>
       </c>
       <c r="BV38" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW38" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="BX38" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="BZ38" t="n">
         <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -10255,100 +10255,100 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="G39" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="H39" t="n">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="I39" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="K39" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="L39" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N39" t="n">
-        <v>1.1</v>
+        <v>2.16</v>
       </c>
       <c r="O39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V39" t="n">
         <v>1.34</v>
       </c>
-      <c r="P39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.3</v>
-      </c>
       <c r="W39" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="X39" t="n">
         <v>90</v>
       </c>
       <c r="Y39" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z39" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA39" t="n">
         <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE39" t="n">
         <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG39" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI39" t="n">
         <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK39" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL39" t="n">
         <v>1000</v>
@@ -10357,128 +10357,128 @@
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO39" t="n">
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="BH39" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="BI39" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="BJ39" t="n">
         <v>1000</v>
       </c>
       <c r="BK39" t="n">
-        <v>1.56</v>
+        <v>1.02</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>1.56</v>
+        <v>1.02</v>
       </c>
       <c r="BN39" t="n">
         <v>1000</v>
       </c>
       <c r="BO39" t="n">
-        <v>1.56</v>
+        <v>3.7</v>
       </c>
       <c r="BP39" t="n">
         <v>1000</v>
       </c>
       <c r="BQ39" t="n">
-        <v>1.56</v>
+        <v>1.02</v>
       </c>
       <c r="BR39" t="n">
         <v>1000</v>
       </c>
       <c r="BS39" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BT39" t="n">
         <v>1000</v>
       </c>
       <c r="BU39" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="BV39" t="n">
         <v>1000</v>
       </c>
       <c r="BW39" t="n">
-        <v>1.56</v>
+        <v>1.02</v>
       </c>
       <c r="BX39" t="n">
         <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>1.56</v>
+        <v>1.02</v>
       </c>
       <c r="BZ39" t="n">
         <v>1000</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.56</v>
+        <v>1.02</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -10512,7 +10512,7 @@
         <v>1.86</v>
       </c>
       <c r="G40" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H40" t="n">
         <v>4.5</v>
@@ -10527,7 +10527,7 @@
         <v>4.1</v>
       </c>
       <c r="L40" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M40" t="n">
         <v>1.05</v>
@@ -10545,13 +10545,13 @@
         <v>1.74</v>
       </c>
       <c r="R40" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S40" t="n">
         <v>2.8</v>
       </c>
       <c r="T40" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U40" t="n">
         <v>2.38</v>
@@ -10575,10 +10575,10 @@
         <v>95</v>
       </c>
       <c r="AB40" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC40" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD40" t="n">
         <v>18</v>
@@ -10587,10 +10587,10 @@
         <v>55</v>
       </c>
       <c r="AF40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG40" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH40" t="n">
         <v>17</v>
@@ -10602,7 +10602,7 @@
         <v>21</v>
       </c>
       <c r="AK40" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AL40" t="n">
         <v>29</v>
@@ -10626,7 +10626,7 @@
         <v>30</v>
       </c>
       <c r="AS40" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AT40" t="n">
         <v>9.800000000000001</v>
@@ -10647,7 +10647,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ40" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA40" t="n">
         <v>46</v>
@@ -10656,7 +10656,7 @@
         <v>18</v>
       </c>
       <c r="BC40" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BD40" t="n">
         <v>25</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -10796,13 +10796,13 @@
         <v>1.74</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="R41" t="n">
         <v>1.28</v>
       </c>
       <c r="S41" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T41" t="n">
         <v>1.9</v>
@@ -10823,7 +10823,7 @@
         <v>970</v>
       </c>
       <c r="Z41" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AA41" t="n">
         <v>900</v>
@@ -10835,10 +10835,10 @@
         <v>970</v>
       </c>
       <c r="AD41" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AE41" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF41" t="n">
         <v>970</v>
@@ -10847,37 +10847,37 @@
         <v>970</v>
       </c>
       <c r="AH41" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AI41" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ41" t="n">
         <v>900</v>
       </c>
       <c r="AK41" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL41" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM41" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN41" t="n">
         <v>970</v>
       </c>
       <c r="AO41" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.12</v>
+        <v>3.85</v>
       </c>
       <c r="AQ41" t="n">
-        <v>2.16</v>
+        <v>2.56</v>
       </c>
       <c r="AR41" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AS41" t="n">
         <v>2.44</v>
@@ -10889,52 +10889,52 @@
         <v>3.4</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AW41" t="n">
         <v>2.38</v>
       </c>
       <c r="AX41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY41" t="n">
         <v>3.55</v>
       </c>
-      <c r="AY41" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AZ41" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BA41" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BB41" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="BD41" t="n">
         <v>2.34</v>
       </c>
       <c r="BE41" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BF41" t="n">
-        <v>2.16</v>
+        <v>2.56</v>
       </c>
       <c r="BG41" t="n">
         <v>2.4</v>
       </c>
       <c r="BH41" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BI41" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BJ41" t="n">
         <v>1000</v>
       </c>
       <c r="BK41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
@@ -10946,13 +10946,13 @@
         <v>1000</v>
       </c>
       <c r="BO41" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP41" t="n">
         <v>1000</v>
       </c>
       <c r="BQ41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR41" t="n">
         <v>1000</v>
@@ -10964,13 +10964,13 @@
         <v>1000</v>
       </c>
       <c r="BU41" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BV41" t="n">
         <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -11017,7 +11017,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G42" t="n">
         <v>1.7</v>
@@ -11026,7 +11026,7 @@
         <v>6</v>
       </c>
       <c r="I42" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J42" t="n">
         <v>3.95</v>
@@ -11035,7 +11035,7 @@
         <v>4.3</v>
       </c>
       <c r="L42" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="M42" t="n">
         <v>1.07</v>
@@ -11044,19 +11044,19 @@
         <v>3.6</v>
       </c>
       <c r="O42" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P42" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R42" t="n">
         <v>1.34</v>
       </c>
       <c r="S42" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T42" t="n">
         <v>1.96</v>
@@ -11098,10 +11098,10 @@
         <v>13</v>
       </c>
       <c r="AG42" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI42" t="n">
         <v>700</v>
@@ -11119,22 +11119,22 @@
         <v>700</v>
       </c>
       <c r="AN42" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO42" t="n">
         <v>700</v>
       </c>
       <c r="AP42" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ42" t="n">
         <v>13.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>3.75</v>
+        <v>34</v>
       </c>
       <c r="AS42" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AT42" t="n">
         <v>5.9</v>
@@ -11146,7 +11146,7 @@
         <v>20</v>
       </c>
       <c r="AW42" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AX42" t="n">
         <v>7.4</v>
@@ -11155,10 +11155,10 @@
         <v>7.4</v>
       </c>
       <c r="AZ42" t="n">
-        <v>15.5</v>
+        <v>3.6</v>
       </c>
       <c r="BA42" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BB42" t="n">
         <v>12.5</v>
@@ -11170,25 +11170,25 @@
         <v>28</v>
       </c>
       <c r="BE42" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BF42" t="n">
         <v>8.6</v>
       </c>
       <c r="BG42" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BH42" t="n">
         <v>3.35</v>
       </c>
       <c r="BI42" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ42" t="n">
         <v>11</v>
       </c>
       <c r="BK42" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
@@ -11200,47 +11200,47 @@
         <v>4.2</v>
       </c>
       <c r="BO42" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP42" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ42" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR42" t="n">
         <v>1000</v>
       </c>
       <c r="BS42" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT42" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU42" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV42" t="n">
         <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX42" t="n">
         <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ42" t="n">
         <v>1000</v>
       </c>
       <c r="CA42" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -11295,13 +11295,13 @@
         <v>1.05</v>
       </c>
       <c r="N43" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="O43" t="n">
         <v>1.26</v>
       </c>
       <c r="P43" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q43" t="n">
         <v>1.74</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -11543,7 +11543,7 @@
         <v>5.2</v>
       </c>
       <c r="L44" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="M44" t="n">
         <v>1.04</v>
@@ -11690,7 +11690,7 @@
         <v>4.3</v>
       </c>
       <c r="BI44" t="n">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="BJ44" t="n">
         <v>10.5</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G45" t="n">
         <v>2.56</v>
@@ -11794,7 +11794,7 @@
         <v>3.25</v>
       </c>
       <c r="K45" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L45" t="n">
         <v>1.34</v>
@@ -11803,7 +11803,7 @@
         <v>1.07</v>
       </c>
       <c r="N45" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="O45" t="n">
         <v>1.3</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>
@@ -12033,22 +12033,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="G46" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="H46" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I46" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K46" t="n">
         <v>4.5</v>
-      </c>
-      <c r="I46" t="n">
-        <v>6</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K46" t="n">
-        <v>4.8</v>
       </c>
       <c r="L46" t="n">
         <v>1.37</v>
@@ -12060,7 +12060,7 @@
         <v>3.7</v>
       </c>
       <c r="O46" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P46" t="n">
         <v>1.96</v>
@@ -12075,16 +12075,16 @@
         <v>2.96</v>
       </c>
       <c r="T46" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="U46" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W46" t="n">
         <v>2.04</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W46" t="n">
-        <v>2.08</v>
       </c>
       <c r="X46" t="n">
         <v>970</v>
@@ -12093,7 +12093,7 @@
         <v>970</v>
       </c>
       <c r="Z46" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA46" t="n">
         <v>1000</v>
@@ -12105,10 +12105,10 @@
         <v>970</v>
       </c>
       <c r="AD46" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AE46" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF46" t="n">
         <v>970</v>
@@ -12120,7 +12120,7 @@
         <v>22</v>
       </c>
       <c r="AI46" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ46" t="n">
         <v>23</v>
@@ -12138,7 +12138,7 @@
         <v>970</v>
       </c>
       <c r="AO46" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP46" t="n">
         <v>1.01</v>
@@ -12195,10 +12195,10 @@
         <v>1.01</v>
       </c>
       <c r="BH46" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BI46" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BJ46" t="n">
         <v>1000</v>
@@ -12210,43 +12210,43 @@
         <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="BN46" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BO46" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP46" t="n">
         <v>1000</v>
       </c>
       <c r="BQ46" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR46" t="n">
         <v>1000</v>
       </c>
       <c r="BS46" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="BT46" t="n">
         <v>1000</v>
       </c>
       <c r="BU46" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV46" t="n">
         <v>1000</v>
       </c>
       <c r="BW46" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BX46" t="n">
         <v>1000</v>
       </c>
       <c r="BY46" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BZ46" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-05 20:39:21</t>
+          <t>2026-06-05 22:51:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -860,7 +860,7 @@
         <v>1.17</v>
       </c>
       <c r="G2" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -869,13 +869,13 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="K2" t="n">
         <v>15</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -890,10 +890,10 @@
         <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
         <v>1.05</v>
@@ -1022,55 +1022,55 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>2.46</v>
       </c>
       <c r="G3" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J3" t="n">
         <v>3.3</v>
@@ -1129,7 +1129,7 @@
         <v>3.55</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
@@ -1162,37 +1162,37 @@
         <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z3" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AA3" t="n">
         <v>280</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
         <v>90</v>
       </c>
       <c r="AF3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AG3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH3" t="n">
         <v>26</v>
@@ -1204,25 +1204,25 @@
         <v>120</v>
       </c>
       <c r="AK3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AL3" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>600</v>
+        <v>38</v>
       </c>
       <c r="AO3" t="n">
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
         <v>10.5</v>
@@ -1231,16 +1231,16 @@
         <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU3" t="n">
         <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX3" t="n">
         <v>7.8</v>
@@ -1249,7 +1249,7 @@
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BA3" t="n">
         <v>23</v>
@@ -1261,70 +1261,70 @@
         <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -1371,10 +1371,10 @@
         <v>4.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J4" t="n">
         <v>3.5</v>
@@ -1383,19 +1383,19 @@
         <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
         <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q4" t="n">
         <v>2.08</v>
@@ -1404,7 +1404,7 @@
         <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T4" t="n">
         <v>1.87</v>
@@ -1413,7 +1413,7 @@
         <v>2.06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="W4" t="n">
         <v>1.29</v>
@@ -1425,7 +1425,7 @@
         <v>9</v>
       </c>
       <c r="Z4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA4" t="n">
         <v>27</v>
@@ -1437,37 +1437,37 @@
         <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF4" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AG4" t="n">
         <v>17.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AL4" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AM4" t="n">
-        <v>140</v>
+        <v>380</v>
       </c>
       <c r="AN4" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AO4" t="n">
         <v>20</v>
@@ -1476,7 +1476,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR4" t="n">
         <v>11</v>
@@ -1488,10 +1488,10 @@
         <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AW4" t="n">
         <v>19.5</v>
@@ -1509,16 +1509,16 @@
         <v>21</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.4</v>
+        <v>29</v>
       </c>
       <c r="BC4" t="n">
         <v>40</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="BF4" t="n">
         <v>19.5</v>
@@ -1530,19 +1530,19 @@
         <v>3.35</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4" t="n">
         <v>7.8</v>
@@ -1554,13 +1554,13 @@
         <v>38</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR4" t="n">
         <v>50</v>
       </c>
       <c r="BS4" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BT4" t="n">
         <v>4.9</v>
@@ -1569,16 +1569,16 @@
         <v>3.65</v>
       </c>
       <c r="BV4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX4" t="n">
         <v>32</v>
       </c>
       <c r="BY4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -1652,13 +1652,13 @@
         <v>1.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>3.05</v>
+        <v>1.05</v>
       </c>
       <c r="T5" t="n">
         <v>1.9</v>
@@ -1685,7 +1685,7 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>65</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
         <v>14</v>
@@ -1739,7 +1739,7 @@
         <v>5.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AU5" t="n">
         <v>3.8</v>
@@ -1766,13 +1766,13 @@
         <v>3.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="BD5" t="n">
         <v>3.65</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="BF5" t="n">
         <v>3.65</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -1987,10 +1987,10 @@
         <v>5.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="AT6" t="n">
         <v>6.2</v>
@@ -2002,7 +2002,7 @@
         <v>5.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="AX6" t="n">
         <v>6.2</v>
@@ -2014,7 +2014,7 @@
         <v>5.1</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="BB6" t="n">
         <v>4.8</v>
@@ -2026,13 +2026,13 @@
         <v>5.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BF6" t="n">
         <v>3.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2044,59 +2044,59 @@
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -2133,16 +2133,16 @@
         <v>1.57</v>
       </c>
       <c r="H7" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
         <v>1.23</v>
@@ -2157,7 +2157,7 @@
         <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="Q7" t="n">
         <v>1.5</v>
@@ -2169,13 +2169,13 @@
         <v>2.16</v>
       </c>
       <c r="T7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U7" t="n">
         <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W7" t="n">
         <v>2.74</v>
@@ -2187,7 +2187,7 @@
         <v>34</v>
       </c>
       <c r="Z7" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AA7" t="n">
         <v>240</v>
@@ -2202,7 +2202,7 @@
         <v>32</v>
       </c>
       <c r="AE7" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AF7" t="n">
         <v>13</v>
@@ -2214,7 +2214,7 @@
         <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AJ7" t="n">
         <v>16.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -2387,19 +2387,19 @@
         <v>1.86</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I8" t="n">
         <v>5.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
         <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M8" t="n">
         <v>1.02</v>
@@ -2417,7 +2417,7 @@
         <v>1.54</v>
       </c>
       <c r="R8" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
         <v>2.34</v>
@@ -2507,7 +2507,7 @@
         <v>5.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AW8" t="n">
         <v>7</v>
@@ -2519,16 +2519,16 @@
         <v>6.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BA8" t="n">
         <v>7</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BD8" t="n">
         <v>6.2</v>
@@ -2546,7 +2546,7 @@
         <v>4.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>2.66</v>
       </c>
       <c r="G9" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H9" t="n">
         <v>2.76</v>
@@ -2647,10 +2647,10 @@
         <v>3.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
         <v>1.33</v>
@@ -2659,7 +2659,7 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
         <v>1.29</v>
@@ -2668,25 +2668,25 @@
         <v>1.84</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="R9" t="n">
         <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T9" t="n">
         <v>1.69</v>
       </c>
       <c r="U9" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
         <v>1.48</v>
       </c>
       <c r="W9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X9" t="n">
         <v>90</v>
@@ -2752,7 +2752,7 @@
         <v>5.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT9" t="n">
         <v>4.5</v>
@@ -2764,7 +2764,7 @@
         <v>4.7</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AX9" t="n">
         <v>5.1</v>
@@ -2776,25 +2776,25 @@
         <v>4.9</v>
       </c>
       <c r="BA9" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BB9" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="BC9" t="n">
         <v>5.7</v>
       </c>
       <c r="BD9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE9" t="n">
         <v>4.5</v>
       </c>
-      <c r="BE9" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF9" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BH9" t="n">
         <v>8.6</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         <v>2.66</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J10" t="n">
         <v>3.55</v>
@@ -2913,19 +2913,19 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S10" t="n">
         <v>2.42</v>
@@ -2937,7 +2937,7 @@
         <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W10" t="n">
         <v>1.57</v>
@@ -3000,13 +3000,13 @@
         <v>6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR10" t="n">
         <v>6</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT10" t="n">
         <v>7</v>
@@ -3042,7 +3042,7 @@
         <v>6.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BF10" t="n">
         <v>5.7</v>
@@ -3051,68 +3051,68 @@
         <v>6</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="G11" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="H11" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11" t="n">
         <v>4.4</v>
       </c>
       <c r="K11" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="L11" t="n">
         <v>1.2</v>
@@ -3173,13 +3173,13 @@
         <v>1.15</v>
       </c>
       <c r="P11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S11" t="n">
         <v>2.1</v>
@@ -3191,16 +3191,16 @@
         <v>2.36</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W11" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="X11" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Y11" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="Z11" t="n">
         <v>170</v>
@@ -3215,7 +3215,7 @@
         <v>42</v>
       </c>
       <c r="AD11" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AE11" t="n">
         <v>240</v>
@@ -3251,22 +3251,22 @@
         <v>70</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS11" t="n">
         <v>4.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AV11" t="n">
         <v>4.2</v>
@@ -3275,40 +3275,40 @@
         <v>4.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BA11" t="n">
         <v>4.2</v>
       </c>
       <c r="BB11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC11" t="n">
         <v>5.4</v>
       </c>
-      <c r="BC11" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BD11" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
@@ -3323,7 +3323,7 @@
         <v>1.49</v>
       </c>
       <c r="BN11" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BO11" t="n">
         <v>3.15</v>
@@ -3332,7 +3332,7 @@
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
         <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
@@ -3427,10 +3427,10 @@
         <v>1.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R12" t="n">
         <v>1.27</v>
@@ -3439,7 +3439,7 @@
         <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U12" t="n">
         <v>1.96</v>
@@ -3514,7 +3514,7 @@
         <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT12" t="n">
         <v>7.2</v>
@@ -3550,10 +3550,10 @@
         <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BG12" t="n">
         <v>2.58</v>
@@ -3568,16 +3568,16 @@
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO12" t="n">
         <v>4.1</v>
@@ -3586,41 +3586,41 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT12" t="n">
         <v>6.8</v>
       </c>
       <c r="BU12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -3651,46 +3651,46 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G13" t="n">
         <v>5.1</v>
       </c>
       <c r="H13" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="I13" t="n">
         <v>2.08</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="M13" t="n">
         <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P13" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R13" t="n">
         <v>1.19</v>
       </c>
       <c r="S13" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="T13" t="n">
         <v>2.16</v>
@@ -3705,10 +3705,10 @@
         <v>1.24</v>
       </c>
       <c r="X13" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Z13" t="n">
         <v>19</v>
@@ -3735,7 +3735,7 @@
         <v>38</v>
       </c>
       <c r="AH13" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="AI13" t="n">
         <v>150</v>
@@ -3750,7 +3750,7 @@
         <v>260</v>
       </c>
       <c r="AM13" t="n">
-        <v>240</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
         <v>600</v>
@@ -3759,16 +3759,16 @@
         <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="AQ13" t="n">
         <v>5.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT13" t="n">
         <v>10</v>
@@ -3777,46 +3777,46 @@
         <v>6.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AY13" t="n">
         <v>17</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BB13" t="n">
         <v>6.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>8.6</v>
+        <v>21</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE13" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="BF13" t="n">
         <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>18.5</v>
+        <v>7.2</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BJ13" t="n">
         <v>12.5</v>
@@ -3846,25 +3846,25 @@
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT13" t="n">
         <v>4.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>12.5</v>
+        <v>6.8</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -3905,28 +3905,28 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G14" t="n">
         <v>1.71</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I14" t="n">
         <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K14" t="n">
         <v>3.95</v>
       </c>
       <c r="L14" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
         <v>3.3</v>
@@ -3944,13 +3944,13 @@
         <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -3962,7 +3962,7 @@
         <v>11.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z14" t="n">
         <v>60</v>
@@ -3971,7 +3971,7 @@
         <v>260</v>
       </c>
       <c r="AB14" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC14" t="n">
         <v>9.800000000000001</v>
@@ -3995,10 +3995,10 @@
         <v>160</v>
       </c>
       <c r="AJ14" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="n">
         <v>50</v>
@@ -4010,7 +4010,7 @@
         <v>15</v>
       </c>
       <c r="AO14" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AP14" t="n">
         <v>10</v>
@@ -4019,13 +4019,13 @@
         <v>17</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU14" t="n">
         <v>7.8</v>
@@ -4034,19 +4034,19 @@
         <v>22</v>
       </c>
       <c r="AW14" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BB14" t="n">
         <v>8.4</v>
@@ -4058,19 +4058,19 @@
         <v>38</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH14" t="n">
         <v>3.15</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
@@ -4082,7 +4082,7 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>3.9</v>
+        <v>1.75</v>
       </c>
       <c r="BN14" t="n">
         <v>4.1</v>
@@ -4112,7 +4112,7 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="G15" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="H15" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="I15" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J15" t="n">
         <v>3.7</v>
@@ -4192,37 +4192,37 @@
         <v>2.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R15" t="n">
         <v>1.51</v>
       </c>
       <c r="S15" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U15" t="n">
         <v>2.42</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W15" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="X15" t="n">
         <v>24</v>
       </c>
       <c r="Y15" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="Z15" t="n">
         <v>65</v>
       </c>
       <c r="AA15" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB15" t="n">
         <v>14</v>
@@ -4231,13 +4231,13 @@
         <v>9.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE15" t="n">
         <v>95</v>
       </c>
       <c r="AF15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG15" t="n">
         <v>12</v>
@@ -4249,25 +4249,25 @@
         <v>150</v>
       </c>
       <c r="AJ15" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AK15" t="n">
         <v>46</v>
       </c>
       <c r="AL15" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AM15" t="n">
         <v>320</v>
       </c>
       <c r="AN15" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>220</v>
+        <v>28</v>
       </c>
       <c r="AP15" t="n">
-        <v>15</v>
+        <v>8.6</v>
       </c>
       <c r="AQ15" t="n">
         <v>15</v>
@@ -4276,19 +4276,19 @@
         <v>15</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT15" t="n">
         <v>11.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV15" t="n">
         <v>11.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX15" t="n">
         <v>13.5</v>
@@ -4312,22 +4312,22 @@
         <v>15</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BF15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG15" t="n">
         <v>10</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>10.5</v>
       </c>
       <c r="BH15" t="n">
         <v>4.2</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK15" t="n">
         <v>4.9</v>
@@ -4336,31 +4336,31 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR15" t="n">
         <v>25</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4375,14 +4375,14 @@
         <v>8</v>
       </c>
       <c r="BZ15" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G16" t="n">
         <v>2.64</v>
@@ -4422,7 +4422,7 @@
         <v>2.6</v>
       </c>
       <c r="I16" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
         <v>4.1</v>
@@ -4431,7 +4431,7 @@
         <v>4.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
@@ -4443,7 +4443,7 @@
         <v>1.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="Q16" t="n">
         <v>1.44</v>
@@ -4452,7 +4452,7 @@
         <v>1.78</v>
       </c>
       <c r="S16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T16" t="n">
         <v>1.45</v>
@@ -4467,7 +4467,7 @@
         <v>1.61</v>
       </c>
       <c r="X16" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="Y16" t="n">
         <v>25</v>
@@ -4521,10 +4521,10 @@
         <v>15</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AQ16" t="n">
-        <v>14.5</v>
+        <v>3.7</v>
       </c>
       <c r="AR16" t="n">
         <v>17.5</v>
@@ -4533,31 +4533,31 @@
         <v>4.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>14</v>
+        <v>3.65</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>10</v>
+        <v>3.6</v>
       </c>
       <c r="AW16" t="n">
         <v>17.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>16.5</v>
+        <v>3.75</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.6</v>
+        <v>3.45</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BA16" t="n">
         <v>19.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BC16" t="n">
         <v>16.5</v>
@@ -4575,68 +4575,68 @@
         <v>9</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.08</v>
+        <v>4.5</v>
       </c>
       <c r="BJ16" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.04</v>
+        <v>6.6</v>
       </c>
       <c r="BN16" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BP16" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.91</v>
+        <v>7.2</v>
       </c>
       <c r="BR16" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.95</v>
+        <v>8</v>
       </c>
       <c r="BT16" t="n">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BV16" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.92</v>
+        <v>7.4</v>
       </c>
       <c r="BX16" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ16" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.87</v>
+        <v>6.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>1.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="H17" t="n">
         <v>4.4</v>
@@ -4685,10 +4685,10 @@
         <v>6.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
         <v>1.1</v>
@@ -4718,7 +4718,7 @@
         <v>1.2</v>
       </c>
       <c r="W17" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X17" t="n">
         <v>85</v>
@@ -4727,7 +4727,7 @@
         <v>160</v>
       </c>
       <c r="Z17" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AA17" t="n">
         <v>140</v>
@@ -4754,7 +4754,7 @@
         <v>17.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ17" t="n">
         <v>22</v>
@@ -4772,13 +4772,13 @@
         <v>3.7</v>
       </c>
       <c r="AO17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.05</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR17" t="n">
         <v>4.2</v>
@@ -4787,46 +4787,46 @@
         <v>4.2</v>
       </c>
       <c r="AT17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV17" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AW17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>6</v>
       </c>
-      <c r="AV17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW17" t="n">
+      <c r="BA17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE17" t="n">
         <v>7.6</v>
       </c>
-      <c r="AX17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BF17" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH17" t="n">
         <v>7.4</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
         <v>3.35</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
         <v>5</v>
@@ -4951,10 +4951,10 @@
         <v>1.11</v>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R18" t="n">
         <v>1.94</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
         <v>4.1</v>
       </c>
       <c r="H19" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="I19" t="n">
         <v>2.08</v>
@@ -5229,10 +5229,10 @@
         <v>1.32</v>
       </c>
       <c r="X19" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="Y19" t="n">
-        <v>46</v>
+        <v>950</v>
       </c>
       <c r="Z19" t="n">
         <v>22</v>
@@ -5241,7 +5241,7 @@
         <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AC19" t="n">
         <v>24</v>
@@ -5256,7 +5256,7 @@
         <v>95</v>
       </c>
       <c r="AG19" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AH19" t="n">
         <v>970</v>
@@ -5283,55 +5283,55 @@
         <v>29</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.9</v>
+        <v>3.25</v>
       </c>
       <c r="AQ19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY19" t="n">
         <v>5.2</v>
       </c>
-      <c r="AR19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX19" t="n">
+      <c r="AZ19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BC19" t="n">
         <v>5.8</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BD19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF19" t="n">
         <v>5.1</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>5</v>
       </c>
       <c r="BG19" t="n">
         <v>3.35</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -5429,25 +5429,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="G20" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="J20" t="n">
         <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>25</v>
+        <v>6.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="M20" t="n">
         <v>1.01</v>
@@ -5456,203 +5456,203 @@
         <v>1.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="R20" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="S20" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>3.4</v>
       </c>
       <c r="V20" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="W20" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AC20" t="n">
         <v>95</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ20" t="n">
         <v>900</v>
       </c>
       <c r="AK20" t="n">
-        <v>150</v>
+        <v>970</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.55</v>
+        <v>4.9</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BJ20" t="n">
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BT20" t="n">
         <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -5683,19 +5683,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G21" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H21" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I21" t="n">
         <v>6.8</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K21" t="n">
         <v>4.9</v>
@@ -5707,25 +5707,25 @@
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
         <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S21" t="n">
         <v>2.8</v>
       </c>
       <c r="T21" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U21" t="n">
         <v>2.02</v>
@@ -5734,10 +5734,10 @@
         <v>1.17</v>
       </c>
       <c r="W21" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y21" t="n">
         <v>24</v>
@@ -5752,7 +5752,7 @@
         <v>10</v>
       </c>
       <c r="AC21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD21" t="n">
         <v>24</v>
@@ -5773,7 +5773,7 @@
         <v>250</v>
       </c>
       <c r="AJ21" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK21" t="n">
         <v>17.5</v>
@@ -5785,13 +5785,13 @@
         <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AO21" t="n">
         <v>150</v>
       </c>
       <c r="AP21" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AQ21" t="n">
         <v>17</v>
@@ -5800,19 +5800,19 @@
         <v>16</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT21" t="n">
         <v>7.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV21" t="n">
         <v>19</v>
       </c>
       <c r="AW21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX21" t="n">
         <v>8.800000000000001</v>
@@ -5824,10 +5824,10 @@
         <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC21" t="n">
         <v>14</v>
@@ -5836,10 +5836,10 @@
         <v>16.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF21" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG21" t="n">
         <v>12</v>
@@ -5866,7 +5866,7 @@
         <v>4.5</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BP21" t="n">
         <v>11</v>
@@ -5890,7 +5890,7 @@
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -5937,100 +5937,100 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="G22" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="H22" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="J22" t="n">
         <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="S22" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="T22" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U22" t="n">
         <v>2.2</v>
       </c>
       <c r="V22" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="W22" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="X22" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
         <v>12.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AC22" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF22" t="n">
         <v>110</v>
       </c>
       <c r="AG22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AJ22" t="n">
         <v>900</v>
       </c>
       <c r="AK22" t="n">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="AL22" t="n">
         <v>250</v>
@@ -6039,70 +6039,70 @@
         <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>310</v>
+        <v>60</v>
       </c>
       <c r="AO22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AP22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ22" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR22" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU22" t="n">
         <v>7.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW22" t="n">
         <v>12.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>6.6</v>
+        <v>16.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AZ22" t="n">
         <v>14.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="BE22" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG22" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ22" t="n">
         <v>9.6</v>
@@ -6114,13 +6114,13 @@
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BO22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
@@ -6132,7 +6132,7 @@
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT22" t="n">
         <v>4.7</v>
@@ -6141,26 +6141,26 @@
         <v>3.7</v>
       </c>
       <c r="BV22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BW22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CA22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G23" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="H23" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="I23" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K23" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.21</v>
@@ -6221,31 +6221,31 @@
         <v>1.15</v>
       </c>
       <c r="P23" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="R23" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="S23" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T23" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U23" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V23" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="X23" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="Y23" t="n">
         <v>160</v>
@@ -6254,13 +6254,13 @@
         <v>450</v>
       </c>
       <c r="AA23" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AB23" t="n">
         <v>13.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AD23" t="n">
         <v>80</v>
@@ -6275,7 +6275,7 @@
         <v>11</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AI23" t="n">
         <v>320</v>
@@ -6284,7 +6284,7 @@
         <v>14</v>
       </c>
       <c r="AK23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL23" t="n">
         <v>32</v>
@@ -6293,58 +6293,58 @@
         <v>260</v>
       </c>
       <c r="AN23" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AO23" t="n">
         <v>330</v>
       </c>
       <c r="AP23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ23" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AR23" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AT23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW23" t="n">
         <v>10</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>7.4</v>
       </c>
       <c r="AX23" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY23" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA23" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BC23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE23" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>7.4</v>
       </c>
       <c r="BF23" t="n">
         <v>4</v>
@@ -6356,65 +6356,65 @@
         <v>5.1</v>
       </c>
       <c r="BI23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ23" t="n">
         <v>10</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN23" t="n">
         <v>4.5</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP23" t="n">
         <v>8.4</v>
       </c>
       <c r="BQ23" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT23" t="n">
         <v>11.5</v>
       </c>
       <c r="BU23" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ23" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="CA23" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -6451,16 +6451,16 @@
         <v>3.55</v>
       </c>
       <c r="H24" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="I24" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="J24" t="n">
         <v>4.7</v>
       </c>
       <c r="K24" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L24" t="n">
         <v>1.19</v>
@@ -6490,16 +6490,16 @@
         <v>1.4</v>
       </c>
       <c r="U24" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V24" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="W24" t="n">
         <v>1.4</v>
       </c>
       <c r="X24" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Y24" t="n">
         <v>22</v>
@@ -6529,7 +6529,7 @@
         <v>17</v>
       </c>
       <c r="AH24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI24" t="n">
         <v>24</v>
@@ -6544,10 +6544,10 @@
         <v>32</v>
       </c>
       <c r="AM24" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN24" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AO24" t="n">
         <v>7.2</v>
@@ -6556,109 +6556,109 @@
         <v>6.8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AR24" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS24" t="n">
         <v>6.2</v>
       </c>
       <c r="AT24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW24" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AX24" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY24" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BA24" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BB24" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BC24" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD24" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE24" t="n">
         <v>6.8</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BH24" t="n">
         <v>5.9</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BJ24" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BL24" t="n">
         <v>60</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BN24" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP24" t="n">
         <v>24</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR24" t="n">
         <v>25</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BT24" t="n">
         <v>6.2</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BV24" t="n">
         <v>13.5</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BX24" t="n">
         <v>19</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
         <v>3.55</v>
       </c>
       <c r="K25" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="L25" t="n">
         <v>1.37</v>
@@ -6729,7 +6729,7 @@
         <v>1.41</v>
       </c>
       <c r="P25" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="Q25" t="n">
         <v>2.12</v>
@@ -6738,7 +6738,7 @@
         <v>1.23</v>
       </c>
       <c r="S25" t="n">
-        <v>3.15</v>
+        <v>1.05</v>
       </c>
       <c r="T25" t="n">
         <v>2.34</v>
@@ -6849,7 +6849,7 @@
         <v>5.1</v>
       </c>
       <c r="BD25" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="BE25" t="n">
         <v>2.44</v>
@@ -6864,65 +6864,65 @@
         <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25" t="n">
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT25" t="n">
         <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7007,7 @@
         <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="Y26" t="n">
         <v>970</v>
@@ -7061,13 +7061,13 @@
         <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR26" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AS26" t="n">
         <v>6.2</v>
@@ -7106,77 +7106,77 @@
         <v>5.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF26" t="n">
         <v>4.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26" t="n">
         <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN26" t="n">
         <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT26" t="n">
         <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -7237,16 +7237,16 @@
         <v>1.08</v>
       </c>
       <c r="P27" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q27" t="n">
         <v>1.25</v>
       </c>
       <c r="R27" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S27" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="T27" t="n">
         <v>1.29</v>
@@ -7372,55 +7372,55 @@
         <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ27" t="n">
         <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN27" t="n">
         <v>1000</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP27" t="n">
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT27" t="n">
         <v>1000</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -7461,16 +7461,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G28" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H28" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I28" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J28" t="n">
         <v>3.55</v>
@@ -7479,13 +7479,13 @@
         <v>4.1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M28" t="n">
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
         <v>1.26</v>
@@ -7500,19 +7500,19 @@
         <v>1.43</v>
       </c>
       <c r="S28" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T28" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U28" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="V28" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W28" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="X28" t="n">
         <v>21</v>
@@ -7530,37 +7530,37 @@
         <v>13</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE28" t="n">
         <v>46</v>
       </c>
       <c r="AF28" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI28" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AJ28" t="n">
         <v>29</v>
       </c>
       <c r="AK28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL28" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AM28" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN28" t="n">
         <v>14.5</v>
@@ -7575,22 +7575,22 @@
         <v>13</v>
       </c>
       <c r="AR28" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.8</v>
+        <v>24</v>
       </c>
       <c r="AT28" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU28" t="n">
         <v>7.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="AX28" t="n">
         <v>12.5</v>
@@ -7599,31 +7599,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BC28" t="n">
         <v>19</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.3</v>
+        <v>18</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BF28" t="n">
         <v>11.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="BH28" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI28" t="n">
         <v>3.1</v>
@@ -7638,7 +7638,7 @@
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN28" t="n">
         <v>5.1</v>
@@ -7650,19 +7650,19 @@
         <v>14.5</v>
       </c>
       <c r="BQ28" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR28" t="n">
         <v>26</v>
       </c>
       <c r="BS28" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT28" t="n">
         <v>7.4</v>
       </c>
       <c r="BU28" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
@@ -7674,7 +7674,7 @@
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -7715,22 +7715,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="G29" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="H29" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="I29" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="J29" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K29" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L29" t="n">
         <v>1.41</v>
@@ -7745,13 +7745,13 @@
         <v>1.34</v>
       </c>
       <c r="P29" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q29" t="n">
         <v>1.98</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
         <v>3.55</v>
@@ -7763,61 +7763,61 @@
         <v>2.1</v>
       </c>
       <c r="V29" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W29" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="X29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y29" t="n">
         <v>13.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA29" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AB29" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE29" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AF29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH29" t="n">
         <v>18</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>18.5</v>
       </c>
       <c r="AI29" t="n">
         <v>55</v>
       </c>
       <c r="AJ29" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK29" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL29" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM29" t="n">
         <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO29" t="n">
         <v>38</v>
@@ -7826,13 +7826,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AR29" t="n">
         <v>15.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AT29" t="n">
         <v>8.199999999999999</v>
@@ -7856,7 +7856,7 @@
         <v>13</v>
       </c>
       <c r="BA29" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BB29" t="n">
         <v>14.5</v>
@@ -7865,16 +7865,16 @@
         <v>14.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF29" t="n">
         <v>18.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH29" t="n">
         <v>3.45</v>
@@ -7883,7 +7883,7 @@
         <v>2.76</v>
       </c>
       <c r="BJ29" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK29" t="n">
         <v>5</v>
@@ -7892,43 +7892,43 @@
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN29" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BO29" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ29" t="n">
         <v>6.8</v>
       </c>
       <c r="BR29" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS29" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT29" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW29" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY29" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -7969,13 +7969,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G30" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H30" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I30" t="n">
         <v>6</v>
@@ -7999,7 +7999,7 @@
         <v>1.49</v>
       </c>
       <c r="P30" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q30" t="n">
         <v>2.32</v>
@@ -8008,7 +8008,7 @@
         <v>1.2</v>
       </c>
       <c r="S30" t="n">
-        <v>2.82</v>
+        <v>1.05</v>
       </c>
       <c r="T30" t="n">
         <v>2.1</v>
@@ -8020,7 +8020,7 @@
         <v>1.22</v>
       </c>
       <c r="W30" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X30" t="n">
         <v>22</v>
@@ -8047,7 +8047,7 @@
         <v>370</v>
       </c>
       <c r="AF30" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AG30" t="n">
         <v>44</v>
@@ -8080,10 +8080,10 @@
         <v>5.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AS30" t="n">
         <v>1.92</v>
@@ -8095,10 +8095,10 @@
         <v>4.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AX30" t="n">
         <v>6.2</v>
@@ -8107,16 +8107,16 @@
         <v>6.4</v>
       </c>
       <c r="AZ30" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BB30" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="BD30" t="n">
         <v>1.92</v>
@@ -8134,65 +8134,65 @@
         <v>1000</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ30" t="n">
         <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN30" t="n">
         <v>1000</v>
       </c>
       <c r="BO30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP30" t="n">
         <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT30" t="n">
         <v>1000</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
         <v>1.73</v>
       </c>
       <c r="G31" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H31" t="n">
         <v>5.3</v>
@@ -8271,7 +8271,7 @@
         <v>1.47</v>
       </c>
       <c r="V31" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W31" t="n">
         <v>2.04</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
         <v>1.14</v>
       </c>
       <c r="S32" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="T32" t="n">
         <v>2.24</v>
@@ -8540,7 +8540,7 @@
         <v>21</v>
       </c>
       <c r="AA32" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AB32" t="n">
         <v>8</v>
@@ -8561,25 +8561,25 @@
         <v>15.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AI32" t="n">
         <v>500</v>
       </c>
       <c r="AJ32" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AK32" t="n">
         <v>55</v>
       </c>
       <c r="AL32" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AM32" t="n">
         <v>500</v>
       </c>
       <c r="AN32" t="n">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AO32" t="n">
         <v>500</v>
@@ -8594,13 +8594,13 @@
         <v>6.4</v>
       </c>
       <c r="AS32" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU32" t="n">
         <v>4.2</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>4</v>
       </c>
       <c r="AV32" t="n">
         <v>5.9</v>
@@ -8609,13 +8609,13 @@
         <v>8</v>
       </c>
       <c r="AX32" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY32" t="n">
         <v>5.8</v>
       </c>
       <c r="AZ32" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA32" t="n">
         <v>8.6</v>
@@ -8624,7 +8624,7 @@
         <v>8</v>
       </c>
       <c r="BC32" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BD32" t="n">
         <v>8.4</v>
@@ -8636,7 +8636,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG32" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH32" t="n">
         <v>2.54</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -8731,13 +8731,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G33" t="n">
         <v>2.64</v>
       </c>
       <c r="H33" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
         <v>3.35</v>
@@ -8749,25 +8749,25 @@
         <v>3.75</v>
       </c>
       <c r="L33" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="M33" t="n">
         <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O33" t="n">
         <v>1.37</v>
       </c>
       <c r="P33" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R33" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
         <v>3.9</v>
@@ -8848,7 +8848,7 @@
         <v>15</v>
       </c>
       <c r="AS33" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT33" t="n">
         <v>8.199999999999999</v>
@@ -8875,22 +8875,22 @@
         <v>4.9</v>
       </c>
       <c r="BB33" t="n">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="BC33" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="BD33" t="n">
         <v>4.9</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BH33" t="n">
         <v>3.25</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -8988,16 +8988,16 @@
         <v>1.89</v>
       </c>
       <c r="G34" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H34" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I34" t="n">
         <v>5.8</v>
       </c>
       <c r="J34" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K34" t="n">
         <v>3.6</v>
@@ -9006,7 +9006,7 @@
         <v>1.47</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N34" t="n">
         <v>2.6</v>
@@ -9018,13 +9018,13 @@
         <v>1.53</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R34" t="n">
         <v>1.19</v>
       </c>
       <c r="S34" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="T34" t="n">
         <v>2.16</v>
@@ -9045,7 +9045,7 @@
         <v>16</v>
       </c>
       <c r="Z34" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AA34" t="n">
         <v>900</v>
@@ -9057,10 +9057,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD34" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE34" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AF34" t="n">
         <v>11</v>
@@ -9072,19 +9072,19 @@
         <v>32</v>
       </c>
       <c r="AI34" t="n">
-        <v>150</v>
+        <v>540</v>
       </c>
       <c r="AJ34" t="n">
-        <v>900</v>
+        <v>42</v>
       </c>
       <c r="AK34" t="n">
         <v>29</v>
       </c>
       <c r="AL34" t="n">
-        <v>75</v>
+        <v>460</v>
       </c>
       <c r="AM34" t="n">
-        <v>270</v>
+        <v>580</v>
       </c>
       <c r="AN34" t="n">
         <v>29</v>
@@ -9093,58 +9093,58 @@
         <v>210</v>
       </c>
       <c r="AP34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU34" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ34" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS34" t="n">
+      <c r="AV34" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD34" t="n">
         <v>5.5</v>
       </c>
-      <c r="AT34" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BE34" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BF34" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BG34" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BH34" t="n">
         <v>2.82</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9272,7 @@
         <v>1.48</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="R35" t="n">
         <v>1.17</v>
@@ -9311,7 +9311,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD35" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AE35" t="n">
         <v>160</v>
@@ -9335,7 +9335,7 @@
         <v>65</v>
       </c>
       <c r="AL35" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AM35" t="n">
         <v>330</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -9547,16 +9547,16 @@
         <v>1.61</v>
       </c>
       <c r="X36" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="Y36" t="n">
         <v>10</v>
       </c>
       <c r="Z36" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AA36" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AB36" t="n">
         <v>6.4</v>
@@ -9568,7 +9568,7 @@
         <v>24</v>
       </c>
       <c r="AE36" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AF36" t="n">
         <v>14</v>
@@ -9577,82 +9577,82 @@
         <v>15.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AI36" t="n">
-        <v>200</v>
+        <v>540</v>
       </c>
       <c r="AJ36" t="n">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="AK36" t="n">
         <v>60</v>
       </c>
       <c r="AL36" t="n">
-        <v>130</v>
+        <v>460</v>
       </c>
       <c r="AM36" t="n">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AN36" t="n">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="AO36" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AP36" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="AR36" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AS36" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ36" t="n">
         <v>6</v>
       </c>
-      <c r="AT36" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW36" t="n">
+      <c r="BA36" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB36" t="n">
         <v>6</v>
       </c>
-      <c r="AX36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BC36" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BD36" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE36" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BF36" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG36" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH36" t="n">
         <v>2.4</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -9771,7 +9771,7 @@
         <v>1.11</v>
       </c>
       <c r="N37" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="O37" t="n">
         <v>1.57</v>
@@ -9804,109 +9804,109 @@
         <v>90</v>
       </c>
       <c r="Y37" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z37" t="n">
+        <v>170</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC37" t="n">
         <v>42</v>
       </c>
-      <c r="AA37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AD37" t="n">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="AE37" t="n">
         <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AG37" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AH37" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="AI37" t="n">
         <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="AK37" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AL37" t="n">
-        <v>85</v>
+        <v>210</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="AO37" t="n">
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="AQ37" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR37" t="n">
         <v>3.3</v>
       </c>
-      <c r="AR37" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AS37" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AT37" t="n">
         <v>3.5</v>
       </c>
-      <c r="AT37" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AU37" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="AV37" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="AW37" t="n">
-        <v>3.5</v>
+        <v>1.99</v>
       </c>
       <c r="AX37" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="AY37" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="AZ37" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BA37" t="n">
-        <v>3.5</v>
+        <v>1.99</v>
       </c>
       <c r="BB37" t="n">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="BC37" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.45</v>
+        <v>2.08</v>
       </c>
       <c r="BE37" t="n">
-        <v>3.55</v>
+        <v>2.08</v>
       </c>
       <c r="BF37" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="BG37" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="BH37" t="n">
         <v>3.95</v>
@@ -9924,7 +9924,7 @@
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN37" t="n">
         <v>1000</v>
@@ -9936,13 +9936,13 @@
         <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BR37" t="n">
         <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BT37" t="n">
         <v>1000</v>
@@ -9954,23 +9954,23 @@
         <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BZ37" t="n">
         <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -10007,7 +10007,7 @@
         <v>2.88</v>
       </c>
       <c r="H38" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="I38" t="n">
         <v>4.1</v>
@@ -10028,7 +10028,7 @@
         <v>2.06</v>
       </c>
       <c r="O38" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="P38" t="n">
         <v>1.37</v>
@@ -10040,7 +10040,7 @@
         <v>1.12</v>
       </c>
       <c r="S38" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="T38" t="n">
         <v>2.28</v>
@@ -10055,112 +10055,112 @@
         <v>1.53</v>
       </c>
       <c r="X38" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="Y38" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z38" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA38" t="n">
-        <v>110</v>
+        <v>420</v>
       </c>
       <c r="AB38" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AC38" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE38" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AF38" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AG38" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH38" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI38" t="n">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="AJ38" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AK38" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL38" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AM38" t="n">
         <v>350</v>
       </c>
       <c r="AN38" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AO38" t="n">
         <v>150</v>
       </c>
       <c r="AP38" t="n">
-        <v>2.84</v>
+        <v>3.7</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR38" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="AS38" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT38" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT38" t="n">
-        <v>2.86</v>
-      </c>
       <c r="AU38" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AV38" t="n">
-        <v>3.65</v>
+        <v>5.4</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AX38" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="AY38" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AZ38" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB38" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="BC38" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BE38" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="BG38" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="BH38" t="n">
         <v>2.52</v>
@@ -10220,11 +10220,11 @@
         <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -10261,7 +10261,7 @@
         <v>2.92</v>
       </c>
       <c r="H39" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="I39" t="n">
         <v>4</v>
@@ -10282,7 +10282,7 @@
         <v>2.16</v>
       </c>
       <c r="O39" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="P39" t="n">
         <v>1.4</v>
@@ -10309,49 +10309,49 @@
         <v>1.53</v>
       </c>
       <c r="X39" t="n">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="Y39" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Z39" t="n">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="AA39" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB39" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AC39" t="n">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="AD39" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE39" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AF39" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AG39" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH39" t="n">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="AI39" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AJ39" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AK39" t="n">
-        <v>55</v>
+        <v>230</v>
       </c>
       <c r="AL39" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AM39" t="n">
         <v>1000</v>
@@ -10363,58 +10363,58 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.82</v>
+        <v>5.1</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.16</v>
+        <v>2.56</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.56</v>
+        <v>3.85</v>
       </c>
       <c r="AU39" t="n">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.22</v>
+        <v>5.7</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.2</v>
+        <v>1.99</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.22</v>
+        <v>6.2</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.22</v>
+        <v>5.3</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.17</v>
+        <v>1.99</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.19</v>
+        <v>1.97</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.19</v>
+        <v>1.97</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.2</v>
+        <v>2.02</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.21</v>
+        <v>2.02</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.2</v>
+        <v>1.96</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.2</v>
+        <v>1.98</v>
       </c>
       <c r="BH39" t="n">
         <v>3.2</v>
@@ -10426,13 +10426,13 @@
         <v>1000</v>
       </c>
       <c r="BK39" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BN39" t="n">
         <v>1000</v>
@@ -10444,13 +10444,13 @@
         <v>1000</v>
       </c>
       <c r="BQ39" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BR39" t="n">
         <v>1000</v>
       </c>
       <c r="BS39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT39" t="n">
         <v>1000</v>
@@ -10462,23 +10462,23 @@
         <v>1000</v>
       </c>
       <c r="BW39" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BX39" t="n">
         <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BZ39" t="n">
         <v>1000</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
         <v>1.88</v>
       </c>
       <c r="H40" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I40" t="n">
         <v>4.7</v>
@@ -10533,28 +10533,28 @@
         <v>1.05</v>
       </c>
       <c r="N40" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O40" t="n">
         <v>1.25</v>
       </c>
       <c r="P40" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R40" t="n">
         <v>1.5</v>
       </c>
       <c r="S40" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="T40" t="n">
         <v>1.71</v>
       </c>
       <c r="U40" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V40" t="n">
         <v>1.27</v>
@@ -10566,16 +10566,16 @@
         <v>18.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z40" t="n">
         <v>38</v>
       </c>
       <c r="AA40" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB40" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC40" t="n">
         <v>9</v>
@@ -10614,19 +10614,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AO40" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP40" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ40" t="n">
         <v>18</v>
       </c>
       <c r="AR40" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS40" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AT40" t="n">
         <v>9.800000000000001</v>
@@ -10635,7 +10635,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV40" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW40" t="n">
         <v>44</v>
@@ -10647,7 +10647,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ40" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA40" t="n">
         <v>46</v>
@@ -10659,7 +10659,7 @@
         <v>17</v>
       </c>
       <c r="BD40" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE40" t="n">
         <v>65</v>
@@ -10668,25 +10668,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG40" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH40" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI40" t="n">
         <v>3.4</v>
       </c>
       <c r="BJ40" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK40" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BL40" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BN40" t="n">
         <v>4.9</v>
@@ -10698,41 +10698,41 @@
         <v>13</v>
       </c>
       <c r="BQ40" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BR40" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS40" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT40" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU40" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BV40" t="n">
         <v>34</v>
       </c>
       <c r="BW40" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX40" t="n">
         <v>40</v>
       </c>
       <c r="BY40" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ40" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CA40" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10796,7 @@
         <v>1.74</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="R41" t="n">
         <v>1.28</v>
@@ -10835,7 +10835,7 @@
         <v>970</v>
       </c>
       <c r="AD41" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE41" t="n">
         <v>700</v>
@@ -10847,7 +10847,7 @@
         <v>970</v>
       </c>
       <c r="AH41" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI41" t="n">
         <v>700</v>
@@ -10874,10 +10874,10 @@
         <v>3.85</v>
       </c>
       <c r="AQ41" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="AR41" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AS41" t="n">
         <v>2.44</v>
@@ -10889,37 +10889,37 @@
         <v>3.4</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AW41" t="n">
         <v>2.38</v>
       </c>
       <c r="AX41" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AY41" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AZ41" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BA41" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BB41" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BD41" t="n">
         <v>2.34</v>
       </c>
       <c r="BE41" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BF41" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BG41" t="n">
         <v>2.4</v>
@@ -10940,7 +10940,7 @@
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN41" t="n">
         <v>1000</v>
@@ -10958,7 +10958,7 @@
         <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT41" t="n">
         <v>1000</v>
@@ -10970,23 +10970,23 @@
         <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ41" t="n">
         <v>1000</v>
       </c>
       <c r="CA41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -11017,7 +11017,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="G42" t="n">
         <v>1.7</v>
@@ -11026,7 +11026,7 @@
         <v>6</v>
       </c>
       <c r="I42" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J42" t="n">
         <v>3.95</v>
@@ -11035,7 +11035,7 @@
         <v>4.3</v>
       </c>
       <c r="L42" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="M42" t="n">
         <v>1.07</v>
@@ -11050,7 +11050,7 @@
         <v>1.9</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
         <v>1.34</v>
@@ -11194,7 +11194,7 @@
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN42" t="n">
         <v>4.2</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -11295,7 +11295,7 @@
         <v>1.05</v>
       </c>
       <c r="N43" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O43" t="n">
         <v>1.26</v>
@@ -11325,10 +11325,10 @@
         <v>2.38</v>
       </c>
       <c r="X43" t="n">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="Y43" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="Z43" t="n">
         <v>60</v>
@@ -11343,7 +11343,7 @@
         <v>11</v>
       </c>
       <c r="AD43" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AE43" t="n">
         <v>100</v>
@@ -11352,16 +11352,16 @@
         <v>12</v>
       </c>
       <c r="AG43" t="n">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="AH43" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI43" t="n">
         <v>95</v>
       </c>
       <c r="AJ43" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK43" t="n">
         <v>19.5</v>
@@ -11373,22 +11373,22 @@
         <v>120</v>
       </c>
       <c r="AN43" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO43" t="n">
         <v>110</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT43" t="n">
         <v>7</v>
@@ -11397,10 +11397,10 @@
         <v>7.4</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX43" t="n">
         <v>8</v>
@@ -11412,25 +11412,25 @@
         <v>1.03</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF43" t="n">
         <v>7</v>
       </c>
       <c r="BG43" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BH43" t="n">
         <v>3.8</v>
@@ -11448,7 +11448,7 @@
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="BN43" t="n">
         <v>11</v>
@@ -11466,7 +11466,7 @@
         <v>1000</v>
       </c>
       <c r="BS43" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="BT43" t="n">
         <v>1000</v>
@@ -11478,13 +11478,13 @@
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="BZ43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -11525,64 +11525,64 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G44" t="n">
         <v>1.69</v>
       </c>
       <c r="H44" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I44" t="n">
         <v>6.8</v>
       </c>
       <c r="J44" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K44" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L44" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M44" t="n">
         <v>1.04</v>
       </c>
       <c r="N44" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O44" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P44" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="R44" t="n">
         <v>1.5</v>
       </c>
       <c r="S44" t="n">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="T44" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="U44" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V44" t="n">
         <v>1.17</v>
       </c>
       <c r="W44" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="X44" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y44" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z44" t="n">
         <v>60</v>
@@ -11591,10 +11591,10 @@
         <v>170</v>
       </c>
       <c r="AB44" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD44" t="n">
         <v>27</v>
@@ -11615,7 +11615,7 @@
         <v>80</v>
       </c>
       <c r="AJ44" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK44" t="n">
         <v>18.5</v>
@@ -11642,7 +11642,7 @@
         <v>1.03</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT44" t="n">
         <v>8.199999999999999</v>
@@ -11654,7 +11654,7 @@
         <v>17.5</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX44" t="n">
         <v>8.4</v>
@@ -11666,7 +11666,7 @@
         <v>15</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB44" t="n">
         <v>11.5</v>
@@ -11675,22 +11675,22 @@
         <v>12</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF44" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BG44" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BH44" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI44" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="BJ44" t="n">
         <v>10.5</v>
@@ -11702,13 +11702,13 @@
         <v>1000</v>
       </c>
       <c r="BM44" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN44" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO44" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BP44" t="n">
         <v>10.5</v>
@@ -11717,7 +11717,7 @@
         <v>4.9</v>
       </c>
       <c r="BR44" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS44" t="n">
         <v>6.6</v>
@@ -11729,26 +11729,26 @@
         <v>4.9</v>
       </c>
       <c r="BV44" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW44" t="n">
         <v>7.8</v>
       </c>
       <c r="BX44" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY44" t="n">
         <v>7.8</v>
       </c>
       <c r="BZ44" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA44" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -11782,7 +11782,7 @@
         <v>2.2</v>
       </c>
       <c r="G45" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H45" t="n">
         <v>3.1</v>
@@ -11797,25 +11797,25 @@
         <v>3.95</v>
       </c>
       <c r="L45" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M45" t="n">
         <v>1.07</v>
       </c>
       <c r="N45" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="O45" t="n">
         <v>1.3</v>
       </c>
       <c r="P45" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Q45" t="n">
         <v>1.81</v>
       </c>
       <c r="R45" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S45" t="n">
         <v>3.05</v>
@@ -11824,13 +11824,13 @@
         <v>1.71</v>
       </c>
       <c r="U45" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V45" t="n">
         <v>1.34</v>
       </c>
       <c r="W45" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X45" t="n">
         <v>17</v>
@@ -11854,7 +11854,7 @@
         <v>18</v>
       </c>
       <c r="AE45" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF45" t="n">
         <v>18</v>
@@ -11866,85 +11866,85 @@
         <v>970</v>
       </c>
       <c r="AI45" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ45" t="n">
         <v>38</v>
       </c>
       <c r="AK45" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL45" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO45" t="n">
         <v>48</v>
       </c>
-      <c r="AM45" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>50</v>
-      </c>
       <c r="AP45" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AQ45" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AR45" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AS45" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AT45" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="AU45" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="AV45" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AW45" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF45" t="n">
         <v>3.95</v>
       </c>
-      <c r="AX45" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE45" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF45" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BG45" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BH45" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BI45" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="BJ45" t="n">
         <v>10.5</v>
@@ -11977,16 +11977,16 @@
         <v>6</v>
       </c>
       <c r="BT45" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU45" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV45" t="n">
         <v>1000</v>
       </c>
       <c r="BW45" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BX45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>
@@ -12036,13 +12036,13 @@
         <v>1.8</v>
       </c>
       <c r="G46" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="H46" t="n">
         <v>4.2</v>
       </c>
       <c r="I46" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J46" t="n">
         <v>3.4</v>
@@ -12063,7 +12063,7 @@
         <v>1.28</v>
       </c>
       <c r="P46" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q46" t="n">
         <v>1.83</v>
@@ -12075,16 +12075,16 @@
         <v>2.96</v>
       </c>
       <c r="T46" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U46" t="n">
         <v>2.06</v>
       </c>
       <c r="V46" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W46" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X46" t="n">
         <v>970</v>
@@ -12195,10 +12195,10 @@
         <v>1.01</v>
       </c>
       <c r="BH46" t="n">
-        <v>6.6</v>
+        <v>3.7</v>
       </c>
       <c r="BI46" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ46" t="n">
         <v>1000</v>
@@ -12210,25 +12210,25 @@
         <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BN46" t="n">
         <v>13</v>
       </c>
       <c r="BO46" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP46" t="n">
         <v>1000</v>
       </c>
       <c r="BQ46" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BR46" t="n">
         <v>1000</v>
       </c>
       <c r="BS46" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="BT46" t="n">
         <v>1000</v>
@@ -12240,13 +12240,13 @@
         <v>1000</v>
       </c>
       <c r="BW46" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BX46" t="n">
         <v>1000</v>
       </c>
       <c r="BY46" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BZ46" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-05 22:51:08</t>
+          <t>2026-06-06 01:02:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="G2" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -872,25 +872,25 @@
         <v>3.05</v>
       </c>
       <c r="K2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1</v>
+        <v>1.96</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P2" t="n">
         <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="R2" t="n">
         <v>1.28</v>
@@ -905,13 +905,13 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W2" t="n">
         <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Y2" t="n">
         <v>1000</v>
@@ -923,10 +923,10 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AC2" t="n">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -935,10 +935,10 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG2" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="AH2" t="n">
         <v>1000</v>
@@ -950,13 +950,13 @@
         <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>790</v>
       </c>
       <c r="AN2" t="n">
         <v>600</v>
@@ -965,55 +965,55 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="BG2" t="n">
         <v>1.55</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -1114,16 +1114,16 @@
         <v>2.46</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I3" t="n">
         <v>3.35</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
         <v>3.55</v>
@@ -1135,22 +1135,22 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="T3" t="n">
         <v>1.8</v>
@@ -1162,7 +1162,7 @@
         <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X3" t="n">
         <v>20</v>
@@ -1180,13 +1180,13 @@
         <v>16</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AE3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF3" t="n">
         <v>27</v>
@@ -1201,7 +1201,7 @@
         <v>250</v>
       </c>
       <c r="AJ3" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AK3" t="n">
         <v>60</v>
@@ -1213,10 +1213,10 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO3" t="n">
-        <v>600</v>
+        <v>50</v>
       </c>
       <c r="AP3" t="n">
         <v>11</v>
@@ -1243,7 +1243,7 @@
         <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
@@ -1252,10 +1252,10 @@
         <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="BB3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC3" t="n">
         <v>13.5</v>
@@ -1264,67 +1264,67 @@
         <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH3" t="n">
         <v>3.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BJ3" t="n">
         <v>10</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN3" t="n">
         <v>5.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT3" t="n">
         <v>6.6</v>
       </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BU3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV3" t="n">
         <v>28</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>4.1</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="I4" t="n">
         <v>2.12</v>
@@ -1389,34 +1389,34 @@
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T4" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U4" t="n">
         <v>2.06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X4" t="n">
         <v>13.5</v>
@@ -1437,7 +1437,7 @@
         <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AE4" t="n">
         <v>24</v>
@@ -1461,7 +1461,7 @@
         <v>60</v>
       </c>
       <c r="AL4" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="AM4" t="n">
         <v>380</v>
@@ -1470,13 +1470,13 @@
         <v>95</v>
       </c>
       <c r="AO4" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR4" t="n">
         <v>11</v>
@@ -1515,7 +1515,7 @@
         <v>40</v>
       </c>
       <c r="BD4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BE4" t="n">
         <v>20</v>
@@ -1527,58 +1527,58 @@
         <v>15.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.6</v>
+        <v>2.98</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BP4" t="n">
         <v>38</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BR4" t="n">
         <v>50</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BV4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX4" t="n">
         <v>32</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -1637,13 +1637,13 @@
         <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O5" t="n">
         <v>1.43</v>
@@ -1652,19 +1652,19 @@
         <v>1.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>1.05</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
         <v>1.9</v>
       </c>
       <c r="U5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V5" t="n">
         <v>1.6</v>
@@ -1703,7 +1703,7 @@
         <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AI5" t="n">
         <v>210</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -1873,61 +1873,61 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="G6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.72</v>
       </c>
-      <c r="H6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O6" t="n">
+      <c r="U6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.2</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.19</v>
-      </c>
       <c r="W6" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X6" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Y6" t="n">
         <v>65</v>
@@ -1945,25 +1945,25 @@
         <v>42</v>
       </c>
       <c r="AD6" t="n">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="AE6" t="n">
         <v>80</v>
       </c>
       <c r="AF6" t="n">
-        <v>40</v>
+        <v>970</v>
       </c>
       <c r="AG6" t="n">
         <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
         <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>970</v>
+        <v>44</v>
       </c>
       <c r="AK6" t="n">
         <v>970</v>
@@ -1975,22 +1975,22 @@
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AO6" t="n">
         <v>75</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="AT6" t="n">
         <v>6.2</v>
@@ -1999,10 +1999,10 @@
         <v>5.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.32</v>
+        <v>2.58</v>
       </c>
       <c r="AX6" t="n">
         <v>6.2</v>
@@ -2011,92 +2011,92 @@
         <v>5.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.41</v>
+        <v>5.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.25</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
         <v>1.23</v>
       </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>1.19</v>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -2127,88 +2127,88 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="G7" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="H7" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="I7" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P7" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="R7" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
         <v>1.14</v>
       </c>
       <c r="W7" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="X7" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="Y7" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="Z7" t="n">
         <v>160</v>
       </c>
       <c r="AA7" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB7" t="n">
         <v>13.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AE7" t="n">
         <v>230</v>
       </c>
       <c r="AF7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
         <v>26</v>
@@ -2220,7 +2220,7 @@
         <v>16.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL7" t="n">
         <v>32</v>
@@ -2235,122 +2235,122 @@
         <v>110</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT7" t="n">
         <v>4.8</v>
       </c>
-      <c r="AR7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4</v>
-      </c>
       <c r="AU7" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.95</v>
+        <v>7.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AZ7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH7" t="n">
         <v>4.6</v>
       </c>
-      <c r="BA7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BI7" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>2.86</v>
+        <v>3.75</v>
       </c>
       <c r="BP7" t="n">
         <v>9.4</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BR7" t="n">
         <v>22</v>
       </c>
       <c r="BS7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="CA7" t="n">
         <v>5.6</v>
       </c>
-      <c r="BT7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>13</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>4.7</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -2381,88 +2381,88 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="G8" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I8" t="n">
         <v>5.3</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S8" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="T8" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="U8" t="n">
         <v>2.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="X8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
         <v>55</v>
       </c>
       <c r="AF8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
         <v>18</v>
@@ -2471,10 +2471,10 @@
         <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL8" t="n">
         <v>28</v>
@@ -2486,31 +2486,31 @@
         <v>7.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AU8" t="n">
         <v>5.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW8" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AX8" t="n">
         <v>7</v>
@@ -2519,92 +2519,92 @@
         <v>6.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BD8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>5.2</v>
       </c>
       <c r="BR8" t="n">
         <v>22</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BV8" t="n">
         <v>36</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BX8" t="n">
         <v>38</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BZ8" t="n">
         <v>15</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -2635,61 +2635,61 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="H9" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="U9" t="n">
         <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="X9" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y9" t="n">
         <v>970</v>
@@ -2743,61 +2743,61 @@
         <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.7</v>
+        <v>2.76</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.3</v>
+        <v>2.94</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU9" t="n">
         <v>5.1</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AY9" t="n">
         <v>7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.9</v>
+        <v>3.5</v>
       </c>
       <c r="BB9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BC9" t="n">
         <v>5.8</v>
       </c>
-      <c r="BC9" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BD9" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
         <v>2.78</v>
@@ -2806,59 +2806,59 @@
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.71</v>
+        <v>1.19</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -2889,28 +2889,28 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="G10" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="H10" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="I10" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
         <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
         <v>4.5</v>
@@ -2919,31 +2919,31 @@
         <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="R10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.42</v>
+        <v>2.82</v>
       </c>
       <c r="T10" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="U10" t="n">
         <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="W10" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Y10" t="n">
         <v>970</v>
@@ -2994,19 +2994,19 @@
         <v>55</v>
       </c>
       <c r="AO10" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>6</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AR10" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
         <v>7</v>
@@ -3018,101 +3018,101 @@
         <v>7</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AY10" t="n">
         <v>7</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BA10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.84</v>
+        <v>1.41</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>3.35</v>
+        <v>7.6</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.72</v>
+        <v>3.05</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -3143,58 +3143,58 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1.48</v>
       </c>
-      <c r="G11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="H11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.44</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="T11" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="U11" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="V11" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W11" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="X11" t="n">
         <v>950</v>
@@ -3251,22 +3251,22 @@
         <v>70</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.15</v>
+        <v>2.56</v>
       </c>
       <c r="AQ11" t="n">
         <v>4.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="AV11" t="n">
         <v>4.2</v>
@@ -3275,13 +3275,13 @@
         <v>4.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.2</v>
+        <v>2.88</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.7</v>
+        <v>2.58</v>
       </c>
       <c r="BA11" t="n">
         <v>4.2</v>
@@ -3290,83 +3290,83 @@
         <v>5.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.4</v>
+        <v>2.86</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="BG11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
         <v>7.4</v>
       </c>
-      <c r="BH11" t="n">
-        <v>970</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>2.74</v>
-      </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.98</v>
+        <v>1.14</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>5.6</v>
+        <v>1.15</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G12" t="n">
         <v>2.58</v>
       </c>
       <c r="H12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
         <v>3.7</v>
@@ -3421,13 +3421,13 @@
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O12" t="n">
         <v>1.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q12" t="n">
         <v>2.12</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G13" t="n">
         <v>5.1</v>
       </c>
       <c r="H13" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I13" t="n">
         <v>2.08</v>
@@ -3666,19 +3666,19 @@
         <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M13" t="n">
         <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="O13" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P13" t="n">
         <v>1.56</v>
@@ -3687,13 +3687,13 @@
         <v>2.62</v>
       </c>
       <c r="R13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S13" t="n">
         <v>5.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U13" t="n">
         <v>1.73</v>
@@ -3702,28 +3702,28 @@
         <v>1.92</v>
       </c>
       <c r="W13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X13" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="n">
         <v>6.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AA13" t="n">
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AC13" t="n">
         <v>8</v>
       </c>
       <c r="AD13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE13" t="n">
         <v>65</v>
@@ -3759,16 +3759,16 @@
         <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ13" t="n">
         <v>5.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT13" t="n">
         <v>10</v>
@@ -3777,52 +3777,52 @@
         <v>6.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY13" t="n">
         <v>17</v>
       </c>
       <c r="AZ13" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BD13" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ13" t="n">
         <v>12.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3834,7 +3834,7 @@
         <v>8.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
@@ -3846,16 +3846,16 @@
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT13" t="n">
         <v>4.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW13" t="n">
         <v>6.8</v>
@@ -3864,7 +3864,7 @@
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="G14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H14" t="n">
         <v>6.8</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J14" t="n">
         <v>3.75</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L14" t="n">
         <v>1.46</v>
@@ -3929,28 +3929,28 @@
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="R14" t="n">
         <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
         <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -3968,61 +3968,61 @@
         <v>60</v>
       </c>
       <c r="AA14" t="n">
-        <v>260</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI14" t="n">
         <v>130</v>
       </c>
-      <c r="AF14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>160</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AL14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM14" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO14" t="n">
         <v>210</v>
       </c>
       <c r="AP14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>17</v>
       </c>
       <c r="AR14" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT14" t="n">
         <v>6.4</v>
@@ -4031,40 +4031,40 @@
         <v>7.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
         <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BD14" t="n">
         <v>38</v>
       </c>
       <c r="BE14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG14" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>7.6</v>
       </c>
       <c r="BH14" t="n">
         <v>3.15</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -4159,58 +4159,58 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G15" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
         <v>3.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="K15" t="n">
         <v>4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="M15" t="n">
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P15" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="R15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="T15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U15" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="X15" t="n">
         <v>24</v>
@@ -4219,7 +4219,7 @@
         <v>18</v>
       </c>
       <c r="Z15" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="AA15" t="n">
         <v>900</v>
@@ -4228,7 +4228,7 @@
         <v>14</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD15" t="n">
         <v>14.5</v>
@@ -4246,19 +4246,19 @@
         <v>16</v>
       </c>
       <c r="AI15" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AJ15" t="n">
         <v>42</v>
       </c>
       <c r="AK15" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AL15" t="n">
         <v>34</v>
       </c>
       <c r="AM15" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN15" t="n">
         <v>13.5</v>
@@ -4273,10 +4273,10 @@
         <v>15</v>
       </c>
       <c r="AR15" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT15" t="n">
         <v>11.5</v>
@@ -4288,10 +4288,10 @@
         <v>11.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AX15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY15" t="n">
         <v>9.800000000000001</v>
@@ -4303,7 +4303,7 @@
         <v>20</v>
       </c>
       <c r="BB15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BC15" t="n">
         <v>17.5</v>
@@ -4324,10 +4324,10 @@
         <v>4.2</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BJ15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK15" t="n">
         <v>4.9</v>
@@ -4336,10 +4336,10 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO15" t="n">
         <v>4.1</v>
@@ -4354,7 +4354,7 @@
         <v>25</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT15" t="n">
         <v>7.4</v>
@@ -4366,23 +4366,23 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ15" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -4413,16 +4413,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G16" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J16" t="n">
         <v>4.1</v>
@@ -4431,40 +4431,40 @@
         <v>4.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P16" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="T16" t="n">
         <v>1.45</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="V16" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W16" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="X16" t="n">
         <v>950</v>
@@ -4488,7 +4488,7 @@
         <v>16.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF16" t="n">
         <v>28</v>
@@ -4518,70 +4518,70 @@
         <v>13.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA16" t="n">
         <v>3.85</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE16" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU16" t="n">
+      <c r="BF16" t="n">
         <v>3.4</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BG16" t="n">
         <v>3.6</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>9</v>
       </c>
       <c r="BH16" t="n">
         <v>5.1</v>
       </c>
       <c r="BI16" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BJ16" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
         <v>6</v>
@@ -4590,7 +4590,7 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="BN16" t="n">
         <v>6.4</v>
@@ -4602,13 +4602,13 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT16" t="n">
         <v>6.6</v>
@@ -4620,23 +4620,23 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -4688,7 +4688,7 @@
         <v>1.14</v>
       </c>
       <c r="M17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
         <v>1.1</v>
@@ -4697,7 +4697,7 @@
         <v>1.07</v>
       </c>
       <c r="P17" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q17" t="n">
         <v>1.22</v>
@@ -4775,10 +4775,10 @@
         <v>25</v>
       </c>
       <c r="AP17" t="n">
-        <v>8.199999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AR17" t="n">
         <v>4.2</v>
@@ -4796,7 +4796,7 @@
         <v>6.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AX17" t="n">
         <v>6.4</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
         <v>3.35</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
         <v>5</v>
@@ -4945,13 +4945,13 @@
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="O18" t="n">
         <v>1.11</v>
       </c>
       <c r="P18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q18" t="n">
         <v>1.36</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -5193,19 +5193,19 @@
         <v>5.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M19" t="n">
         <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
         <v>1.1</v>
       </c>
       <c r="P19" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q19" t="n">
         <v>1.32</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.71</v>
       </c>
       <c r="G20" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H20" t="n">
         <v>3.5</v>
@@ -5453,28 +5453,28 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.1</v>
+        <v>10</v>
       </c>
       <c r="O20" t="n">
         <v>1.07</v>
       </c>
       <c r="P20" t="n">
-        <v>1.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="R20" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="S20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="T20" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="U20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="V20" t="n">
         <v>1.3</v>
@@ -5483,25 +5483,25 @@
         <v>2.06</v>
       </c>
       <c r="X20" t="n">
-        <v>170</v>
+        <v>950</v>
       </c>
       <c r="Y20" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="Z20" t="n">
         <v>120</v>
       </c>
       <c r="AA20" t="n">
-        <v>900</v>
+        <v>290</v>
       </c>
       <c r="AB20" t="n">
-        <v>65</v>
+        <v>950</v>
       </c>
       <c r="AC20" t="n">
-        <v>95</v>
+        <v>970</v>
       </c>
       <c r="AD20" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="AE20" t="n">
         <v>290</v>
@@ -5519,7 +5519,7 @@
         <v>75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>900</v>
+        <v>30</v>
       </c>
       <c r="AK20" t="n">
         <v>970</v>
@@ -5528,7 +5528,7 @@
         <v>170</v>
       </c>
       <c r="AM20" t="n">
-        <v>40</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
         <v>4.9</v>
@@ -5537,28 +5537,28 @@
         <v>970</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.55</v>
+        <v>5.8</v>
       </c>
       <c r="AQ20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT20" t="n">
         <v>5.9</v>
       </c>
-      <c r="AR20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AU20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX20" t="n">
         <v>5.6</v>
@@ -5573,25 +5573,25 @@
         <v>5.9</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE20" t="n">
         <v>6</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH20" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
         <v>3.85</v>
@@ -5606,53 +5606,53 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BN20" t="n">
         <v>6.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BT20" t="n">
         <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
         <v>6</v>
       </c>
-      <c r="BX20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="G21" t="n">
         <v>1.71</v>
@@ -5695,34 +5695,34 @@
         <v>6.8</v>
       </c>
       <c r="J21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
         <v>4.9</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
         <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R21" t="n">
         <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="T21" t="n">
         <v>1.79</v>
@@ -5731,7 +5731,7 @@
         <v>2.02</v>
       </c>
       <c r="V21" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W21" t="n">
         <v>2.4</v>
@@ -5743,7 +5743,7 @@
         <v>24</v>
       </c>
       <c r="Z21" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AA21" t="n">
         <v>180</v>
@@ -5779,7 +5779,7 @@
         <v>17.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM21" t="n">
         <v>580</v>
@@ -5794,7 +5794,7 @@
         <v>16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AR21" t="n">
         <v>16</v>
@@ -5812,19 +5812,19 @@
         <v>19</v>
       </c>
       <c r="AW21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ21" t="n">
         <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB21" t="n">
         <v>13</v>
@@ -5836,7 +5836,7 @@
         <v>16.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF21" t="n">
         <v>6.8</v>
@@ -5866,7 +5866,7 @@
         <v>4.5</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="BP21" t="n">
         <v>11</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -5937,187 +5937,187 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="G22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K22" t="n">
         <v>4.8</v>
       </c>
-      <c r="H22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="J22" t="n">
-        <v>4</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L22" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M22" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="R22" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="S22" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="T22" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V22" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="W22" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="X22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y22" t="n">
         <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>19.5</v>
+        <v>34</v>
       </c>
       <c r="AB22" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AD22" t="n">
         <v>10.5</v>
       </c>
       <c r="AE22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>90</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>160</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AP22" t="n">
         <v>18</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>110</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>320</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>250</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>16</v>
       </c>
       <c r="AQ22" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR22" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AV22" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW22" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AX22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>16.5</v>
       </c>
-      <c r="AY22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BA22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BB22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC22" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BD22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE22" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="BF22" t="n">
-        <v>9.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="BG22" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BH22" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BJ22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN22" t="n">
         <v>9.6</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>8.6</v>
       </c>
       <c r="BO22" t="n">
         <v>5.1</v>
@@ -6126,41 +6126,41 @@
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT22" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BU22" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BV22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BW22" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BZ22" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="CA22" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -6191,28 +6191,28 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="G23" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J23" t="n">
         <v>5.3</v>
       </c>
       <c r="K23" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N23" t="n">
         <v>6.6</v>
@@ -6221,34 +6221,34 @@
         <v>1.15</v>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="S23" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="T23" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U23" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V23" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W23" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="X23" t="n">
         <v>85</v>
       </c>
       <c r="Y23" t="n">
-        <v>160</v>
+        <v>950</v>
       </c>
       <c r="Z23" t="n">
         <v>450</v>
@@ -6260,10 +6260,10 @@
         <v>13.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AD23" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="AE23" t="n">
         <v>400</v>
@@ -6281,7 +6281,7 @@
         <v>320</v>
       </c>
       <c r="AJ23" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AK23" t="n">
         <v>25</v>
@@ -6293,7 +6293,7 @@
         <v>260</v>
       </c>
       <c r="AN23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AO23" t="n">
         <v>330</v>
@@ -6305,16 +6305,16 @@
         <v>29</v>
       </c>
       <c r="AR23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT23" t="n">
         <v>11.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV23" t="n">
         <v>15</v>
@@ -6332,7 +6332,7 @@
         <v>11</v>
       </c>
       <c r="BA23" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB23" t="n">
         <v>7.8</v>
@@ -6347,22 +6347,22 @@
         <v>10.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BG23" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH23" t="n">
         <v>5.1</v>
       </c>
       <c r="BI23" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BJ23" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
@@ -6377,22 +6377,22 @@
         <v>3.6</v>
       </c>
       <c r="BP23" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BQ23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU23" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
@@ -6407,14 +6407,14 @@
         <v>11</v>
       </c>
       <c r="BZ23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H24" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="I24" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="J24" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K24" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L24" t="n">
         <v>1.19</v>
@@ -6469,7 +6469,7 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>1.1</v>
+        <v>1.68</v>
       </c>
       <c r="O24" t="n">
         <v>1.11</v>
@@ -6478,7 +6478,7 @@
         <v>3.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R24" t="n">
         <v>1.9</v>
@@ -6490,37 +6490,37 @@
         <v>1.4</v>
       </c>
       <c r="U24" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="V24" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X24" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Y24" t="n">
         <v>22</v>
       </c>
       <c r="Z24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA24" t="n">
         <v>28</v>
       </c>
       <c r="AB24" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AC24" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD24" t="n">
         <v>13</v>
       </c>
       <c r="AE24" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AF24" t="n">
         <v>36</v>
@@ -6529,136 +6529,136 @@
         <v>17</v>
       </c>
       <c r="AH24" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI24" t="n">
         <v>24</v>
       </c>
       <c r="AJ24" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AK24" t="n">
         <v>32</v>
       </c>
       <c r="AL24" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM24" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AN24" t="n">
         <v>17.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AP24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR24" t="n">
         <v>6.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU24" t="n">
         <v>7</v>
       </c>
       <c r="AV24" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AW24" t="n">
         <v>6.2</v>
       </c>
       <c r="AX24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD24" t="n">
         <v>6.4</v>
       </c>
-      <c r="AY24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB24" t="n">
+      <c r="BE24" t="n">
         <v>7</v>
       </c>
-      <c r="BC24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BF24" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BH24" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BL24" t="n">
         <v>60</v>
       </c>
       <c r="BM24" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BN24" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ24" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR24" t="n">
         <v>25</v>
       </c>
       <c r="BS24" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BT24" t="n">
         <v>6.2</v>
       </c>
       <c r="BU24" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BV24" t="n">
         <v>13.5</v>
       </c>
       <c r="BW24" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BX24" t="n">
         <v>19</v>
       </c>
       <c r="BY24" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -6699,64 +6699,64 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="G25" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="I25" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="J25" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="K25" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="M25" t="n">
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P25" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="R25" t="n">
         <v>1.23</v>
       </c>
       <c r="S25" t="n">
-        <v>1.05</v>
+        <v>4.4</v>
       </c>
       <c r="T25" t="n">
         <v>2.34</v>
       </c>
       <c r="U25" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="V25" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W25" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="X25" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Y25" t="n">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="Z25" t="n">
         <v>330</v>
@@ -6765,13 +6765,13 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>13</v>
+        <v>950</v>
       </c>
       <c r="AC25" t="n">
         <v>20</v>
       </c>
       <c r="AD25" t="n">
-        <v>170</v>
+        <v>950</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
@@ -6780,10 +6780,10 @@
         <v>40</v>
       </c>
       <c r="AG25" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AH25" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="AI25" t="n">
         <v>540</v>
@@ -6792,10 +6792,10 @@
         <v>900</v>
       </c>
       <c r="AK25" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL25" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
@@ -6810,13 +6810,13 @@
         <v>5.8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="AR25" t="n">
         <v>4.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.94</v>
+        <v>2.18</v>
       </c>
       <c r="AT25" t="n">
         <v>4.2</v>
@@ -6828,7 +6828,7 @@
         <v>4.2</v>
       </c>
       <c r="AW25" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AX25" t="n">
         <v>4.9</v>
@@ -6837,34 +6837,34 @@
         <v>6.2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.45</v>
+        <v>2.52</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="BB25" t="n">
         <v>7.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="BD25" t="n">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="BE25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI25" t="n">
         <v>2.44</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>1.04</v>
       </c>
       <c r="BJ25" t="n">
         <v>1000</v>
@@ -6882,7 +6882,7 @@
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -6953,16 +6953,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="G26" t="n">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="H26" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="J26" t="n">
         <v>3.6</v>
@@ -6971,31 +6971,31 @@
         <v>4.5</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="O26" t="n">
         <v>1.18</v>
       </c>
       <c r="P26" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="R26" t="n">
         <v>1.58</v>
       </c>
       <c r="S26" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T26" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U26" t="n">
         <v>2.52</v>
@@ -7031,7 +7031,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="n">
-        <v>120</v>
+        <v>970</v>
       </c>
       <c r="AG26" t="n">
         <v>970</v>
@@ -7058,125 +7058,125 @@
         <v>55</v>
       </c>
       <c r="AO26" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AP26" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="AQ26" t="n">
         <v>5.2</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="AS26" t="n">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="AT26" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AU26" t="n">
         <v>5.6</v>
       </c>
       <c r="AV26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY26" t="n">
         <v>5</v>
       </c>
-      <c r="AW26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY26" t="n">
+      <c r="AZ26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BH26" t="n">
         <v>4.6</v>
       </c>
-      <c r="AZ26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG26" t="n">
+      <c r="BI26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK26" t="n">
         <v>4.7</v>
       </c>
-      <c r="BH26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="BN26" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BT26" t="n">
         <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G27" t="n">
         <v>2.66</v>
@@ -7219,25 +7219,25 @@
         <v>2.84</v>
       </c>
       <c r="J27" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K27" t="n">
         <v>5.4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M27" t="n">
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.1</v>
+        <v>10</v>
       </c>
       <c r="O27" t="n">
         <v>1.08</v>
       </c>
       <c r="P27" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="n">
         <v>1.25</v>
@@ -7246,10 +7246,10 @@
         <v>2.16</v>
       </c>
       <c r="S27" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="U27" t="n">
         <v>3.55</v>
@@ -7258,13 +7258,13 @@
         <v>1.54</v>
       </c>
       <c r="W27" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X27" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="Y27" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z27" t="n">
         <v>36</v>
@@ -7279,7 +7279,7 @@
         <v>16.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -7297,7 +7297,7 @@
         <v>24</v>
       </c>
       <c r="AJ27" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK27" t="n">
         <v>24</v>
@@ -7315,112 +7315,112 @@
         <v>8.6</v>
       </c>
       <c r="AP27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS27" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS27" t="n">
+      <c r="AT27" t="n">
         <v>6.2</v>
       </c>
-      <c r="AT27" t="n">
-        <v>6</v>
-      </c>
       <c r="AU27" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="AV27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.7</v>
+        <v>17</v>
       </c>
       <c r="AX27" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BI27" t="n">
         <v>5</v>
       </c>
-      <c r="AZ27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA27" t="n">
+      <c r="BJ27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>44</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BS27" t="n">
         <v>5.6</v>
       </c>
-      <c r="BB27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC27" t="n">
+      <c r="BT27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>19</v>
+      </c>
+      <c r="BY27" t="n">
         <v>5.6</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY27" t="n">
-        <v>1.04</v>
       </c>
       <c r="BZ27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -7461,67 +7461,67 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="G28" t="n">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="H28" t="n">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="I28" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="J28" t="n">
         <v>3.55</v>
       </c>
       <c r="K28" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L28" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M28" t="n">
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R28" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S28" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="T28" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="U28" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="V28" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="W28" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="X28" t="n">
         <v>21</v>
       </c>
       <c r="Y28" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AA28" t="n">
         <v>900</v>
@@ -7530,151 +7530,151 @@
         <v>13</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH28" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>17</v>
       </c>
       <c r="AI28" t="n">
         <v>120</v>
       </c>
       <c r="AJ28" t="n">
-        <v>29</v>
+        <v>900</v>
       </c>
       <c r="AK28" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AL28" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AM28" t="n">
         <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AP28" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>24</v>
+        <v>7.8</v>
       </c>
       <c r="AT28" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AW28" t="n">
         <v>18</v>
       </c>
       <c r="AX28" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="BC28" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BD28" t="n">
-        <v>18</v>
+        <v>7.4</v>
       </c>
       <c r="BE28" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ28" t="n">
         <v>7.2</v>
       </c>
-      <c r="BF28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>29</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN28" t="n">
+      <c r="BR28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU28" t="n">
         <v>5.1</v>
       </c>
-      <c r="BO28" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR28" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU28" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -7718,10 +7718,10 @@
         <v>2.36</v>
       </c>
       <c r="G29" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H29" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I29" t="n">
         <v>3.4</v>
@@ -7730,7 +7730,7 @@
         <v>3.3</v>
       </c>
       <c r="K29" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L29" t="n">
         <v>1.41</v>
@@ -7739,16 +7739,16 @@
         <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O29" t="n">
         <v>1.34</v>
       </c>
       <c r="P29" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R29" t="n">
         <v>1.33</v>
@@ -7760,13 +7760,13 @@
         <v>1.76</v>
       </c>
       <c r="U29" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V29" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W29" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X29" t="n">
         <v>14</v>
@@ -7817,7 +7817,7 @@
         <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO29" t="n">
         <v>38</v>
@@ -7829,22 +7829,22 @@
         <v>10.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT29" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU29" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV29" t="n">
         <v>10</v>
       </c>
       <c r="AW29" t="n">
-        <v>16</v>
+        <v>7.4</v>
       </c>
       <c r="AX29" t="n">
         <v>13</v>
@@ -7853,7 +7853,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ29" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA29" t="n">
         <v>7.6</v>
@@ -7865,7 +7865,7 @@
         <v>14.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE29" t="n">
         <v>8.199999999999999</v>
@@ -7880,19 +7880,19 @@
         <v>3.45</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM29" t="n">
         <v>10</v>
-      </c>
-      <c r="BK29" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM29" t="n">
-        <v>9.6</v>
       </c>
       <c r="BN29" t="n">
         <v>5.6</v>
@@ -7901,16 +7901,16 @@
         <v>4.3</v>
       </c>
       <c r="BP29" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR29" t="n">
         <v>34</v>
       </c>
       <c r="BS29" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT29" t="n">
         <v>6.6</v>
@@ -7922,13 +7922,13 @@
         <v>26</v>
       </c>
       <c r="BW29" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -7969,67 +7969,67 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="G30" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H30" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="J30" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K30" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="M30" t="n">
         <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="O30" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P30" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="R30" t="n">
         <v>1.2</v>
       </c>
       <c r="S30" t="n">
-        <v>1.05</v>
+        <v>5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U30" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V30" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W30" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X30" t="n">
         <v>22</v>
       </c>
       <c r="Y30" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="Z30" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AA30" t="n">
         <v>900</v>
@@ -8041,10 +8041,10 @@
         <v>42</v>
       </c>
       <c r="AD30" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="AE30" t="n">
-        <v>370</v>
+        <v>700</v>
       </c>
       <c r="AF30" t="n">
         <v>40</v>
@@ -8053,10 +8053,10 @@
         <v>44</v>
       </c>
       <c r="AH30" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AI30" t="n">
-        <v>370</v>
+        <v>700</v>
       </c>
       <c r="AJ30" t="n">
         <v>900</v>
@@ -8065,25 +8065,25 @@
         <v>130</v>
       </c>
       <c r="AL30" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AM30" t="n">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="AN30" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AO30" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AP30" t="n">
         <v>5.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AR30" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AS30" t="n">
         <v>1.92</v>
@@ -8095,10 +8095,10 @@
         <v>4.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AX30" t="n">
         <v>6.2</v>
@@ -8107,28 +8107,28 @@
         <v>6.4</v>
       </c>
       <c r="AZ30" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="BB30" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="BF30" t="n">
         <v>4.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="BH30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -8223,49 +8223,49 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="G31" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="H31" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="I31" t="n">
         <v>7.8</v>
       </c>
       <c r="J31" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K31" t="n">
         <v>3.55</v>
       </c>
       <c r="L31" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="M31" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N31" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="O31" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="P31" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="R31" t="n">
         <v>1.12</v>
       </c>
       <c r="S31" t="n">
-        <v>1.05</v>
+        <v>7.2</v>
       </c>
       <c r="T31" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U31" t="n">
         <v>1.47</v>
@@ -8274,10 +8274,10 @@
         <v>1.15</v>
       </c>
       <c r="W31" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X31" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y31" t="n">
         <v>15</v>
@@ -8286,7 +8286,7 @@
         <v>160</v>
       </c>
       <c r="AA31" t="n">
-        <v>340</v>
+        <v>700</v>
       </c>
       <c r="AB31" t="n">
         <v>5.4</v>
@@ -8298,7 +8298,7 @@
         <v>75</v>
       </c>
       <c r="AE31" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AF31" t="n">
         <v>9.4</v>
@@ -8310,7 +8310,7 @@
         <v>110</v>
       </c>
       <c r="AI31" t="n">
-        <v>540</v>
+        <v>700</v>
       </c>
       <c r="AJ31" t="n">
         <v>23</v>
@@ -8322,73 +8322,73 @@
         <v>460</v>
       </c>
       <c r="AM31" t="n">
-        <v>570</v>
+        <v>700</v>
       </c>
       <c r="AN31" t="n">
         <v>120</v>
       </c>
       <c r="AO31" t="n">
-        <v>590</v>
+        <v>700</v>
       </c>
       <c r="AP31" t="n">
         <v>3.8</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AR31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS31" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AU31" t="n">
         <v>4.2</v>
       </c>
       <c r="AV31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF31" t="n">
         <v>6.4</v>
       </c>
-      <c r="AW31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BG31" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH31" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BI31" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="BJ31" t="n">
         <v>16</v>
@@ -8400,13 +8400,13 @@
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.99</v>
+        <v>2.94</v>
       </c>
       <c r="BN31" t="n">
         <v>4.3</v>
       </c>
       <c r="BO31" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BP31" t="n">
         <v>16.5</v>
@@ -8418,35 +8418,35 @@
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.93</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT31" t="n">
         <v>11</v>
       </c>
       <c r="BU31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.96</v>
+        <v>8.6</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.97</v>
+        <v>2.9</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.94</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -8477,10 +8477,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G32" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H32" t="n">
         <v>2.96</v>
@@ -8489,34 +8489,34 @@
         <v>3.45</v>
       </c>
       <c r="J32" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="K32" t="n">
         <v>3.1</v>
       </c>
       <c r="L32" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="M32" t="n">
         <v>1.15</v>
       </c>
       <c r="N32" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="O32" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="P32" t="n">
         <v>1.41</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="R32" t="n">
         <v>1.14</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T32" t="n">
         <v>2.24</v>
@@ -8525,10 +8525,10 @@
         <v>1.65</v>
       </c>
       <c r="V32" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W32" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="X32" t="n">
         <v>7.4</v>
@@ -8582,46 +8582,46 @@
         <v>210</v>
       </c>
       <c r="AO32" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP32" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AQ32" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR32" t="n">
-        <v>6.4</v>
+        <v>16.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AT32" t="n">
         <v>4.3</v>
       </c>
       <c r="AU32" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AV32" t="n">
-        <v>5.9</v>
+        <v>13</v>
       </c>
       <c r="AW32" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AX32" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BA32" t="n">
         <v>8.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BC32" t="n">
         <v>8</v>
@@ -8633,19 +8633,19 @@
         <v>9</v>
       </c>
       <c r="BF32" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH32" t="n">
         <v>2.54</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="BJ32" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK32" t="n">
         <v>6</v>
@@ -8654,25 +8654,25 @@
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BN32" t="n">
         <v>5.9</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP32" t="n">
         <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="BR32" t="n">
         <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="BT32" t="n">
         <v>6.2</v>
@@ -8684,7 +8684,7 @@
         <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
@@ -8696,11 +8696,11 @@
         <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -8731,22 +8731,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G33" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I33" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J33" t="n">
         <v>3.35</v>
       </c>
       <c r="K33" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L33" t="n">
         <v>1.44</v>
@@ -8755,10 +8755,10 @@
         <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O33" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P33" t="n">
         <v>1.81</v>
@@ -8767,10 +8767,10 @@
         <v>2.1</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S33" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T33" t="n">
         <v>1.85</v>
@@ -8779,10 +8779,10 @@
         <v>2.02</v>
       </c>
       <c r="V33" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W33" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X33" t="n">
         <v>15</v>
@@ -8896,19 +8896,19 @@
         <v>3.25</v>
       </c>
       <c r="BI33" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BJ33" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK33" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN33" t="n">
         <v>5.5</v>
@@ -8920,41 +8920,41 @@
         <v>20</v>
       </c>
       <c r="BQ33" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR33" t="n">
         <v>36</v>
       </c>
       <c r="BS33" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT33" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU33" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV33" t="n">
         <v>26</v>
       </c>
       <c r="BW33" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ33" t="n">
         <v>32</v>
       </c>
       <c r="CA33" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -8994,16 +8994,16 @@
         <v>4.9</v>
       </c>
       <c r="I34" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J34" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K34" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L34" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="M34" t="n">
         <v>1.11</v>
@@ -9033,10 +9033,10 @@
         <v>1.68</v>
       </c>
       <c r="V34" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W34" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X34" t="n">
         <v>11</v>
@@ -9090,7 +9090,7 @@
         <v>29</v>
       </c>
       <c r="AO34" t="n">
-        <v>210</v>
+        <v>600</v>
       </c>
       <c r="AP34" t="n">
         <v>7.6</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -9242,37 +9242,37 @@
         <v>1.81</v>
       </c>
       <c r="G35" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="H35" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="I35" t="n">
         <v>6.4</v>
       </c>
       <c r="J35" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K35" t="n">
         <v>3.55</v>
       </c>
       <c r="L35" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="M35" t="n">
         <v>1.13</v>
       </c>
       <c r="N35" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="O35" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P35" t="n">
         <v>1.48</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="R35" t="n">
         <v>1.17</v>
@@ -9290,7 +9290,7 @@
         <v>1.19</v>
       </c>
       <c r="W35" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X35" t="n">
         <v>9.800000000000001</v>
@@ -9347,22 +9347,22 @@
         <v>300</v>
       </c>
       <c r="AP35" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AR35" t="n">
         <v>6.8</v>
       </c>
       <c r="AS35" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="AU35" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="AV35" t="n">
         <v>6</v>
@@ -9371,22 +9371,22 @@
         <v>7.4</v>
       </c>
       <c r="AX35" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="AY35" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="AZ35" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BA35" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.8</v>
+        <v>16</v>
       </c>
       <c r="BC35" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BD35" t="n">
         <v>7</v>
@@ -9395,7 +9395,7 @@
         <v>7.6</v>
       </c>
       <c r="BF35" t="n">
-        <v>6.2</v>
+        <v>17.5</v>
       </c>
       <c r="BG35" t="n">
         <v>7.6</v>
@@ -9404,7 +9404,7 @@
         <v>2.7</v>
       </c>
       <c r="BI35" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="BJ35" t="n">
         <v>13</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -9493,46 +9493,46 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G36" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H36" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I36" t="n">
         <v>4.9</v>
       </c>
       <c r="J36" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="K36" t="n">
         <v>3.1</v>
       </c>
       <c r="L36" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="M36" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="N36" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="O36" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="P36" t="n">
         <v>1.32</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
         <v>1.12</v>
       </c>
       <c r="S36" t="n">
-        <v>1.05</v>
+        <v>7.2</v>
       </c>
       <c r="T36" t="n">
         <v>2.48</v>
@@ -9541,10 +9541,10 @@
         <v>1.5</v>
       </c>
       <c r="V36" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W36" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="X36" t="n">
         <v>6.6</v>
@@ -9601,10 +9601,10 @@
         <v>500</v>
       </c>
       <c r="AP36" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AR36" t="n">
         <v>5.8</v>
@@ -9613,10 +9613,10 @@
         <v>6.8</v>
       </c>
       <c r="AT36" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="AU36" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AV36" t="n">
         <v>5.5</v>
@@ -9631,13 +9631,13 @@
         <v>4.9</v>
       </c>
       <c r="AZ36" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BA36" t="n">
         <v>6.8</v>
       </c>
       <c r="BB36" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BC36" t="n">
         <v>6.4</v>
@@ -9658,7 +9658,7 @@
         <v>2.4</v>
       </c>
       <c r="BI36" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="BJ36" t="n">
         <v>15</v>
@@ -9676,7 +9676,7 @@
         <v>5.2</v>
       </c>
       <c r="BO36" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="BP36" t="n">
         <v>26</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -9747,58 +9747,58 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G37" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H37" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="I37" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="J37" t="n">
         <v>2.84</v>
       </c>
       <c r="K37" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="L37" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="M37" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N37" t="n">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="O37" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P37" t="n">
         <v>1.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="R37" t="n">
         <v>1.15</v>
       </c>
       <c r="S37" t="n">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="T37" t="n">
         <v>2.2</v>
       </c>
       <c r="U37" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V37" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W37" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="X37" t="n">
         <v>90</v>
@@ -9810,7 +9810,7 @@
         <v>170</v>
       </c>
       <c r="AA37" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AB37" t="n">
         <v>970</v>
@@ -9819,10 +9819,10 @@
         <v>42</v>
       </c>
       <c r="AD37" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="AE37" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AF37" t="n">
         <v>970</v>
@@ -9831,10 +9831,10 @@
         <v>970</v>
       </c>
       <c r="AH37" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="AI37" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AJ37" t="n">
         <v>140</v>
@@ -9855,16 +9855,16 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AQ37" t="n">
         <v>5.8</v>
       </c>
       <c r="AR37" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="AT37" t="n">
         <v>3.5</v>
@@ -9873,46 +9873,46 @@
         <v>4.2</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AX37" t="n">
         <v>5.1</v>
       </c>
       <c r="AY37" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AZ37" t="n">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="BB37" t="n">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="BC37" t="n">
-        <v>3.35</v>
+        <v>2.76</v>
       </c>
       <c r="BD37" t="n">
         <v>2.08</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="BF37" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BG37" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="BH37" t="n">
         <v>3.95</v>
       </c>
       <c r="BI37" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="BJ37" t="n">
         <v>1000</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -10004,43 +10004,43 @@
         <v>2.44</v>
       </c>
       <c r="G38" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="H38" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I38" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="K38" t="n">
         <v>3.15</v>
       </c>
       <c r="L38" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="M38" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="N38" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="O38" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="P38" t="n">
         <v>1.37</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="R38" t="n">
         <v>1.12</v>
       </c>
       <c r="S38" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="T38" t="n">
         <v>2.28</v>
@@ -10049,10 +10049,10 @@
         <v>1.59</v>
       </c>
       <c r="V38" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W38" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X38" t="n">
         <v>7.2</v>
@@ -10109,37 +10109,37 @@
         <v>150</v>
       </c>
       <c r="AP38" t="n">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="AQ38" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AR38" t="n">
-        <v>5.8</v>
+        <v>19</v>
       </c>
       <c r="AS38" t="n">
         <v>7</v>
       </c>
       <c r="AT38" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AU38" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV38" t="n">
-        <v>5.4</v>
+        <v>14.5</v>
       </c>
       <c r="AW38" t="n">
         <v>7</v>
       </c>
       <c r="AX38" t="n">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="AY38" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ38" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="BA38" t="n">
         <v>7.2</v>
@@ -10166,7 +10166,7 @@
         <v>2.52</v>
       </c>
       <c r="BI38" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="BJ38" t="n">
         <v>13.5</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -10255,46 +10255,46 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G39" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="H39" t="n">
         <v>3.25</v>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J39" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="K39" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L39" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="M39" t="n">
         <v>1.16</v>
       </c>
       <c r="N39" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="O39" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="P39" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="R39" t="n">
         <v>1.13</v>
       </c>
       <c r="S39" t="n">
-        <v>1.05</v>
+        <v>6.2</v>
       </c>
       <c r="T39" t="n">
         <v>2.28</v>
@@ -10303,10 +10303,10 @@
         <v>1.63</v>
       </c>
       <c r="V39" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W39" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X39" t="n">
         <v>14</v>
@@ -10339,7 +10339,7 @@
         <v>970</v>
       </c>
       <c r="AH39" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="AI39" t="n">
         <v>350</v>
@@ -10363,16 +10363,16 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="AQ39" t="n">
         <v>5.1</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AS39" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AT39" t="n">
         <v>3.85</v>
@@ -10381,46 +10381,46 @@
         <v>4.2</v>
       </c>
       <c r="AV39" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AX39" t="n">
         <v>6.2</v>
       </c>
       <c r="AY39" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="BA39" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="BC39" t="n">
         <v>1.97</v>
       </c>
       <c r="BD39" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="BH39" t="n">
         <v>3.2</v>
       </c>
       <c r="BI39" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="BJ39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -10509,16 +10509,16 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G40" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="H40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I40" t="n">
         <v>4.6</v>
-      </c>
-      <c r="I40" t="n">
-        <v>4.7</v>
       </c>
       <c r="J40" t="n">
         <v>4</v>
@@ -10527,40 +10527,40 @@
         <v>4.1</v>
       </c>
       <c r="L40" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M40" t="n">
         <v>1.05</v>
       </c>
       <c r="N40" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O40" t="n">
         <v>1.25</v>
       </c>
       <c r="P40" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R40" t="n">
         <v>1.5</v>
       </c>
       <c r="S40" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T40" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U40" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V40" t="n">
         <v>1.27</v>
       </c>
       <c r="W40" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X40" t="n">
         <v>18.5</v>
@@ -10569,37 +10569,37 @@
         <v>20</v>
       </c>
       <c r="Z40" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA40" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB40" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC40" t="n">
         <v>9</v>
       </c>
       <c r="AD40" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG40" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH40" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI40" t="n">
         <v>55</v>
       </c>
       <c r="AJ40" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK40" t="n">
         <v>18.5</v>
@@ -10611,64 +10611,64 @@
         <v>80</v>
       </c>
       <c r="AN40" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AO40" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP40" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ40" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AR40" t="n">
         <v>32</v>
       </c>
       <c r="AS40" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AT40" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU40" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV40" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW40" t="n">
         <v>44</v>
       </c>
       <c r="AX40" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY40" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ40" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA40" t="n">
         <v>46</v>
       </c>
       <c r="BB40" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BC40" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD40" t="n">
         <v>27</v>
       </c>
       <c r="BE40" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF40" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG40" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BH40" t="n">
         <v>3.95</v>
@@ -10680,13 +10680,13 @@
         <v>9.6</v>
       </c>
       <c r="BK40" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL40" t="n">
         <v>100</v>
       </c>
       <c r="BM40" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN40" t="n">
         <v>4.9</v>
@@ -10698,16 +10698,16 @@
         <v>13</v>
       </c>
       <c r="BQ40" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR40" t="n">
         <v>24</v>
       </c>
       <c r="BS40" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT40" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU40" t="n">
         <v>5.1</v>
@@ -10716,23 +10716,23 @@
         <v>34</v>
       </c>
       <c r="BW40" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX40" t="n">
         <v>40</v>
       </c>
       <c r="BY40" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ40" t="n">
         <v>17</v>
       </c>
       <c r="CA40" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10802,7 @@
         <v>1.28</v>
       </c>
       <c r="S41" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T41" t="n">
         <v>1.9</v>
@@ -10817,10 +10817,10 @@
         <v>2.02</v>
       </c>
       <c r="X41" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Y41" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Z41" t="n">
         <v>500</v>
@@ -10829,10 +10829,10 @@
         <v>900</v>
       </c>
       <c r="AB41" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC41" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AD41" t="n">
         <v>950</v>
@@ -10841,13 +10841,13 @@
         <v>700</v>
       </c>
       <c r="AF41" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG41" t="n">
         <v>970</v>
       </c>
       <c r="AH41" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI41" t="n">
         <v>700</v>
@@ -10862,73 +10862,73 @@
         <v>500</v>
       </c>
       <c r="AM41" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN41" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO41" t="n">
         <v>700</v>
       </c>
       <c r="AP41" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AT41" t="n">
         <v>3.85</v>
       </c>
-      <c r="AQ41" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>3.15</v>
-      </c>
       <c r="AU41" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.22</v>
+        <v>4.4</v>
       </c>
       <c r="AW41" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="AX41" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="AY41" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ41" t="n">
-        <v>2.24</v>
+        <v>4.4</v>
       </c>
       <c r="BA41" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="BB41" t="n">
-        <v>2.24</v>
+        <v>4.5</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.24</v>
+        <v>4.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>2.34</v>
+        <v>2.72</v>
       </c>
       <c r="BE41" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="BF41" t="n">
-        <v>2.54</v>
+        <v>4.3</v>
       </c>
       <c r="BG41" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="BH41" t="n">
         <v>6.6</v>
       </c>
       <c r="BI41" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BJ41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -11026,7 +11026,7 @@
         <v>6</v>
       </c>
       <c r="I42" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J42" t="n">
         <v>3.95</v>
@@ -11041,7 +11041,7 @@
         <v>1.07</v>
       </c>
       <c r="N42" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O42" t="n">
         <v>1.33</v>
@@ -11056,10 +11056,10 @@
         <v>1.34</v>
       </c>
       <c r="S42" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T42" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U42" t="n">
         <v>1.91</v>
@@ -11077,7 +11077,7 @@
         <v>25</v>
       </c>
       <c r="Z42" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA42" t="n">
         <v>900</v>
@@ -11095,7 +11095,7 @@
         <v>700</v>
       </c>
       <c r="AF42" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG42" t="n">
         <v>11.5</v>
@@ -11134,7 +11134,7 @@
         <v>34</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT42" t="n">
         <v>5.9</v>
@@ -11146,19 +11146,19 @@
         <v>20</v>
       </c>
       <c r="AW42" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX42" t="n">
         <v>7.4</v>
       </c>
       <c r="AY42" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ42" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BA42" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB42" t="n">
         <v>12.5</v>
@@ -11170,19 +11170,19 @@
         <v>28</v>
       </c>
       <c r="BE42" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF42" t="n">
         <v>8.6</v>
       </c>
       <c r="BG42" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BH42" t="n">
         <v>3.35</v>
       </c>
       <c r="BI42" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ42" t="n">
         <v>11</v>
@@ -11218,29 +11218,29 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU42" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV42" t="n">
         <v>1000</v>
       </c>
       <c r="BW42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY42" t="n">
         <v>13</v>
       </c>
-      <c r="BX42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY42" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BZ42" t="n">
         <v>1000</v>
       </c>
       <c r="CA42" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -11271,85 +11271,85 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="G43" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="H43" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="I43" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J43" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="K43" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L43" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="M43" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N43" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="O43" t="n">
         <v>1.26</v>
       </c>
       <c r="P43" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="R43" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S43" t="n">
         <v>2.96</v>
       </c>
       <c r="T43" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="U43" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
         <v>1.16</v>
       </c>
       <c r="W43" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="X43" t="n">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="Y43" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="Z43" t="n">
         <v>60</v>
       </c>
       <c r="AA43" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB43" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC43" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC43" t="n">
-        <v>11</v>
-      </c>
       <c r="AD43" t="n">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="AE43" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF43" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG43" t="n">
         <v>950</v>
@@ -11358,13 +11358,13 @@
         <v>950</v>
       </c>
       <c r="AI43" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ43" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AK43" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL43" t="n">
         <v>38</v>
@@ -11373,31 +11373,31 @@
         <v>120</v>
       </c>
       <c r="AN43" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AO43" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.05</v>
+        <v>13</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS43" t="n">
         <v>1.01</v>
       </c>
       <c r="AT43" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AU43" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AW43" t="n">
         <v>1.01</v>
@@ -11406,22 +11406,22 @@
         <v>8</v>
       </c>
       <c r="AY43" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA43" t="n">
         <v>1.01</v>
       </c>
       <c r="BB43" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD43" t="n">
         <v>1.05</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>1.01</v>
       </c>
       <c r="BE43" t="n">
         <v>1.01</v>
@@ -11433,68 +11433,68 @@
         <v>1.01</v>
       </c>
       <c r="BH43" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BI43" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ43" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK43" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL43" t="n">
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>1.42</v>
+        <v>11</v>
       </c>
       <c r="BN43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ43" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS43" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT43" t="n">
         <v>11</v>
       </c>
-      <c r="BO43" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BP43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ43" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BR43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS43" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BT43" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU43" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV43" t="n">
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>1.39</v>
+        <v>10</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="BZ43" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA43" t="n">
-        <v>1.33</v>
+        <v>7</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -11525,10 +11525,10 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="G44" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="H44" t="n">
         <v>5.6</v>
@@ -11537,46 +11537,46 @@
         <v>6.8</v>
       </c>
       <c r="J44" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K44" t="n">
         <v>5</v>
       </c>
       <c r="L44" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M44" t="n">
         <v>1.04</v>
       </c>
       <c r="N44" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O44" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P44" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R44" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S44" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="T44" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U44" t="n">
         <v>2.04</v>
       </c>
       <c r="V44" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W44" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="X44" t="n">
         <v>24</v>
@@ -11639,10 +11639,10 @@
         <v>18.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT44" t="n">
         <v>8.199999999999999</v>
@@ -11654,7 +11654,7 @@
         <v>17.5</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX44" t="n">
         <v>8.4</v>
@@ -11666,7 +11666,7 @@
         <v>15</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB44" t="n">
         <v>11.5</v>
@@ -11675,16 +11675,16 @@
         <v>12</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.05</v>
+        <v>4.8</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF44" t="n">
         <v>6</v>
       </c>
       <c r="BG44" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH44" t="n">
         <v>4.2</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -11779,13 +11779,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G45" t="n">
         <v>2.54</v>
       </c>
       <c r="H45" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I45" t="n">
         <v>3.95</v>
@@ -11794,205 +11794,205 @@
         <v>3.25</v>
       </c>
       <c r="K45" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="L45" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O45" t="n">
         <v>1.37</v>
       </c>
-      <c r="M45" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N45" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1.3</v>
-      </c>
       <c r="P45" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="R45" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S45" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="T45" t="n">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="U45" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="V45" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W45" t="n">
         <v>1.65</v>
       </c>
       <c r="X45" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="Y45" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z45" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AA45" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB45" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC45" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD45" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE45" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF45" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AG45" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH45" t="n">
         <v>970</v>
       </c>
       <c r="AI45" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ45" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK45" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AL45" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM45" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AN45" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AO45" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AP45" t="n">
-        <v>3.75</v>
+        <v>2.46</v>
       </c>
       <c r="AQ45" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="AR45" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="AS45" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="AT45" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="AU45" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="AV45" t="n">
-        <v>3.8</v>
+        <v>2.54</v>
       </c>
       <c r="AW45" t="n">
-        <v>4.4</v>
+        <v>2.86</v>
       </c>
       <c r="AX45" t="n">
-        <v>3.8</v>
+        <v>2.52</v>
       </c>
       <c r="AY45" t="n">
-        <v>3.55</v>
+        <v>2.48</v>
       </c>
       <c r="AZ45" t="n">
-        <v>3.85</v>
+        <v>2.68</v>
       </c>
       <c r="BA45" t="n">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="BB45" t="n">
-        <v>4.3</v>
+        <v>2.78</v>
       </c>
       <c r="BC45" t="n">
-        <v>4.1</v>
+        <v>2.74</v>
       </c>
       <c r="BD45" t="n">
-        <v>4.4</v>
+        <v>2.86</v>
       </c>
       <c r="BE45" t="n">
-        <v>4.6</v>
+        <v>2.96</v>
       </c>
       <c r="BF45" t="n">
-        <v>3.95</v>
+        <v>2.7</v>
       </c>
       <c r="BG45" t="n">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="BH45" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="BI45" t="n">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="BJ45" t="n">
         <v>10.5</v>
       </c>
       <c r="BK45" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BL45" t="n">
         <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BN45" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BO45" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="BP45" t="n">
         <v>1000</v>
       </c>
       <c r="BQ45" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BR45" t="n">
         <v>1000</v>
       </c>
       <c r="BS45" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BT45" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BU45" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BV45" t="n">
         <v>1000</v>
       </c>
       <c r="BW45" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BX45" t="n">
         <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ45" t="n">
         <v>0</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -12033,46 +12033,46 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G46" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="H46" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I46" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J46" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K46" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L46" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M46" t="n">
         <v>1.06</v>
       </c>
       <c r="N46" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O46" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P46" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="R46" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S46" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="T46" t="n">
         <v>1.76</v>
@@ -12081,10 +12081,10 @@
         <v>2.06</v>
       </c>
       <c r="V46" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W46" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X46" t="n">
         <v>970</v>
@@ -12117,7 +12117,7 @@
         <v>970</v>
       </c>
       <c r="AH46" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AI46" t="n">
         <v>1000</v>
@@ -12126,7 +12126,7 @@
         <v>23</v>
       </c>
       <c r="AK46" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL46" t="n">
         <v>40</v>
@@ -12141,58 +12141,58 @@
         <v>75</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BH46" t="n">
         <v>3.7</v>
@@ -12210,10 +12210,10 @@
         <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="BN46" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="BO46" t="n">
         <v>3.65</v>
@@ -12228,7 +12228,7 @@
         <v>1000</v>
       </c>
       <c r="BS46" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BT46" t="n">
         <v>1000</v>
@@ -12240,13 +12240,13 @@
         <v>1000</v>
       </c>
       <c r="BW46" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="BX46" t="n">
         <v>1000</v>
       </c>
       <c r="BY46" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="BZ46" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,105 +843,105 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Provincial Osorno</t>
+          <t>Deportes Rengo Unido</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>Lota Schwager</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S2" t="n">
+        <v>90</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V2" t="n">
         <v>4.7</v>
       </c>
-      <c r="H2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.16</v>
-      </c>
       <c r="W2" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>1.73</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB2" t="n">
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.42</v>
+        <v>6.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>990</v>
+        <v>55</v>
       </c>
       <c r="AH2" t="n">
-        <v>990</v>
+        <v>320</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -965,58 +965,58 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>29</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>29</v>
+        <v>1.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>29</v>
+        <v>6.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AT2" t="n">
-        <v>3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.71</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.71</v>
+        <v>13.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.7</v>
+        <v>32</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.7</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.71</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB2" t="n">
-        <v>3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.71</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.71</v>
+        <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.71</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.71</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.71</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Cavalry</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="G3" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="H3" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="O3" t="n">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>1.48</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.04</v>
+        <v>2.88</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="S3" t="n">
-        <v>3.65</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="X3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>420</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>290</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>310</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>210</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>32</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>160</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>90</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>330</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>150</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BI3" t="n">
         <v>1.93</v>
       </c>
-      <c r="U3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="BJ3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>150</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>120</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>210</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>130</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>950</v>
+      </c>
+      <c r="BY3" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y3" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO3" t="n">
+      <c r="BZ3" t="n">
+        <v>150</v>
+      </c>
+      <c r="CA3" t="n">
         <v>120</v>
       </c>
-      <c r="AP3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>940</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>60</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>70</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>30</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>17</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chilean Segunda Division</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Deportes Rengo Unido</t>
+          <t>FC Supra du Quebec</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lota Schwager</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.05</v>
+        <v>1.59</v>
       </c>
       <c r="G4" t="n">
-        <v>3.45</v>
+        <v>1.79</v>
       </c>
       <c r="H4" t="n">
-        <v>2.36</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="n">
-        <v>2.56</v>
+        <v>44</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>1.09</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>1.02</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>1.02</v>
       </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.14</v>
+        <v>1.35</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="U4" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="V4" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK4" t="n">
         <v>18</v>
       </c>
-      <c r="AA4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>50</v>
-      </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AM4" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.6</v>
+        <v>1.23</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.4</v>
+        <v>1.52</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.5</v>
+        <v>1.29</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.6</v>
+        <v>1.24</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.199999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.6</v>
+        <v>1.29</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.6</v>
+        <v>1.29</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.2</v>
+        <v>1.23</v>
       </c>
       <c r="AX4" t="n">
-        <v>14.5</v>
+        <v>1.29</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14.5</v>
+        <v>1.33</v>
       </c>
       <c r="BA4" t="n">
-        <v>8</v>
+        <v>1.29</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.8</v>
+        <v>1.29</v>
       </c>
       <c r="BC4" t="n">
-        <v>22</v>
+        <v>1.17</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.4</v>
+        <v>1.27</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.4</v>
+        <v>1.29</v>
       </c>
       <c r="BF4" t="n">
-        <v>16.5</v>
+        <v>1.53</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.8</v>
+        <v>1.26</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,99 +1605,99 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>CA Rentistas</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Colon FC</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.51</v>
+        <v>2.1</v>
       </c>
       <c r="G5" t="n">
-        <v>1.56</v>
+        <v>2.2</v>
       </c>
       <c r="H5" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>8.6</v>
+        <v>4.3</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>2.66</v>
       </c>
       <c r="O5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.3</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.13</v>
-      </c>
       <c r="W5" t="n">
-        <v>2.78</v>
+        <v>1.83</v>
       </c>
       <c r="X5" t="n">
-        <v>17.5</v>
+        <v>9</v>
       </c>
       <c r="Y5" t="n">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="AA5" t="n">
-        <v>270</v>
+        <v>190</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>420</v>
+        <v>90</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AG5" t="n">
         <v>11</v>
@@ -1706,121 +1706,121 @@
         <v>32</v>
       </c>
       <c r="AI5" t="n">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="AJ5" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="AK5" t="n">
-        <v>18.5</v>
+        <v>38</v>
       </c>
       <c r="AL5" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AM5" t="n">
-        <v>630</v>
+        <v>360</v>
       </c>
       <c r="AN5" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="AO5" t="n">
-        <v>360</v>
+        <v>170</v>
       </c>
       <c r="AP5" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>19</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX5" t="n">
         <v>10</v>
       </c>
-      <c r="AS5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>150</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>75</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>180</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AV5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX5" t="n">
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT5" t="n">
         <v>7.6</v>
       </c>
-      <c r="AY5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BU5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1832,24 +1832,24 @@
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Supra du Quebec</t>
+          <t>CSD Rangers</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Club Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.66</v>
+        <v>2.32</v>
       </c>
       <c r="G6" t="n">
-        <v>1.74</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>2.56</v>
+        <v>1.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="R6" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>2.44</v>
+        <v>3.65</v>
       </c>
       <c r="T6" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="U6" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="V6" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="W6" t="n">
-        <v>2.32</v>
+        <v>1.71</v>
       </c>
       <c r="X6" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AA6" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AB6" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AC6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AG6" t="n">
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18.5</v>
+        <v>48</v>
       </c>
       <c r="AK6" t="n">
-        <v>18.5</v>
+        <v>36</v>
       </c>
       <c r="AL6" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AM6" t="n">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AN6" t="n">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="AO6" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="AP6" t="n">
-        <v>19.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU6" t="n">
         <v>6.6</v>
       </c>
-      <c r="AT6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>9</v>
-      </c>
       <c r="AV6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC6" t="n">
         <v>10</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>12</v>
       </c>
       <c r="BD6" t="n">
         <v>6.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.4</v>
+        <v>80</v>
       </c>
       <c r="BF6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BP6" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BR6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT6" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BV6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,752 +2113,244 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CA Rentistas</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>Deportes Recoleta</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="G7" t="n">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="H7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N7" t="n">
         <v>4.1</v>
       </c>
-      <c r="I7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.62</v>
-      </c>
       <c r="O7" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.66</v>
+        <v>1.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>1.71</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W7" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="X7" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
         <v>950</v>
       </c>
       <c r="AI7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM7" t="n">
         <v>130</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
       <c r="AN7" t="n">
-        <v>34</v>
+        <v>14.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AX7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.7</v>
+        <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.3</v>
+        <v>80</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.72</v>
+        <v>3.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.38</v>
+        <v>100</v>
       </c>
       <c r="BN7" t="n">
         <v>4.7</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.14</v>
+        <v>8</v>
       </c>
       <c r="BT7" t="n">
-        <v>7.8</v>
+        <v>950</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Chilean Primera B</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CSD Rangers</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Club Deportes Santa Cruz</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="X8" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-06-06 18:34:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Chilean Primera B</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Deportes Iquique</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Deportes Recoleta</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chilean Segunda Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Deportes Rengo Unido</t>
+          <t>CA Rentistas</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lota Schwager</t>
+          <t>Colon FC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="H2" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="I2" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -881,31 +881,31 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="O2" t="n">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="R2" t="n">
         <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="T2" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U2" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="V2" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="W2" t="n">
         <v>1.01</v>
@@ -914,109 +914,109 @@
         <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.8</v>
+        <v>880</v>
       </c>
       <c r="AA2" t="n">
-        <v>95</v>
+        <v>970</v>
       </c>
       <c r="AB2" t="n">
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.4</v>
+        <v>850</v>
       </c>
       <c r="AD2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS2" t="n">
         <v>30</v>
       </c>
-      <c r="AE2" t="n">
-        <v>400</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>320</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>44</v>
-      </c>
       <c r="AT2" t="n">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AW2" t="n">
-        <v>13.5</v>
+        <v>38</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AY2" t="n">
         <v>32</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.800000000000001</v>
+        <v>90</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>9.800000000000001</v>
+        <v>120</v>
       </c>
       <c r="BD2" t="n">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.800000000000001</v>
+        <v>120</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.800000000000001</v>
+        <v>70</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>CSD Rangers</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Club Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.62</v>
+        <v>3.7</v>
       </c>
       <c r="G3" t="n">
-        <v>1.68</v>
+        <v>3.9</v>
       </c>
       <c r="H3" t="n">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>10</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S3" t="n">
+        <v>38</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>290</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU3" t="n">
         <v>8.4</v>
       </c>
-      <c r="J3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S3" t="n">
-        <v>7</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="X3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>420</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>290</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>310</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>210</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8</v>
-      </c>
       <c r="AV3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY3" t="n">
         <v>30</v>
       </c>
-      <c r="AW3" t="n">
-        <v>170</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="BA3" t="n">
+        <v>190</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>150</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>250</v>
+      </c>
+      <c r="BG3" t="n">
         <v>160</v>
       </c>
-      <c r="BB3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>90</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>330</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>150</v>
-      </c>
       <c r="BH3" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,72 +1351,72 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FC Supra du Quebec</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Deportes Recoleta</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="G4" t="n">
-        <v>1.79</v>
+        <v>1.31</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
+        <v>20</v>
       </c>
       <c r="I4" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="J4" t="n">
-        <v>1.09</v>
+        <v>5.3</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V4" t="n">
         <v>1.04</v>
       </c>
-      <c r="N4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1431,926 +1431,164 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO4" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.23</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.52</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.29</v>
+        <v>10.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.24</v>
+        <v>10.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.29</v>
+        <v>3.55</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.29</v>
+        <v>6.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.29</v>
+        <v>23</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.23</v>
+        <v>130</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.29</v>
+        <v>4.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.33</v>
+        <v>30</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.29</v>
+        <v>140</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.29</v>
+        <v>11.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.17</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.27</v>
+        <v>65</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.29</v>
+        <v>220</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.53</v>
+        <v>23</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.26</v>
+        <v>240</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Uruguayan Segunda Division</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CA Rentistas</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Colon FC</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="X5" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>230</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>360</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>150</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>23</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>75</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>180</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>2026-06-06 20:44:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Chilean Primera B</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CSD Rangers</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Club Deportes Santa Cruz</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="X6" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-06-06 20:44:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Chilean Primera B</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Deportes Iquique</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Deportes Recoleta</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="X7" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>100</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>950</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
